--- a/tame_output/ON/bt/strategyON_20240815.xlsx
+++ b/tame_output/ON/bt/strategyON_20240815.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>91.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-647.5%</t>
+          <t>-649.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.8%</t>
+          <t>-168.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-156.5%</t>
+          <t>-158.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
     </row>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.685161381615278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803188</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.764245306094328</v>
+        <v>2.706750647194325</v>
       </c>
       <c r="D1967" t="n">
         <v>-4.134655996801031</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.110026483060168</v>
+        <v>1.052531824160165</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.096058402132512</v>
+        <v>3.03856374323251</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.764907654485986</v>
+        <v>2.707412995585984</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.128503290748247</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.11314991387294</v>
+        <v>1.055655254972937</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.042917715255839</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>2.706493472326094</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.145312588898749</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.105506671352849</v>
+        <v>1.048012012452847</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.031912613105648</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>2.772829026122915</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.083014590122627</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.196761424660119</v>
+        <v>1.139266765760117</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.125424725467134</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>2.575121027837042</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.881224392457469</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.079769505440309</v>
+        <v>1.022274846540307</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.046527642482754</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>2.645411260159217</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.932111105143663</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.129705052688007</v>
+        <v>1.072210393788004</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.086285847193213</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>2.660038996275261</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.845500362493856</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.178977085863973</v>
+        <v>1.121482426963971</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.148089022032351</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>2.658574977099932</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.905709660499141</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.153429347486531</v>
+        <v>1.095934688586529</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.110499424053852</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>2.657066595139861</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.829287614067214</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.18248978409923</v>
+        <v>1.124995125199228</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.108991042093781</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>2.656929462575297</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.784914482428645</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.200101904190094</v>
+        <v>1.142607245290092</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.135477788512358</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>2.651323256713888</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.80739483328753</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.185503557985131</v>
+        <v>1.128008899085128</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.129871582650948</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>2.657705013741692</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.759739102726474</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.210947607237358</v>
+        <v>1.153452948337355</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.164846778015387</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>2.662597387116417</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.659220944227719</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.256047244011584</v>
+        <v>1.198552585111582</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.230050046489364</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>2.649352059592289</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.643315614795367</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.249164048260397</v>
+        <v>1.191669389360395</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.169337122539693</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>2.653449762202918</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.598477213186969</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.271197111514385</v>
+        <v>1.213702452614383</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.176160884917243</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>2.657610701833996</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.617975669428977</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.26755866864866</v>
+        <v>1.210064009748658</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.151471039780379</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>2.663490304361833</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.573772832343077</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.291119406010857</v>
+        <v>1.233624747110855</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.183872344559756</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>2.661900304831081</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.581332498180124</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.286505540145286</v>
+        <v>1.229010881245284</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.215164387434895</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>2.71314807001412</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.423041080640851</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.401069872344035</v>
+        <v>1.343575213444032</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.266412152617935</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>2.711588774608373</v>
       </c>
       <c r="D1986" t="n">
         <v>-3.215399077006375</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.482567378392078</v>
+        <v>1.425072719492076</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.389438059392874</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>2.706537002846643</v>
       </c>
       <c r="D1987" t="n">
         <v>-3.164366984283847</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.497928443719359</v>
+        <v>1.440433784819357</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.415005543264661</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>2.723724406939348</v>
       </c>
       <c r="D1988" t="n">
         <v>-3.099142803156641</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.541205520262947</v>
+        <v>1.483710861362944</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.471327456033689</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>2.719685379238629</v>
       </c>
       <c r="D1989" t="n">
         <v>-3.061715783085508</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.552137300590681</v>
+        <v>1.494642641690678</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.470439351150478</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>2.720942171569869</v>
       </c>
       <c r="D1990" t="n">
         <v>-3.081827439120216</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.545349430508038</v>
+        <v>1.487854771608035</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535807209380172</v>
+        <v>3.47831255048017</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>2.88149994259108</v>
       </c>
       <c r="D1991" t="n">
         <v>-3.028082624693011</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.72740512730013</v>
+        <v>1.669910468400128</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.702402966065661</v>
+        <v>3.644908307165658</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>3.001612851808897</v>
       </c>
       <c r="D1992" t="n">
         <v>-2.953300363667998</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.877430940927953</v>
+        <v>1.81993628202795</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.867385231898485</v>
+        <v>3.809890572998483</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>2.993320827822756</v>
       </c>
       <c r="D1993" t="n">
         <v>-2.92721627940419</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.879572550647335</v>
+        <v>1.822077891747332</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.859093207912344</v>
+        <v>3.801598549012342</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>2.991514023406535</v>
       </c>
       <c r="D1994" t="n">
         <v>-2.83933836629507</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.912916911474762</v>
+        <v>1.85542225257476</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.926841788950134</v>
+        <v>3.869347130050132</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>3.009068429133327</v>
       </c>
       <c r="D1995" t="n">
         <v>-2.830445904901786</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.934028301758867</v>
+        <v>1.876533642858865</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.944396194676925</v>
+        <v>3.886901535776923</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>3.000923476537911</v>
       </c>
       <c r="D1996" t="n">
         <v>-2.998922021871664</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.8584929023755</v>
+        <v>1.800998243475498</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.919482540651561</v>
+        <v>3.861987881751559</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>2.982193173725773</v>
       </c>
       <c r="D1997" t="n">
         <v>-2.552665829242224</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.018265076615138</v>
+        <v>1.960770417715135</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.843921036037643</v>
+        <v>3.786426377137641</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>2.972857196222677</v>
       </c>
       <c r="D1998" t="n">
         <v>-2.529944725559072</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.018017540585303</v>
+        <v>1.960522881685301</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.834585058534548</v>
+        <v>3.777090399634546</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>3.131763322073846</v>
       </c>
       <c r="D1999" t="n">
         <v>-2.659146538853114</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.125242941118855</v>
+        <v>2.067748282218853</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.915970096409292</v>
+        <v>3.85847543750929</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>3.168841144567493</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.81392754563137</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.100408360901199</v>
+        <v>2.042913702001197</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933027314470253</v>
+        <v>3.87553265557025</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>3.165516500557038</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.806872855416196</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.099905592976814</v>
+        <v>2.042410934076812</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933935484588902</v>
+        <v>3.8764408256889</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>3.175522654201779</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.779921631089708</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.120692236352151</v>
+        <v>2.063197577452149</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952869845850275</v>
+        <v>3.895375186950273</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.359625786346739</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.915874639146025</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.250414165274584</v>
+        <v>2.192919506374582</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136972977995235</v>
+        <v>4.079478319095233</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.351742481249732</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.938282756950897</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.233567613055628</v>
+        <v>2.176072954155626</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129089672898228</v>
+        <v>4.071595013998226</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.35379648079937</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.966506992528497</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.224331918374226</v>
+        <v>2.166837259474224</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141929723918651</v>
+        <v>4.084435065018648</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.410050198521217</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.975947918417027</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.276809265740661</v>
+        <v>2.219314606840659</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271639712166532</v>
+        <v>4.21414505326653</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.412941293066518</v>
       </c>
       <c r="D2007" t="n">
         <v>-3.028221525752668</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.258790917351705</v>
+        <v>2.201296258451703</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.243166642310449</v>
+        <v>4.185671983410447</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.411053105960293</v>
       </c>
       <c r="D2008" t="n">
         <v>-3.104551503353574</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.226370739205118</v>
+        <v>2.168876080305116</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.241278455204224</v>
+        <v>4.183783796304222</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.405873335563155</v>
       </c>
       <c r="D2009" t="n">
         <v>-3.306805223677928</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.140289480678239</v>
+        <v>2.082794821778237</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.114746452612474</v>
+        <v>4.057251793712472</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.404307345773308</v>
       </c>
       <c r="D2010" t="n">
         <v>-3.468373649205183</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.074096120677489</v>
+        <v>2.016601461777487</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.037110708543898</v>
+        <v>3.979616049643896</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.417380752639226</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.600674941302736</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.034249010704387</v>
+        <v>1.976754351804384</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.050184115409817</v>
+        <v>3.992689456509815</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.409385949422166</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.786543252141966</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.951906883151635</v>
+        <v>1.894412224251632</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947049956200789</v>
+        <v>3.889555297300786</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.407909990549168</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.814444039251439</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.939270609434848</v>
+        <v>1.881775950534845</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.92481584284203</v>
+        <v>3.867321183942027</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.404674434526367</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.936970141954333</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.887024612330889</v>
+        <v>1.829529953430886</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848064625197492</v>
+        <v>3.79056996629749</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.471380394116871</v>
       </c>
       <c r="D2015" t="n">
         <v>-4.167484638139921</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.861524773447157</v>
+        <v>1.804030114547155</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.776461887076643</v>
+        <v>3.71896722817664</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.611692113118718</v>
       </c>
       <c r="D2016" t="n">
         <v>-4.424205456134745</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.899148165251075</v>
+        <v>1.841653506351072</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.851724861592201</v>
+        <v>3.794230202692199</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.680672382264357</v>
       </c>
       <c r="D2017" t="n">
         <v>-4.578191873910885</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.906533867286258</v>
+        <v>1.849039208386256</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.920705130737841</v>
+        <v>3.863210471837839</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.666723584384478</v>
       </c>
       <c r="D2018" t="n">
         <v>-4.527669970083219</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.912793830937445</v>
+        <v>1.855299172037443</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.906756332857962</v>
+        <v>3.849261673957959</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.678594073439892</v>
       </c>
       <c r="D2019" t="n">
         <v>-4.780145124090944</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.82367425838977</v>
+        <v>1.766179599489768</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.918626821913375</v>
+        <v>3.861132163013373</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.679804607958836</v>
       </c>
       <c r="D2020" t="n">
         <v>-5.073040880570356</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.707726490316948</v>
+        <v>1.650231831416946</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.919837356432319</v>
+        <v>3.862342697532317</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.683926350186157</v>
       </c>
       <c r="D2021" t="n">
         <v>-5.259705008705164</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.637182581290347</v>
+        <v>1.579687922390344</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2774911784645746</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.907915716164905</v>
+        <v>3.850421057264902</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.679004202922347</v>
       </c>
       <c r="D2022" t="n">
         <v>-5.537669404288438</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.521074675793227</v>
+        <v>1.463580016893224</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1878714441790904</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.849221728329804</v>
+        <v>3.791727069429801</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.841208259621391</v>
       </c>
       <c r="D2023" t="n">
         <v>-5.654637096927329</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.636491655436715</v>
+        <v>1.578996996536712</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1878714441790904</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.011425785028848</v>
+        <v>3.953931126128846</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.836054897585205</v>
       </c>
       <c r="D2024" t="n">
         <v>-5.739355039148282</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.597451116512147</v>
+        <v>1.539956457612145</v>
       </c>
       <c r="F2024" t="n">
         <v>0.102755415251044</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.955202805635834</v>
+        <v>3.897708146735832</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.846284315153696</v>
       </c>
       <c r="D2025" t="n">
         <v>-5.821289857417165</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.574906606773085</v>
+        <v>1.517411947873083</v>
       </c>
       <c r="F2025" t="n">
         <v>0.0928206696639638</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.959471375852077</v>
+        <v>3.901976716952075</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.855209953609599</v>
       </c>
       <c r="D2026" t="n">
         <v>-5.923265979665572</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.543041796329625</v>
+        <v>1.485547137429622</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.00915545258444378</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.907211340958935</v>
+        <v>3.849716682058933</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.847362840853774</v>
       </c>
       <c r="D2027" t="n">
         <v>-5.813259696188351</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.579197196964689</v>
+        <v>1.521702538064686</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01404911933283143</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.913286971353475</v>
+        <v>3.855792312453473</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.851612851575748</v>
       </c>
       <c r="D2028" t="n">
         <v>-5.670200120447426</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.640671037983033</v>
+        <v>1.583176379083031</v>
       </c>
       <c r="F2028" t="n">
         <v>0.02206254592281071</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.922345038029437</v>
+        <v>3.864850379129435</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.858873734458284</v>
       </c>
       <c r="D2029" t="n">
         <v>-5.368753394975588</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.768510611054304</v>
+        <v>1.711015952154302</v>
       </c>
       <c r="F2029" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.110473956195076</v>
+        <v>4.052979297295074</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.859844912210995</v>
       </c>
       <c r="D2030" t="n">
         <v>-5.393343639210772</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.759645691112941</v>
+        <v>1.702151032212939</v>
       </c>
       <c r="F2030" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.111445133947786</v>
+        <v>4.053950475047784</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.860687816590751</v>
       </c>
       <c r="D2031" t="n">
         <v>-5.342305263204252</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.780903945895304</v>
+        <v>1.723409286995302</v>
       </c>
       <c r="F2031" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.112288038327542</v>
+        <v>4.054793379427539</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.879725915464896</v>
       </c>
       <c r="D2032" t="n">
         <v>-5.301165968337621</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.816397762716102</v>
+        <v>1.7589031038161</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3646485662612788</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.156009714121665</v>
+        <v>4.098515055221664</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.695909911588831</v>
       </c>
       <c r="D2033" t="n">
         <v>-5.190559828258019</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.676824214871877</v>
+        <v>1.619329555971876</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4752547063408808</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.038557394293361</v>
+        <v>3.981062735393359</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.699411955662795</v>
       </c>
       <c r="D2034" t="n">
         <v>-5.321140562788861</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.628093965133504</v>
+        <v>1.570599306233503</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.963710997648819</v>
+        <v>3.906216338748818</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.683838774738877</v>
       </c>
       <c r="D2035" t="n">
         <v>-5.1566442285979</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.678319317885971</v>
+        <v>1.62082465898597</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.948137816724902</v>
+        <v>3.890643157824901</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.683026485175307</v>
       </c>
       <c r="D2036" t="n">
         <v>-5.184014161282332</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.666559055248628</v>
+        <v>1.609064396348627</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.947325527161332</v>
+        <v>3.88983086826133</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.692895264300379</v>
       </c>
       <c r="D2037" t="n">
         <v>-5.194399356172221</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.672273756417745</v>
+        <v>1.614779097517744</v>
       </c>
       <c r="F2037" t="n">
         <v>0.334288776920149</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.95096318935247</v>
+        <v>3.893468530452469</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.763732270076805</v>
       </c>
       <c r="D2038" t="n">
         <v>-5.212987514894446</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.73567549870528</v>
+        <v>1.678180839805279</v>
       </c>
       <c r="F2038" t="n">
         <v>0.3157006181979236</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.01064729989556</v>
+        <v>3.953152640995559</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.760601280895103</v>
       </c>
       <c r="D2039" t="n">
         <v>-5.213286061590482</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.732425090845164</v>
+        <v>1.674930431945163</v>
       </c>
       <c r="F2039" t="n">
         <v>0.3157006181979236</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.007516310713859</v>
+        <v>3.950021651813858</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.765132175834494</v>
       </c>
       <c r="D2040" t="n">
         <v>-5.112462927900054</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.777285239260727</v>
+        <v>1.719790580360725</v>
       </c>
       <c r="F2040" t="n">
         <v>0.3281648336822774</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.019525734943863</v>
+        <v>3.962031076043862</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.765261429313038</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.921681567147647</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.853727037040233</v>
+        <v>1.796232378140231</v>
       </c>
       <c r="F2041" t="n">
         <v>0.5189461944346848</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.13412380487385</v>
+        <v>4.076629145973849</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.745098275050634</v>
       </c>
       <c r="D2042" t="n">
         <v>-4.903164713105827</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.840970624394558</v>
+        <v>1.783475965494556</v>
       </c>
       <c r="F2042" t="n">
         <v>0.531876323859893</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.121718728266572</v>
+        <v>4.064224069366571</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.780065211662693</v>
       </c>
       <c r="D2043" t="n">
         <v>-4.877971528604509</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.886014834807143</v>
+        <v>1.828520175907142</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5570695083612114</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.171801575579421</v>
+        <v>4.11430691667942</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.77375177956413</v>
       </c>
       <c r="D2044" t="n">
         <v>-4.865917401691546</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.884523053473766</v>
+        <v>1.827028394573765</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5691236352741742</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.172720619628636</v>
+        <v>4.115225960728635</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.775632409748266</v>
       </c>
       <c r="D2045" t="n">
         <v>-4.872540648381904</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.883754384981759</v>
+        <v>1.826259726081757</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5625003885838158</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.170627301798557</v>
+        <v>4.113132642898556</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.788483435626149</v>
       </c>
       <c r="D2046" t="n">
         <v>-4.769660058853312</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.937757646671078</v>
+        <v>1.880262987771077</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.245206681393595</v>
+        <v>4.187712022493594</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.808686105799743</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.793102098033398</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.948583501172638</v>
+        <v>1.891088842272636</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.26540935156719</v>
+        <v>4.207914692667188</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.808686105799743</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.81117460632501</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.941354497855993</v>
+        <v>1.883859838955992</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.26540935156719</v>
+        <v>4.207914692667188</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.76893801939321</v>
       </c>
       <c r="D2049" t="n">
         <v>-5.042348400201642</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.809136893898807</v>
+        <v>1.751642234998806</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.225661265160657</v>
+        <v>4.168166606260655</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.77596063839015</v>
       </c>
       <c r="D2050" t="n">
         <v>-5.011062379661187</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.828673921111929</v>
+        <v>1.771179262211928</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6966669986528641</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.25145549648187</v>
+        <v>4.193960837581868</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.875131637963054</v>
       </c>
       <c r="D2051" t="n">
         <v>-4.858036987547902</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.989055077530147</v>
+        <v>1.931560418630146</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8496923907661482</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.442441731322744</v>
+        <v>4.384947072422743</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.120092521771348</v>
+        <v>4.062597862871346</v>
       </c>
       <c r="D2052" t="n">
         <v>-4.886344301421173</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.165198376889131</v>
+        <v>2.10770371798913</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8496923907661482</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.629907956231037</v>
+        <v>4.572413297331035</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.08949547312543</v>
+        <v>4.032000814225428</v>
       </c>
       <c r="D2053" t="n">
         <v>-5.052937526534695</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.067964038197804</v>
+        <v>2.010469379297803</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.499354972517006</v>
+        <v>4.441860313617005</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.093171875787148</v>
+        <v>4.035677216887146</v>
       </c>
       <c r="D2054" t="n">
         <v>-4.879873147152395</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.140866192612442</v>
+        <v>2.083371533712441</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.503031375178724</v>
+        <v>4.445536716278722</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.090789930910643</v>
+        <v>4.033295272010641</v>
       </c>
       <c r="D2055" t="n">
         <v>-4.850627166696698</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.150182639918216</v>
+        <v>2.092687981018215</v>
       </c>
       <c r="F2055" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.500649430302219</v>
+        <v>4.443154771402217</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.810858865958654</v>
+        <v>3.836705573978609</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.088083170068278</v>
+        <v>4.030588511168276</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.858840462417254</v>
+        <v>-4.876404574943747</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.144190560787629</v>
+        <v>2.07967025687703</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6748858699320706</v>
+        <v>0.6573217574055773</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.49301469202752</v>
+        <v>4.424981565611623</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240815.xlsx
+++ b/tame_output/ON/bt/strategyON_20240815.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-649.2%</t>
+          <t>-639.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-168.3%</t>
+          <t>-164.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.2%</t>
+          <t>-320.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-158.3%</t>
+          <t>-158.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.57367402532254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770575</v>
+        <v>3.676841549770574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615278</v>
+        <v>3.685161381615277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812098</v>
+        <v>3.684843823812097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646212</v>
+        <v>3.710935533646211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955323</v>
+        <v>3.728577929955322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232408</v>
+        <v>3.747702660232407</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436224</v>
+        <v>3.766317079436223</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388723</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626468</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.706750647194325</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.134655996801031</v>
+        <v>-4.03646207207102</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.052531824160165</v>
+        <v>1.09180939405217</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.707412995585984</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.128503290748247</v>
+        <v>-4.030309366018235</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.055655254972937</v>
+        <v>1.094932824864942</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
@@ -46838,10 +46838,10 @@
         <v>2.706493472326094</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.145312588898749</v>
+        <v>-4.047118664168737</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.048012012452847</v>
+        <v>1.087289582344852</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
@@ -46861,10 +46861,10 @@
         <v>2.772829026122915</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.083014590122627</v>
+        <v>-3.984820665392615</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.139266765760117</v>
+        <v>1.178544335652121</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.575121027837042</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.881224392457469</v>
+        <v>-3.783030467727457</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.022274846540307</v>
+        <v>1.061552416432312</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.645411260159217</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.932111105143663</v>
+        <v>-3.833917180413652</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.072210393788004</v>
+        <v>1.111487963680009</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.660038996275261</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.845500362493856</v>
+        <v>-3.747306437763845</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.121482426963971</v>
+        <v>1.160759996855975</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.658574977099932</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.905709660499141</v>
+        <v>-3.807515735769129</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.095934688586529</v>
+        <v>1.135212258478533</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.657066595139861</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.829287614067214</v>
+        <v>-3.731093689337202</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.124995125199228</v>
+        <v>1.164272695091233</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.656929462575297</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.784914482428645</v>
+        <v>-3.686720557698634</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.142607245290092</v>
+        <v>1.181884815182096</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.651323256713888</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.80739483328753</v>
+        <v>-3.709200908557519</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.128008899085128</v>
+        <v>1.167286468977133</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.657705013741692</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.759739102726474</v>
+        <v>-3.661545177996463</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.153452948337355</v>
+        <v>1.19273051822936</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.662597387116417</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.659220944227719</v>
+        <v>-3.561027019497709</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.198552585111582</v>
+        <v>1.237830155003586</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.649352059592289</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.643315614795367</v>
+        <v>-3.545121690065356</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.191669389360395</v>
+        <v>1.2309469592524</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.653449762202918</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.598477213186969</v>
+        <v>-3.500283288456958</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.213702452614383</v>
+        <v>1.252980022506387</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.657610701833996</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.617975669428977</v>
+        <v>-3.519781744698966</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.210064009748658</v>
+        <v>1.249341579640662</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.663490304361833</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.573772832343077</v>
+        <v>-3.475578907613066</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.233624747110855</v>
+        <v>1.272902317002859</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.661900304831081</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.581332498180124</v>
+        <v>-3.483138573450113</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.229010881245284</v>
+        <v>1.268288451137288</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.71314807001412</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.423041080640851</v>
+        <v>-3.32484715591084</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.343575213444032</v>
+        <v>1.382852783336037</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.711588774608373</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.215399077006375</v>
+        <v>-3.117205152276364</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.425072719492076</v>
+        <v>1.46435028938408</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.706537002846643</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.164366984283847</v>
+        <v>-3.066173059553836</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.440433784819357</v>
+        <v>1.479711354711362</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.723724406939348</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.099142803156641</v>
+        <v>-3.00094887842663</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.483710861362944</v>
+        <v>1.522988431254949</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.719685379238629</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.061715783085508</v>
+        <v>-2.963521858355497</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.494642641690678</v>
+        <v>1.533920211582683</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.720942171569869</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.081827439120216</v>
+        <v>-2.983633514390205</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.487854771608035</v>
+        <v>1.52713234150004</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.88149994259108</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.028082624693011</v>
+        <v>-2.929888699963</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.669910468400128</v>
+        <v>1.709188038292133</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.001612851808897</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.953300363667998</v>
+        <v>-2.855106438937987</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.81993628202795</v>
+        <v>1.859213851919955</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.993320827822756</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.92721627940419</v>
+        <v>-2.82902235467418</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.822077891747332</v>
+        <v>1.861355461639337</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.991514023406535</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.83933836629507</v>
+        <v>-2.741144441565059</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.85542225257476</v>
+        <v>1.894699822466765</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.009068429133327</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.830445904901786</v>
+        <v>-2.732251980171776</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.876533642858865</v>
+        <v>1.915811212750869</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.000923476537911</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.998922021871664</v>
+        <v>-2.900728097141653</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.800998243475498</v>
+        <v>1.840275813367502</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.982193173725773</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.552665829242224</v>
+        <v>-2.454471904512213</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.960770417715135</v>
+        <v>2.00004798760714</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.972857196222677</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.529944725559072</v>
+        <v>-2.431750800829061</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.960522881685301</v>
+        <v>1.999800451577305</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.131763322073846</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.659146538853114</v>
+        <v>-2.560952614123103</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.067748282218853</v>
+        <v>2.107025852110858</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.168841144567493</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.81392754563137</v>
+        <v>-2.715733620901359</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.042913702001197</v>
+        <v>2.082191271893202</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.165516500557038</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.806872855416196</v>
+        <v>-2.708678930686185</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.042410934076812</v>
+        <v>2.081688503968817</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.175522654201779</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.779921631089708</v>
+        <v>-2.681727706359697</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.063197577452149</v>
+        <v>2.102475147344153</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.359625786346739</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.915874639146025</v>
+        <v>-2.817680714416014</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.192919506374582</v>
+        <v>2.232197076266586</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.351742481249732</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.938282756950897</v>
+        <v>-2.840088832220886</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.176072954155626</v>
+        <v>2.215350524047631</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.35379648079937</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.966506992528497</v>
+        <v>-2.868313067798486</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.166837259474224</v>
+        <v>2.206114829366228</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.410050198521217</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.975947918417027</v>
+        <v>-2.877753993687016</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.219314606840659</v>
+        <v>2.258592176732663</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.412941293066518</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.028221525752668</v>
+        <v>-2.930027601022657</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.201296258451703</v>
+        <v>2.240573828343708</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.411053105960293</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.104551503353574</v>
+        <v>-3.006357578623563</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.168876080305116</v>
+        <v>2.20815365019712</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.405873335563155</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.306805223677928</v>
+        <v>-3.208611298947917</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.082794821778237</v>
+        <v>2.122072391670241</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.404307345773308</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.468373649205183</v>
+        <v>-3.370179724475172</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.016601461777487</v>
+        <v>2.055879031669491</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.417380752639226</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.600674941302736</v>
+        <v>-3.502481016572725</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.976754351804384</v>
+        <v>2.016031921696389</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.409385949422166</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.786543252141966</v>
+        <v>-3.688349327411955</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.894412224251632</v>
+        <v>1.933689794143637</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.407909990549168</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.814444039251439</v>
+        <v>-3.716250114521428</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.881775950534845</v>
+        <v>1.92105352042685</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.404674434526367</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.936970141954333</v>
+        <v>-3.838776217224322</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.829529953430886</v>
+        <v>1.868807523322891</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.471380394116871</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.167484638139921</v>
+        <v>-4.06929071340991</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.804030114547155</v>
+        <v>1.843307684439159</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.611692113118718</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.424205456134745</v>
+        <v>-4.326011531404735</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.841653506351072</v>
+        <v>1.880931076243076</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.680672382264357</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.578191873910885</v>
+        <v>-4.479997949180875</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.849039208386256</v>
+        <v>1.88831677827826</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.666723584384478</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.527669970083219</v>
+        <v>-4.429476045353209</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.855299172037443</v>
+        <v>1.894576741929447</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
@@ -47988,10 +47988,10 @@
         <v>3.678594073439892</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.780145124090944</v>
+        <v>-4.681951199360934</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.766179599489768</v>
+        <v>1.805457169381772</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.679804607958836</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.073040880570356</v>
+        <v>-4.974846955840346</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.650231831416946</v>
+        <v>1.68950940130895</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.683926350186157</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.259705008705164</v>
+        <v>-5.161511083975154</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.579687922390344</v>
+        <v>1.618965492282348</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2774911784645746</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.679004202922347</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.537669404288438</v>
+        <v>-5.439475479558427</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.463580016893224</v>
+        <v>1.502857586785229</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1878714441790904</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.841208259621391</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.654637096927329</v>
+        <v>-5.556443172197318</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.578996996536712</v>
+        <v>1.618274566428716</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1878714441790904</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.836054897585205</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.739355039148282</v>
+        <v>-5.641161114418272</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.539956457612145</v>
+        <v>1.579234027504149</v>
       </c>
       <c r="F2024" t="n">
         <v>0.102755415251044</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.846284315153696</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.821289857417165</v>
+        <v>-5.723095932687155</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.517411947873083</v>
+        <v>1.556689517765087</v>
       </c>
       <c r="F2025" t="n">
         <v>0.0928206696639638</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.855209953609599</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.923265979665572</v>
+        <v>-5.825072054935562</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.485547137429622</v>
+        <v>1.524824707321626</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.00915545258444378</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.847362840853774</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.813259696188351</v>
+        <v>-5.715065771458341</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.521702538064686</v>
+        <v>1.560980107956691</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01404911933283143</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.851612851575748</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.670200120447426</v>
+        <v>-5.572006195717416</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.583176379083031</v>
+        <v>1.622453948975035</v>
       </c>
       <c r="F2028" t="n">
         <v>0.02206254592281071</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.858873734458284</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.368753394975588</v>
+        <v>-5.270559470245578</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.711015952154302</v>
+        <v>1.750293522046306</v>
       </c>
       <c r="F2029" t="n">
         <v>0.323509271394648</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.859844912210995</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.393343639210772</v>
+        <v>-5.295149714480762</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.702151032212939</v>
+        <v>1.741428602104943</v>
       </c>
       <c r="F2030" t="n">
         <v>0.323509271394648</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.860687816590751</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.342305263204252</v>
+        <v>-5.244111338474242</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.723409286995302</v>
+        <v>1.762686856887306</v>
       </c>
       <c r="F2031" t="n">
         <v>0.323509271394648</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.879725915464896</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.301165968337621</v>
+        <v>-5.202972043607611</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.7589031038161</v>
+        <v>1.798180673708104</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3646485662612788</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.695909911588831</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.190559828258019</v>
+        <v>-5.092365903528009</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.619329555971876</v>
+        <v>1.65860712586388</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4752547063408808</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.699411955662795</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.321140562788861</v>
+        <v>-5.222946638058851</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.570599306233503</v>
+        <v>1.609876876125507</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3446739718100383</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.683838774738877</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.1566442285979</v>
+        <v>-5.05845030386789</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.62082465898597</v>
+        <v>1.660102228877974</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3446739718100383</v>
@@ -48379,10 +48379,10 @@
         <v>3.683026485175307</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.184014161282332</v>
+        <v>-5.085820236552322</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.609064396348627</v>
+        <v>1.648341966240631</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3446739718100383</v>
@@ -48402,10 +48402,10 @@
         <v>3.692895264300379</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.194399356172221</v>
+        <v>-5.096205431442211</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.614779097517744</v>
+        <v>1.654056667409748</v>
       </c>
       <c r="F2037" t="n">
         <v>0.334288776920149</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.763732270076805</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.212987514894446</v>
+        <v>-5.114793590164436</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.678180839805279</v>
+        <v>1.717458409697283</v>
       </c>
       <c r="F2038" t="n">
         <v>0.3157006181979236</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.760601280895103</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.213286061590482</v>
+        <v>-5.115092136860472</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.674930431945163</v>
+        <v>1.714208001837167</v>
       </c>
       <c r="F2039" t="n">
         <v>0.3157006181979236</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.765132175834494</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.112462927900054</v>
+        <v>-5.014269003170044</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.719790580360725</v>
+        <v>1.759068150252729</v>
       </c>
       <c r="F2040" t="n">
         <v>0.3281648336822774</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.765261429313038</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.921681567147647</v>
+        <v>-4.823487642417637</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.796232378140231</v>
+        <v>1.835509948032235</v>
       </c>
       <c r="F2041" t="n">
         <v>0.5189461944346848</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.745098275050634</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.903164713105827</v>
+        <v>-4.804970788375817</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.783475965494556</v>
+        <v>1.82275353538656</v>
       </c>
       <c r="F2042" t="n">
         <v>0.531876323859893</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.780065211662693</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.877971528604509</v>
+        <v>-4.779777603874499</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.828520175907142</v>
+        <v>1.867797745799146</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5570695083612114</v>
@@ -48563,10 +48563,10 @@
         <v>3.77375177956413</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.865917401691546</v>
+        <v>-4.767723476961536</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.827028394573765</v>
+        <v>1.866305964465769</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5691236352741742</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811009</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.775632409748266</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.872540648381904</v>
+        <v>-4.774346723651894</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.826259726081757</v>
+        <v>1.865537295973761</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5625003885838158</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.788483435626149</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.769660058853312</v>
+        <v>-4.671466134123301</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.880262987771077</v>
+        <v>1.919540557663081</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6653809781124087</v>
@@ -48632,10 +48632,10 @@
         <v>3.808686105799743</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.793102098033398</v>
+        <v>-4.694908173303388</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.891088842272636</v>
+        <v>1.93036641216464</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6653809781124087</v>
@@ -48655,10 +48655,10 @@
         <v>3.808686105799743</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.81117460632501</v>
+        <v>-4.712980681595</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.883859838955992</v>
+        <v>1.923137408847996</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6653809781124087</v>
@@ -48678,10 +48678,10 @@
         <v>3.76893801939321</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.042348400201642</v>
+        <v>-4.944154475471632</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.751642234998806</v>
+        <v>1.790919804890809</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6653809781124087</v>
@@ -48701,10 +48701,10 @@
         <v>3.77596063839015</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.011062379661187</v>
+        <v>-4.912868454931177</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.771179262211928</v>
+        <v>1.810456832103932</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6966669986528641</v>
@@ -48724,10 +48724,10 @@
         <v>3.875131637963054</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.858036987547902</v>
+        <v>-4.759843062817892</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.931560418630146</v>
+        <v>1.97083798852215</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8496923907661482</v>
@@ -48747,10 +48747,10 @@
         <v>4.062597862871346</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.886344301421173</v>
+        <v>-4.788150376691163</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.10770371798913</v>
+        <v>2.146981287881134</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8496923907661482</v>
@@ -48770,10 +48770,10 @@
         <v>4.032000814225428</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.052937526534695</v>
+        <v>-4.954743601804685</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.010469379297803</v>
+        <v>2.049746949189807</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6830991656526257</v>
@@ -48793,10 +48793,10 @@
         <v>4.035677216887146</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.879873147152395</v>
+        <v>-4.781679222422385</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.083371533712441</v>
+        <v>2.122649103604445</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6830991656526257</v>
@@ -48816,10 +48816,10 @@
         <v>4.033295272010641</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.850627166696698</v>
+        <v>-4.752433241966688</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.092687981018215</v>
+        <v>2.131965550910219</v>
       </c>
       <c r="F2055" t="n">
         <v>0.6830991656526257</v>
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.836705573978609</v>
+        <v>3.867440324112442</v>
       </c>
       <c r="C2056" t="n">
         <v>4.030588511168276</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.876404574943747</v>
+        <v>-4.778028851331075</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.07967025687703</v>
+        <v>2.119020546322099</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6573217574055773</v>
+        <v>0.6575035562882394</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.424981565611623</v>
+        <v>4.42509064494122</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240815.xlsx
+++ b/tame_output/ON/bt/strategyON_20240815.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>97.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.4%</t>
+          <t>-646.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.3%</t>
+          <t>-161.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.0%</t>
+          <t>-320.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-158.2%</t>
+          <t>-156.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
     </row>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.636292910321671</v>
+        <v>-4.628421434975942</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.109438407134259</v>
+        <v>1.112586997272551</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4646190436009336</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.618579223443805</v>
+        <v>-4.610707748098076</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.117202465802746</v>
+        <v>1.120351055941037</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4678003724978504</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.509774337964078</v>
+        <v>-4.501902862618349</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.15772249121463</v>
+        <v>1.160871081352921</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4678003724978504</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.289753539927068</v>
+        <v>-4.281882064581339</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.247309847440048</v>
+        <v>1.25045843757834</v>
       </c>
       <c r="F1929" t="n">
         <v>0.6090202175658307</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.15688585086379</v>
+        <v>-4.149014375518061</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.316351105867182</v>
+        <v>1.319499696005474</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.036712767499291</v>
+        <v>-4.028841292153563</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.365566183653284</v>
+        <v>1.368714773791575</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.901459406169314</v>
+        <v>-3.893587930823585</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.429755630746715</v>
+        <v>1.432904220885006</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.961334233527007</v>
+        <v>-3.953462758181278</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.391843191205064</v>
+        <v>1.394991781343355</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.841514002616169</v>
+        <v>-3.83364252727044</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.455060452803607</v>
+        <v>1.458209042941898</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.843983709077975</v>
+        <v>-3.836112233732246</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.361716769541326</v>
+        <v>1.364865359679618</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.912353895401985</v>
+        <v>-3.904482420056256</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253630556497024</v>
+        <v>1.256779146635315</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.926141948249032</v>
+        <v>-3.918270472903303</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.238552043990096</v>
+        <v>1.241700634128388</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.981662024141621</v>
+        <v>-3.973790548795892</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.353374850325263</v>
+        <v>1.356523440463554</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.806187764349152</v>
+        <v>-3.798316289003423</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.428131786234038</v>
+        <v>1.43128037637233</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.9171240169904</v>
+        <v>-3.909252541644672</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.359499313938746</v>
+        <v>1.362647904077037</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.883460471518119</v>
+        <v>-3.87558899617239</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.301503045529108</v>
+        <v>1.3046516356674</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8450413729493054</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.823607852314395</v>
+        <v>-3.815736376968667</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.33561647964273</v>
+        <v>1.338765069781021</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8450413729493054</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.737364389288018</v>
+        <v>-3.729492913942289</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.365060135427141</v>
+        <v>1.368208725565433</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8450413729493054</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.782671208686998</v>
+        <v>-3.774799733341269</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.338713183112075</v>
+        <v>1.341861773250366</v>
       </c>
       <c r="F1944" t="n">
         <v>0.8042312099400746</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.8117043133893</v>
+        <v>-3.803832838043571</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.327651814264256</v>
+        <v>1.330800404402547</v>
       </c>
       <c r="F1945" t="n">
         <v>0.8042312099400746</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.71889383193844</v>
+        <v>-3.711022356592712</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.294048698735965</v>
+        <v>1.297197288874257</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8970416913909339</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.763283301267868</v>
+        <v>-3.755411825922139</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.278166386928795</v>
+        <v>1.281314977067086</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8526522220615063</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.879824906373211</v>
+        <v>-3.871953431027482</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.226625453398381</v>
+        <v>1.229774043536672</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7361106169561635</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.919749000955782</v>
+        <v>-3.911877525610054</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.216147111396019</v>
+        <v>1.219295701534311</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7361106169561635</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.947529398857136</v>
+        <v>-3.939657923511407</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.216532154004017</v>
+        <v>1.219680744142309</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7083302190548104</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.065910071587274</v>
+        <v>-4.058038596241545</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.007535604912615</v>
+        <v>1.010684195050907</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6411123669038342</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.174524150030605</v>
+        <v>-4.166652674684876</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.084239634254488</v>
+        <v>1.08738822439278</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6411123669038342</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.139115111782462</v>
+        <v>-4.131243636436733</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.112916275656068</v>
+        <v>1.11606486579436</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.100731449224311</v>
+        <v>-4.092859973878582</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.125689182021698</v>
+        <v>1.128837772159989</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.923615119189145</v>
+        <v>-3.915743643843416</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.193264742881066</v>
+        <v>1.196413333019358</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.96870736402269</v>
+        <v>-3.960835888676962</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.175911236709561</v>
+        <v>1.179059826847852</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.789331942783923</v>
+        <v>-3.781460467438194</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.241448380511482</v>
+        <v>1.244596970649774</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.834346156304529</v>
+        <v>-3.8264746809588</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.20425015043483</v>
+        <v>1.207398740573121</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.101350666576964</v>
+        <v>-4.093479191231236</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.103139908664801</v>
+        <v>1.106288498803093</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.202548448014137</v>
+        <v>-4.194676972668408</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.061864717986433</v>
+        <v>1.065013308124725</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.196037481399824</v>
+        <v>-4.188166006054096</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.062069066186475</v>
+        <v>1.065217656324767</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.176999353692527</v>
+        <v>-4.169127878346798</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.066209036477639</v>
+        <v>1.069357626615931</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.229515155967348</v>
+        <v>-4.221643680621619</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.164497117201901</v>
+        <v>1.167645707340193</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.243381917301265</v>
+        <v>-4.235510441955537</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.159783741654468</v>
+        <v>1.162932331792759</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.198577745761336</v>
+        <v>-4.190706270415607</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.183713940667366</v>
+        <v>1.186862530805657</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.050834775526333</v>
+        <v>-4.042963300180604</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.140761350038566</v>
+        <v>1.143909940176858</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.706750647194325</v>
+        <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.03646207207102</v>
+        <v>-4.126784521455303</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.09180939405217</v>
+        <v>1.113175073198459</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.03856374323251</v>
+        <v>3.096058402132512</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.707412995585984</v>
+        <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.030309366018235</v>
+        <v>-4.120631815402518</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.094932824864942</v>
+        <v>1.116298504011231</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.042917715255839</v>
+        <v>3.100412374155841</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.706493472326094</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.047118664168737</v>
+        <v>-4.13744111355302</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.087289582344852</v>
+        <v>1.108655261491141</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.031912613105648</v>
+        <v>3.08940727200565</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.772829026122915</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.984820665392615</v>
+        <v>-4.075143114776898</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.178544335652121</v>
+        <v>1.199910014798411</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.125424725467134</v>
+        <v>3.182919384367136</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.575121027837042</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.783030467727457</v>
+        <v>-3.87335291711174</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.061552416432312</v>
+        <v>1.082918095578601</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.046527642482754</v>
+        <v>3.104022301382756</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.645411260159217</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.833917180413652</v>
+        <v>-3.924239629797935</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.111487963680009</v>
+        <v>1.132853642826298</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.086285847193213</v>
+        <v>3.143780506093215</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.660038996275261</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.747306437763845</v>
+        <v>-3.837628887148127</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.160759996855975</v>
+        <v>1.182125676002265</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.148089022032351</v>
+        <v>3.205583680932353</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.658574977099932</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.807515735769129</v>
+        <v>-3.897838185153412</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.135212258478533</v>
+        <v>1.156577937624823</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.110499424053852</v>
+        <v>3.167994082953854</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.657066595139861</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.731093689337202</v>
+        <v>-3.821416138721485</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.164272695091233</v>
+        <v>1.185638374237522</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.108991042093781</v>
+        <v>3.166485700993783</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.656929462575297</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.686720557698634</v>
+        <v>-3.777043007082916</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.181884815182096</v>
+        <v>1.203250494328385</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.135477788512358</v>
+        <v>3.19297244741236</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.651323256713888</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.709200908557519</v>
+        <v>-3.799523357941801</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.167286468977133</v>
+        <v>1.188652148123422</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.129871582650948</v>
+        <v>3.187366241550951</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.657705013741692</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.661545177996463</v>
+        <v>-3.751867627380745</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.19273051822936</v>
+        <v>1.214096197375649</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.164846778015387</v>
+        <v>3.222341436915389</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.662597387116417</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.561027019497709</v>
+        <v>-3.651349468881991</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.237830155003586</v>
+        <v>1.259195834149876</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.230050046489364</v>
+        <v>3.287544705389366</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.649352059592289</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.545121690065356</v>
+        <v>-3.635444139449638</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.2309469592524</v>
+        <v>1.252312638398689</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.169337122539693</v>
+        <v>3.226831781439695</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.653449762202918</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.500283288456958</v>
+        <v>-3.59060573784124</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.252980022506387</v>
+        <v>1.274345701652677</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.176160884917243</v>
+        <v>3.233655543817246</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.657610701833996</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.519781744698966</v>
+        <v>-3.610104194083248</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.249341579640662</v>
+        <v>1.270707258786951</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.151471039780379</v>
+        <v>3.208965698680381</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.663490304361833</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.475578907613066</v>
+        <v>-3.565901356997348</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.272902317002859</v>
+        <v>1.294267996149149</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.183872344559756</v>
+        <v>3.241367003459758</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.661900304831081</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.483138573450113</v>
+        <v>-3.573461022834395</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.268288451137288</v>
+        <v>1.289654130283578</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.215164387434895</v>
+        <v>3.272659046334898</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.71314807001412</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.32484715591084</v>
+        <v>-3.415169605295123</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.382852783336037</v>
+        <v>1.404218462482326</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.266412152617935</v>
+        <v>3.323906811517937</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.711588774608373</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.117205152276364</v>
+        <v>-3.207527601660646</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.46435028938408</v>
+        <v>1.48571596853037</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.389438059392874</v>
+        <v>3.446932718292876</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.706537002846643</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.066173059553836</v>
+        <v>-3.156495508938118</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.479711354711362</v>
+        <v>1.501077033857651</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.415005543264661</v>
+        <v>3.472500202164663</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.723724406939348</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.00094887842663</v>
+        <v>-3.091271327810913</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.522988431254949</v>
+        <v>1.544354110401238</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.471327456033689</v>
+        <v>3.528822114933691</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.719685379238629</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.963521858355497</v>
+        <v>-3.053844307739779</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.533920211582683</v>
+        <v>1.555285890728972</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.470439351150478</v>
+        <v>3.527934010050481</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.720942171569869</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.983633514390205</v>
+        <v>-3.073955963774487</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.52713234150004</v>
+        <v>1.548498020646329</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.47831255048017</v>
+        <v>3.535807209380172</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.88149994259108</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.929888699963</v>
+        <v>-3.020211149347282</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.709188038292133</v>
+        <v>1.730553717438422</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.644908307165658</v>
+        <v>3.702402966065661</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.001612851808897</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.855106438937987</v>
+        <v>-2.94542888832227</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.859213851919955</v>
+        <v>1.880579531066244</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.809890572998483</v>
+        <v>3.867385231898485</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.993320827822756</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.82902235467418</v>
+        <v>-2.919344804058462</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.861355461639337</v>
+        <v>1.882721140785626</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.801598549012342</v>
+        <v>3.859093207912344</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.991514023406535</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.741144441565059</v>
+        <v>-2.831466890949341</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.894699822466765</v>
+        <v>1.916065501613054</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.869347130050132</v>
+        <v>3.926841788950134</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.009068429133327</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.732251980171776</v>
+        <v>-2.822574429556058</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.915811212750869</v>
+        <v>1.937176891897159</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.886901535776923</v>
+        <v>3.944396194676925</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.000923476537911</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.900728097141653</v>
+        <v>-2.991050546525936</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.840275813367502</v>
+        <v>1.861641492513791</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.861987881751559</v>
+        <v>3.919482540651561</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.982193173725773</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.454471904512213</v>
+        <v>-2.544794353896496</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.00004798760714</v>
+        <v>2.021413666753429</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.786426377137641</v>
+        <v>3.843921036037643</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.972857196222677</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.431750800829061</v>
+        <v>-2.522073250213343</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.999800451577305</v>
+        <v>2.021166130723595</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.777090399634546</v>
+        <v>3.834585058534548</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.131763322073846</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.560952614123103</v>
+        <v>-2.651275063507386</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.107025852110858</v>
+        <v>2.128391531257147</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.85847543750929</v>
+        <v>3.915970096409292</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.168841144567493</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.715733620901359</v>
+        <v>-2.806056070285641</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.082191271893202</v>
+        <v>2.103556951039491</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.87553265557025</v>
+        <v>3.933027314470253</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.165516500557038</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.708678930686185</v>
+        <v>-2.799001380070468</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.081688503968817</v>
+        <v>2.103054183115106</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.8764408256889</v>
+        <v>3.933935484588902</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.175522654201779</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.681727706359697</v>
+        <v>-2.77205015574398</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.102475147344153</v>
+        <v>2.123840826490443</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.895375186950273</v>
+        <v>3.952869845850275</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.359625786346739</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.817680714416014</v>
+        <v>-2.908003163800296</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.232197076266586</v>
+        <v>2.253562755412876</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.079478319095233</v>
+        <v>4.136972977995235</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.351742481249732</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.840088832220886</v>
+        <v>-2.930411281605168</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.215350524047631</v>
+        <v>2.23671620319392</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.071595013998226</v>
+        <v>4.129089672898228</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.35379648079937</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.868313067798486</v>
+        <v>-2.958635517182768</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.206114829366228</v>
+        <v>2.227480508512517</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.084435065018648</v>
+        <v>4.141929723918651</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.410050198521217</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.877753993687016</v>
+        <v>-2.968076443071298</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.258592176732663</v>
+        <v>2.279957855878953</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.21414505326653</v>
+        <v>4.271639712166532</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.412941293066518</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.930027601022657</v>
+        <v>-3.02035005040694</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.240573828343708</v>
+        <v>2.261939507489997</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.185671983410447</v>
+        <v>4.243166642310449</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.411053105960293</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.006357578623563</v>
+        <v>-3.096680028007845</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.20815365019712</v>
+        <v>2.22951932934341</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.183783796304222</v>
+        <v>4.241278455204224</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.405873335563155</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.208611298947917</v>
+        <v>-3.298933748332199</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.122072391670241</v>
+        <v>2.143438070816531</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.057251793712472</v>
+        <v>4.114746452612474</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.404307345773308</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.370179724475172</v>
+        <v>-3.460502173859454</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.055879031669491</v>
+        <v>2.077244710815781</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.979616049643896</v>
+        <v>4.037110708543898</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.417380752639226</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.502481016572725</v>
+        <v>-3.592803465957007</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.016031921696389</v>
+        <v>2.037397600842678</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.992689456509815</v>
+        <v>4.050184115409817</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.409385949422166</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.688349327411955</v>
+        <v>-3.778671776796237</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.933689794143637</v>
+        <v>1.955055473289926</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.889555297300786</v>
+        <v>3.947049956200789</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.407909990549168</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.716250114521428</v>
+        <v>-3.80657256390571</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.92105352042685</v>
+        <v>1.942419199573139</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.867321183942027</v>
+        <v>3.92481584284203</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.404674434526367</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.838776217224322</v>
+        <v>-3.929098666608604</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.868807523322891</v>
+        <v>1.89017320246918</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.79056996629749</v>
+        <v>3.848064625197492</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.471380394116871</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.06929071340991</v>
+        <v>-4.159613162794193</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.843307684439159</v>
+        <v>1.864673363585449</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.71896722817664</v>
+        <v>3.776461887076643</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.611692113118718</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.326011531404735</v>
+        <v>-4.416333980789016</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.880931076243076</v>
+        <v>1.902296755389366</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.794230202692199</v>
+        <v>3.851724861592201</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.680672382264357</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.479997949180875</v>
+        <v>-4.570320398565157</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.88831677827826</v>
+        <v>1.90968245742455</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.863210471837839</v>
+        <v>3.920705130737841</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.666723584384478</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.429476045353209</v>
+        <v>-4.519798494737491</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.894576741929447</v>
+        <v>1.915942421075737</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.849261673957959</v>
+        <v>3.906756332857962</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.678594073439892</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.681951199360934</v>
+        <v>-4.772273648745215</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.805457169381772</v>
+        <v>1.826822848528061</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.861132163013373</v>
+        <v>3.918626821913375</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.679804607958836</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.974846955840346</v>
+        <v>-5.065169405224627</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.68950940130895</v>
+        <v>1.71087508045524</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.862342697532317</v>
+        <v>3.919837356432319</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.683926350186157</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.161511083975154</v>
+        <v>-5.251833533359435</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.618965492282348</v>
+        <v>1.640331171428638</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2774911784645746</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.850421057264902</v>
+        <v>3.907915716164905</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.679004202922347</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.439475479558427</v>
+        <v>-5.529797928942709</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.502857586785229</v>
+        <v>1.524223265931518</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1878714441790904</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.791727069429801</v>
+        <v>3.849221728329804</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.841208259621391</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.556443172197318</v>
+        <v>-5.6467656215816</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.618274566428716</v>
+        <v>1.639640245575006</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1878714441790904</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.953931126128846</v>
+        <v>4.011425785028848</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.836054897585205</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.641161114418272</v>
+        <v>-5.731483563802553</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.579234027504149</v>
+        <v>1.600599706650439</v>
       </c>
       <c r="F2024" t="n">
         <v>0.102755415251044</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.897708146735832</v>
+        <v>3.955202805635834</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.846284315153696</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.723095932687155</v>
+        <v>-5.813418382071436</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.556689517765087</v>
+        <v>1.578055196911377</v>
       </c>
       <c r="F2025" t="n">
         <v>0.0928206696639638</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.901976716952075</v>
+        <v>3.959471375852077</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.855209953609599</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.825072054935562</v>
+        <v>-5.915394504319844</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.524824707321626</v>
+        <v>1.546190386467916</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.00915545258444378</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.849716682058933</v>
+        <v>3.907211340958935</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.847362840853774</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.715065771458341</v>
+        <v>-5.805388220842622</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.560980107956691</v>
+        <v>1.58234578710298</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01404911933283143</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.855792312453473</v>
+        <v>3.913286971353475</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.851612851575748</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.572006195717416</v>
+        <v>-5.662328645101697</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.622453948975035</v>
+        <v>1.643819628121324</v>
       </c>
       <c r="F2028" t="n">
         <v>0.02206254592281071</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.864850379129435</v>
+        <v>3.922345038029437</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.858873734458284</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.270559470245578</v>
+        <v>-5.360881919629859</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.750293522046306</v>
+        <v>1.771659201192596</v>
       </c>
       <c r="F2029" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.052979297295074</v>
+        <v>4.110473956195076</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.859844912210995</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.295149714480762</v>
+        <v>-5.385472163865043</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.741428602104943</v>
+        <v>1.762794281251232</v>
       </c>
       <c r="F2030" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.053950475047784</v>
+        <v>4.111445133947786</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.860687816590751</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.244111338474242</v>
+        <v>-5.334433787858523</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.762686856887306</v>
+        <v>1.784052536033596</v>
       </c>
       <c r="F2031" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.054793379427539</v>
+        <v>4.112288038327542</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.879725915464896</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.202972043607611</v>
+        <v>-5.293294492991892</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.798180673708104</v>
+        <v>1.819546352854394</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3646485662612788</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.098515055221664</v>
+        <v>4.156009714121665</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.695909911588831</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.092365903528009</v>
+        <v>-5.18268835291229</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.65860712586388</v>
+        <v>1.679972805010169</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4752547063408808</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.981062735393359</v>
+        <v>4.038557394293361</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.699411955662795</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.222946638058851</v>
+        <v>-5.313269087443133</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.609876876125507</v>
+        <v>1.631242555271796</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.906216338748818</v>
+        <v>3.963710997648819</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.683838774738877</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.05845030386789</v>
+        <v>-5.148772753252171</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.660102228877974</v>
+        <v>1.681467908024263</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.890643157824901</v>
+        <v>3.948137816724902</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.683026485175307</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.085820236552322</v>
+        <v>-5.176142685936603</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.648341966240631</v>
+        <v>1.66970764538692</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.88983086826133</v>
+        <v>3.947325527161332</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.692895264300379</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.096205431442211</v>
+        <v>-5.186527880826493</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.654056667409748</v>
+        <v>1.675422346556037</v>
       </c>
       <c r="F2037" t="n">
         <v>0.334288776920149</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.893468530452469</v>
+        <v>3.95096318935247</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.763732270076805</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.114793590164436</v>
+        <v>-5.205116039548717</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.717458409697283</v>
+        <v>1.738824088843572</v>
       </c>
       <c r="F2038" t="n">
         <v>0.3157006181979236</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.953152640995559</v>
+        <v>4.01064729989556</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.760601280895103</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.115092136860472</v>
+        <v>-5.205414586244753</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.714208001837167</v>
+        <v>1.735573680983456</v>
       </c>
       <c r="F2039" t="n">
         <v>0.3157006181979236</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.950021651813858</v>
+        <v>4.007516310713859</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.765132175834494</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.014269003170044</v>
+        <v>-5.104591452554326</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.759068150252729</v>
+        <v>1.780433829399018</v>
       </c>
       <c r="F2040" t="n">
         <v>0.3281648336822774</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.962031076043862</v>
+        <v>4.019525734943863</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.765261429313038</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.823487642417637</v>
+        <v>-4.913810091801919</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.835509948032235</v>
+        <v>1.856875627178524</v>
       </c>
       <c r="F2041" t="n">
         <v>0.5189461944346848</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.076629145973849</v>
+        <v>4.13412380487385</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.745098275050634</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.804970788375817</v>
+        <v>-4.895293237760098</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.82275353538656</v>
+        <v>1.844119214532849</v>
       </c>
       <c r="F2042" t="n">
         <v>0.531876323859893</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.064224069366571</v>
+        <v>4.121718728266572</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.780065211662693</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.779777603874499</v>
+        <v>-4.87010005325878</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.867797745799146</v>
+        <v>1.889163424945435</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5570695083612114</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.11430691667942</v>
+        <v>4.171801575579421</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.77375177956413</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.767723476961536</v>
+        <v>-4.858045926345818</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.866305964465769</v>
+        <v>1.887671643612058</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5691236352741742</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.115225960728635</v>
+        <v>4.172720619628636</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.775632409748266</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.774346723651894</v>
+        <v>-4.864669173036176</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.865537295973761</v>
+        <v>1.88690297512005</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5625003885838158</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.113132642898556</v>
+        <v>4.170627301798557</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.788483435626149</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.671466134123301</v>
+        <v>-4.761788583507583</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.919540557663081</v>
+        <v>1.940906236809369</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.187712022493594</v>
+        <v>4.245206681393595</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.808686105799743</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.694908173303388</v>
+        <v>-4.78523062268767</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.93036641216464</v>
+        <v>1.951732091310929</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.207914692667188</v>
+        <v>4.26540935156719</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.808686105799743</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.712980681595</v>
+        <v>-4.803303130979281</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.923137408847996</v>
+        <v>1.944503087994285</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.207914692667188</v>
+        <v>4.26540935156719</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.76893801939321</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.944154475471632</v>
+        <v>-5.034476924855913</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.790919804890809</v>
+        <v>1.812285484037099</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.168166606260655</v>
+        <v>4.225661265160657</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.77596063839015</v>
+        <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.912868454931177</v>
+        <v>-5.003190904315458</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.810456832103932</v>
+        <v>1.83182251125022</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6966669986528641</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.193960837581868</v>
+        <v>4.25145549648187</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.875131637963054</v>
+        <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.759843062817892</v>
+        <v>-4.850165512202174</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.97083798852215</v>
+        <v>1.992203667668438</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8496923907661482</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.384947072422743</v>
+        <v>4.442441731322744</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.062597862871346</v>
+        <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.788150376691163</v>
+        <v>-4.878472826075444</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.146981287881134</v>
+        <v>2.168346967027423</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8496923907661482</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.572413297331035</v>
+        <v>4.629907956231037</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.032000814225428</v>
+        <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.954743601804685</v>
+        <v>-5.045066051188966</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.049746949189807</v>
+        <v>2.071112628336096</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.441860313617005</v>
+        <v>4.499354972517006</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.035677216887146</v>
+        <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.781679222422385</v>
+        <v>-4.872001671806666</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.122649103604445</v>
+        <v>2.144014782750734</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.445536716278722</v>
+        <v>4.503031375178724</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.033295272010641</v>
+        <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.752433241966688</v>
+        <v>-4.84275569135097</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.131965550910219</v>
+        <v>2.153331230056508</v>
       </c>
       <c r="F2055" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.443154771402217</v>
+        <v>4.500649430302219</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.867440324112442</v>
+        <v>3.77689768646953</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.030588511168276</v>
+        <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.778028851331075</v>
+        <v>-4.852470967689106</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.119020546322099</v>
+        <v>2.146738358678888</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6575035562882394</v>
+        <v>0.673383889314489</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.42509064494122</v>
+        <v>4.492113503656972</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240815.xlsx
+++ b/tame_output/ON/bt/strategyON_20240815.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>101.3%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-646.8%</t>
+          <t>-647.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.5%</t>
+          <t>-167.6%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.5%</t>
+          <t>-320.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-33.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2056"/>
+  <dimension ref="A1:G2057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191731</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108632</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097814</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094109</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199278</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969586</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.419979433923078</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737163</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341306</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539457</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764393</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297395</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532254</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158918</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940714</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770574</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615277</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812097</v>
+        <v>3.684843823812098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646211</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611563</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955322</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232407</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436223</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097238</v>
+        <v>3.800829354097237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017766</v>
+        <v>3.789311112017764</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839719</v>
+        <v>3.833252747839717</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388723</v>
+        <v>3.839374447388722</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626468</v>
+        <v>3.856161751626467</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.797694884242287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.821593509367677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.628421434975942</v>
+        <v>-4.636292910321671</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.112586997272551</v>
+        <v>1.109438407134259</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4646190436009336</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.610707748098076</v>
+        <v>-4.618579223443805</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.120351055941037</v>
+        <v>1.117202465802746</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4678003724978504</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.84861662650233</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.501902862618349</v>
+        <v>-4.509774337964078</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.160871081352921</v>
+        <v>1.15772249121463</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4678003724978504</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675931</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.281882064581339</v>
+        <v>-4.289753539927068</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.25045843757834</v>
+        <v>1.247309847440048</v>
       </c>
       <c r="F1929" t="n">
         <v>0.6090202175658307</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539942</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.149014375518061</v>
+        <v>-4.15688585086379</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.319499696005474</v>
+        <v>1.316351105867182</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.028841292153563</v>
+        <v>-4.036712767499291</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.368714773791575</v>
+        <v>1.365566183653284</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.893587930823585</v>
+        <v>-3.901459406169314</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.432904220885006</v>
+        <v>1.429755630746715</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.953462758181278</v>
+        <v>-3.961334233527007</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.394991781343355</v>
+        <v>1.391843191205064</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.83364252727044</v>
+        <v>-3.841514002616169</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.458209042941898</v>
+        <v>1.455060452803607</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.836112233732246</v>
+        <v>-3.843983709077975</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.364865359679618</v>
+        <v>1.361716769541326</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003595</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.904482420056256</v>
+        <v>-3.912353895401985</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.256779146635315</v>
+        <v>1.253630556497024</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.918270472903303</v>
+        <v>-3.926141948249032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.241700634128388</v>
+        <v>1.238552043990096</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.973790548795892</v>
+        <v>-3.981662024141621</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.356523440463554</v>
+        <v>1.353374850325263</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.798316289003423</v>
+        <v>-3.806187764349152</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.43128037637233</v>
+        <v>1.428131786234038</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225436</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.909252541644672</v>
+        <v>-3.9171240169904</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.362647904077037</v>
+        <v>1.359499313938746</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.87558899617239</v>
+        <v>-3.883460471518119</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.3046516356674</v>
+        <v>1.301503045529108</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8450413729493054</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.815736376968667</v>
+        <v>-3.823607852314395</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.338765069781021</v>
+        <v>1.33561647964273</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8450413729493054</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.729492913942289</v>
+        <v>-3.737364389288018</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.368208725565433</v>
+        <v>1.365060135427141</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8450413729493054</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.774799733341269</v>
+        <v>-3.782671208686998</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.341861773250366</v>
+        <v>1.338713183112075</v>
       </c>
       <c r="F1944" t="n">
         <v>0.8042312099400746</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803188</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.803832838043571</v>
+        <v>-3.8117043133893</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.330800404402547</v>
+        <v>1.327651814264256</v>
       </c>
       <c r="F1945" t="n">
         <v>0.8042312099400746</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.711022356592712</v>
+        <v>-3.71889383193844</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.297197288874257</v>
+        <v>1.294048698735965</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8970416913909339</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.755411825922139</v>
+        <v>-3.763283301267868</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.281314977067086</v>
+        <v>1.278166386928795</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8526522220615063</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.871953431027482</v>
+        <v>-3.879824906373211</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.229774043536672</v>
+        <v>1.226625453398381</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7361106169561635</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.911877525610054</v>
+        <v>-3.919749000955782</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.219295701534311</v>
+        <v>1.216147111396019</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7361106169561635</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.939657923511407</v>
+        <v>-3.947529398857136</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.219680744142309</v>
+        <v>1.216532154004017</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7083302190548104</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.058038596241545</v>
+        <v>-4.065910071587274</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.010684195050907</v>
+        <v>1.007535604912615</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6411123669038342</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.166652674684876</v>
+        <v>-4.174524150030605</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.08738822439278</v>
+        <v>1.084239634254488</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6411123669038342</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.131243636436733</v>
+        <v>-4.139115111782462</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.11606486579436</v>
+        <v>1.112916275656068</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.092859973878582</v>
+        <v>-4.100731449224311</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.128837772159989</v>
+        <v>1.125689182021698</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.915743643843416</v>
+        <v>-3.923615119189145</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.196413333019358</v>
+        <v>1.193264742881066</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.960835888676962</v>
+        <v>-3.96870736402269</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.179059826847852</v>
+        <v>1.175911236709561</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.781460467438194</v>
+        <v>-3.789331942783923</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.244596970649774</v>
+        <v>1.241448380511482</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.8264746809588</v>
+        <v>-3.834346156304529</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.207398740573121</v>
+        <v>1.20425015043483</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.093479191231236</v>
+        <v>-4.101350666576964</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.106288498803093</v>
+        <v>1.103139908664801</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.194676972668408</v>
+        <v>-4.202548448014137</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.065013308124725</v>
+        <v>1.061864717986433</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.188166006054096</v>
+        <v>-4.196037481399824</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.065217656324767</v>
+        <v>1.062069066186475</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.169127878346798</v>
+        <v>-4.176999353692527</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.069357626615931</v>
+        <v>1.066209036477639</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.221643680621619</v>
+        <v>-4.229515155967348</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.167645707340193</v>
+        <v>1.164497117201901</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.235510441955537</v>
+        <v>-4.243381917301265</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.162932331792759</v>
+        <v>1.159783741654468</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.190706270415607</v>
+        <v>-4.198577745761336</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.186862530805657</v>
+        <v>1.183713940667366</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.042963300180604</v>
+        <v>-4.050834775526333</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.143909940176858</v>
+        <v>1.140761350038566</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.764245306094328</v>
+        <v>2.706750647194325</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.126784521455303</v>
+        <v>-4.134655996801031</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.113175073198459</v>
+        <v>1.052531824160165</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.096058402132512</v>
+        <v>3.03856374323251</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.764907654485986</v>
+        <v>2.707412995585984</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.120631815402518</v>
+        <v>-4.128503290748247</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.116298504011231</v>
+        <v>1.055655254972937</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.042917715255839</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.763988131226096</v>
+        <v>2.706493472326094</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.13744111355302</v>
+        <v>-4.145312588898749</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.108655261491141</v>
+        <v>1.048012012452847</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.031912613105648</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.86736263679842</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.830323685022917</v>
+        <v>2.772829026122915</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.075143114776898</v>
+        <v>-4.083014590122627</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.199910014798411</v>
+        <v>1.139266765760117</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.125424725467134</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.632615686737044</v>
+        <v>2.575121027837042</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.87335291711174</v>
+        <v>-3.881224392457469</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.082918095578601</v>
+        <v>1.022274846540307</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.046527642482754</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.702905919059219</v>
+        <v>2.645411260159217</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.924239629797935</v>
+        <v>-3.932111105143663</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.132853642826298</v>
+        <v>1.072210393788004</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.086285847193213</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319538</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.717533655175263</v>
+        <v>2.660038996275261</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.837628887148127</v>
+        <v>-3.845500362493856</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.182125676002265</v>
+        <v>1.121482426963971</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.148089022032351</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489378</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.716069635999935</v>
+        <v>2.658574977099932</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.897838185153412</v>
+        <v>-3.905709660499141</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.156577937624823</v>
+        <v>1.095934688586529</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.110499424053852</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397787</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.714561254039863</v>
+        <v>2.657066595139861</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.821416138721485</v>
+        <v>-3.829287614067214</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.185638374237522</v>
+        <v>1.124995125199228</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.108991042093781</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316242</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.714424121475299</v>
+        <v>2.656929462575297</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.777043007082916</v>
+        <v>-3.784914482428645</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.203250494328385</v>
+        <v>1.142607245290092</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.135477788512358</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.70881791561389</v>
+        <v>2.651323256713888</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.799523357941801</v>
+        <v>-3.80739483328753</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.188652148123422</v>
+        <v>1.128008899085128</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.129871582650948</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.715199672641694</v>
+        <v>2.657705013741692</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.751867627380745</v>
+        <v>-3.759739102726474</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.214096197375649</v>
+        <v>1.153452948337355</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.164846778015387</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.720092046016419</v>
+        <v>2.662597387116417</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.651349468881991</v>
+        <v>-3.659220944227719</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.259195834149876</v>
+        <v>1.198552585111582</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.230050046489364</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.706846718492292</v>
+        <v>2.649352059592289</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.635444139449638</v>
+        <v>-3.643315614795367</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.252312638398689</v>
+        <v>1.191669389360395</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.169337122539693</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932763</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.71094442110292</v>
+        <v>2.653449762202918</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.59060573784124</v>
+        <v>-3.598477213186969</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.274345701652677</v>
+        <v>1.213702452614383</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.176160884917243</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.715105360733998</v>
+        <v>2.657610701833996</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.610104194083248</v>
+        <v>-3.617975669428977</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.270707258786951</v>
+        <v>1.210064009748658</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.151471039780379</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.720984963261835</v>
+        <v>2.663490304361833</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.565901356997348</v>
+        <v>-3.573772832343077</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.294267996149149</v>
+        <v>1.233624747110855</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.183872344559756</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265638</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.719394963731083</v>
+        <v>2.661900304831081</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.573461022834395</v>
+        <v>-3.581332498180124</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.289654130283578</v>
+        <v>1.229010881245284</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.215164387434895</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.770642728914122</v>
+        <v>2.71314807001412</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.415169605295123</v>
+        <v>-3.423041080640851</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.404218462482326</v>
+        <v>1.343575213444032</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.266412152617935</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.769083433508376</v>
+        <v>2.711588774608373</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.207527601660646</v>
+        <v>-3.215399077006375</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.48571596853037</v>
+        <v>1.425072719492076</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.389438059392874</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.764031661746646</v>
+        <v>2.706537002846643</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.156495508938118</v>
+        <v>-3.164366984283847</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.501077033857651</v>
+        <v>1.440433784819357</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.415005543264661</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404846</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.781219065839351</v>
+        <v>2.723724406939348</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.091271327810913</v>
+        <v>-3.099142803156641</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.544354110401238</v>
+        <v>1.483710861362944</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.471327456033689</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.84006118688255</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.777180038138631</v>
+        <v>2.719685379238629</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.053844307739779</v>
+        <v>-3.061715783085508</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.555285890728972</v>
+        <v>1.494642641690678</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.470439351150478</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992653</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.778436830469871</v>
+        <v>2.720942171569869</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.073955963774487</v>
+        <v>-3.081827439120216</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.548498020646329</v>
+        <v>1.487854771608035</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535807209380172</v>
+        <v>3.47831255048017</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636279</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.938994601491082</v>
+        <v>2.88149994259108</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.020211149347282</v>
+        <v>-3.028082624693011</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.730553717438422</v>
+        <v>1.669910468400128</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.702402966065661</v>
+        <v>3.644908307165658</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957617</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.059107510708899</v>
+        <v>3.001612851808897</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.94542888832227</v>
+        <v>-2.953300363667998</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.880579531066244</v>
+        <v>1.81993628202795</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.867385231898485</v>
+        <v>3.809890572998483</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.050815486722758</v>
+        <v>2.993320827822756</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.919344804058462</v>
+        <v>-2.92721627940419</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.882721140785626</v>
+        <v>1.822077891747332</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.859093207912344</v>
+        <v>3.801598549012342</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.049008682306538</v>
+        <v>2.991514023406535</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.831466890949341</v>
+        <v>-2.83933836629507</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.916065501613054</v>
+        <v>1.85542225257476</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.926841788950134</v>
+        <v>3.869347130050132</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959852</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.066563088033329</v>
+        <v>3.009068429133327</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.822574429556058</v>
+        <v>-2.830445904901786</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.937176891897159</v>
+        <v>1.876533642858865</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.944396194676925</v>
+        <v>3.886901535776923</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.058418135437913</v>
+        <v>3.000923476537911</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.991050546525936</v>
+        <v>-2.998922021871664</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.861641492513791</v>
+        <v>1.800998243475498</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.919482540651561</v>
+        <v>3.861987881751559</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.039687832625775</v>
+        <v>2.982193173725773</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.544794353896496</v>
+        <v>-2.552665829242224</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.021413666753429</v>
+        <v>1.960770417715135</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.843921036037643</v>
+        <v>3.786426377137641</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.030351855122679</v>
+        <v>2.972857196222677</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.522073250213343</v>
+        <v>-2.529944725559072</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.021166130723595</v>
+        <v>1.960522881685301</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.834585058534548</v>
+        <v>3.777090399634546</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777666</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.189257980973848</v>
+        <v>3.131763322073846</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.651275063507386</v>
+        <v>-2.659146538853114</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.128391531257147</v>
+        <v>2.067748282218853</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.915970096409292</v>
+        <v>3.85847543750929</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644406</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.226335803467495</v>
+        <v>3.168841144567493</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.806056070285641</v>
+        <v>-2.81392754563137</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.103556951039491</v>
+        <v>2.042913702001197</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933027314470253</v>
+        <v>3.87553265557025</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.22301115945704</v>
+        <v>3.165516500557038</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.799001380070468</v>
+        <v>-2.806872855416196</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.103054183115106</v>
+        <v>2.042410934076812</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933935484588902</v>
+        <v>3.8764408256889</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331109</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.233017313101782</v>
+        <v>3.175522654201779</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.77205015574398</v>
+        <v>-2.779921631089708</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.123840826490443</v>
+        <v>2.063197577452149</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952869845850275</v>
+        <v>3.895375186950273</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784101</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.417120445246741</v>
+        <v>3.359625786346739</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.908003163800296</v>
+        <v>-2.915874639146025</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.253562755412876</v>
+        <v>2.192919506374582</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136972977995235</v>
+        <v>4.079478319095233</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.409237140149735</v>
+        <v>3.351742481249732</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.930411281605168</v>
+        <v>-2.938282756950897</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.23671620319392</v>
+        <v>2.176072954155626</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129089672898228</v>
+        <v>4.071595013998226</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.411291139699372</v>
+        <v>3.35379648079937</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.958635517182768</v>
+        <v>-2.966506992528497</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.227480508512517</v>
+        <v>2.166837259474224</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141929723918651</v>
+        <v>4.084435065018648</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.467544857421219</v>
+        <v>3.410050198521217</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.968076443071298</v>
+        <v>-2.975947918417027</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.279957855878953</v>
+        <v>2.219314606840659</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271639712166532</v>
+        <v>4.21414505326653</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.47043595196652</v>
+        <v>3.412941293066518</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.02035005040694</v>
+        <v>-3.028221525752668</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.261939507489997</v>
+        <v>2.201296258451703</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.243166642310449</v>
+        <v>4.185671983410447</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347697</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.468547764860295</v>
+        <v>3.411053105960293</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.096680028007845</v>
+        <v>-3.104551503353574</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.22951932934341</v>
+        <v>2.168876080305116</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.241278455204224</v>
+        <v>4.183783796304222</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887742</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.463367994463157</v>
+        <v>3.405873335563155</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.298933748332199</v>
+        <v>-3.306805223677928</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.143438070816531</v>
+        <v>2.082794821778237</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.114746452612474</v>
+        <v>4.057251793712472</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.46180200467331</v>
+        <v>3.404307345773308</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.460502173859454</v>
+        <v>-3.468373649205183</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.077244710815781</v>
+        <v>2.016601461777487</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.037110708543898</v>
+        <v>3.979616049643896</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389348</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.474875411539228</v>
+        <v>3.417380752639226</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.592803465957007</v>
+        <v>-3.600674941302736</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.037397600842678</v>
+        <v>1.976754351804384</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.050184115409817</v>
+        <v>3.992689456509815</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.466880608322168</v>
+        <v>3.409385949422166</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.778671776796237</v>
+        <v>-3.786543252141966</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.955055473289926</v>
+        <v>1.894412224251632</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947049956200789</v>
+        <v>3.889555297300786</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.46540464944917</v>
+        <v>3.407909990549168</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.80657256390571</v>
+        <v>-3.814444039251439</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.942419199573139</v>
+        <v>1.881775950534845</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.92481584284203</v>
+        <v>3.867321183942027</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787382</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.462169093426369</v>
+        <v>3.404674434526367</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.929098666608604</v>
+        <v>-3.936970141954333</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.89017320246918</v>
+        <v>1.829529953430886</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848064625197492</v>
+        <v>3.79056996629749</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.528875053016873</v>
+        <v>3.471380394116871</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.159613162794193</v>
+        <v>-4.167484638139921</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.864673363585449</v>
+        <v>1.804030114547155</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.776461887076643</v>
+        <v>3.71896722817664</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.64075008781466</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.66918677201872</v>
+        <v>3.611692113118718</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.416333980789016</v>
+        <v>-4.424205456134745</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.902296755389366</v>
+        <v>1.841653506351072</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.851724861592201</v>
+        <v>3.794230202692199</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.73816704116436</v>
+        <v>3.680672382264357</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.570320398565157</v>
+        <v>-4.578191873910885</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.90968245742455</v>
+        <v>1.849039208386256</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.920705130737841</v>
+        <v>3.863210471837839</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423382</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.724218243284481</v>
+        <v>3.666723584384478</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.519798494737491</v>
+        <v>-4.527669970083219</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.915942421075737</v>
+        <v>1.855299172037443</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.906756332857962</v>
+        <v>3.849261673957959</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609748</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.736088732339895</v>
+        <v>3.678594073439892</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.772273648745215</v>
+        <v>-4.780145124090944</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.826822848528061</v>
+        <v>1.766179599489768</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.918626821913375</v>
+        <v>3.861132163013373</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973152</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.737299266858838</v>
+        <v>3.679804607958836</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.065169405224627</v>
+        <v>-5.073040880570356</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.71087508045524</v>
+        <v>1.650231831416946</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.919837356432319</v>
+        <v>3.862342697532317</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.66350945725194</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.74142100908616</v>
+        <v>3.683926350186157</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.251833533359435</v>
+        <v>-5.259705008705164</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.640331171428638</v>
+        <v>1.579687922390344</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2774911784645746</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.907915716164905</v>
+        <v>3.850421057264902</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916196</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.736498861822349</v>
+        <v>3.679004202922347</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.529797928942709</v>
+        <v>-5.537669404288438</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.524223265931518</v>
+        <v>1.463580016893224</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1878714441790904</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.849221728329804</v>
+        <v>3.791727069429801</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830323</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.898702918521393</v>
+        <v>3.841208259621391</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.6467656215816</v>
+        <v>-5.654637096927329</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.639640245575006</v>
+        <v>1.578996996536712</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1878714441790904</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.011425785028848</v>
+        <v>3.953931126128846</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.893549556485207</v>
+        <v>3.836054897585205</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.731483563802553</v>
+        <v>-5.739355039148282</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.600599706650439</v>
+        <v>1.539956457612145</v>
       </c>
       <c r="F2024" t="n">
         <v>0.102755415251044</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.955202805635834</v>
+        <v>3.897708146735832</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.903778974053699</v>
+        <v>3.846284315153696</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.813418382071436</v>
+        <v>-5.821289857417165</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.578055196911377</v>
+        <v>1.517411947873083</v>
       </c>
       <c r="F2025" t="n">
         <v>0.0928206696639638</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.959471375852077</v>
+        <v>3.901976716952075</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.912704612509601</v>
+        <v>3.855209953609599</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.915394504319844</v>
+        <v>-5.923265979665572</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.546190386467916</v>
+        <v>1.485547137429622</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.00915545258444378</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.907211340958935</v>
+        <v>3.849716682058933</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.904857499753776</v>
+        <v>3.847362840853774</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.805388220842622</v>
+        <v>-5.813259696188351</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.58234578710298</v>
+        <v>1.521702538064686</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01404911933283143</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.913286971353475</v>
+        <v>3.855792312453473</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.909107510475751</v>
+        <v>3.851612851575748</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.662328645101697</v>
+        <v>-5.670200120447426</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.643819628121324</v>
+        <v>1.583176379083031</v>
       </c>
       <c r="F2028" t="n">
         <v>0.02206254592281071</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.922345038029437</v>
+        <v>3.864850379129435</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.916368393358287</v>
+        <v>3.858873734458284</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.360881919629859</v>
+        <v>-5.368753394975588</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.771659201192596</v>
+        <v>1.711015952154302</v>
       </c>
       <c r="F2029" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.110473956195076</v>
+        <v>4.052979297295074</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.917339571110997</v>
+        <v>3.859844912210995</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.385472163865043</v>
+        <v>-5.393343639210772</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.762794281251232</v>
+        <v>1.702151032212939</v>
       </c>
       <c r="F2030" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.111445133947786</v>
+        <v>4.053950475047784</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.918182475490752</v>
+        <v>3.860687816590751</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.334433787858523</v>
+        <v>-5.342305263204252</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.784052536033596</v>
+        <v>1.723409286995302</v>
       </c>
       <c r="F2031" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.112288038327542</v>
+        <v>4.054793379427539</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.937220574364898</v>
+        <v>3.879725915464896</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.293294492991892</v>
+        <v>-5.301165968337621</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.819546352854394</v>
+        <v>1.7589031038161</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3646485662612788</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.156009714121665</v>
+        <v>4.098515055221664</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.753404570488832</v>
+        <v>3.695909911588831</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.18268835291229</v>
+        <v>-5.190559828258019</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.679972805010169</v>
+        <v>1.619329555971876</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4752547063408808</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.038557394293361</v>
+        <v>3.981062735393359</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.756906614562796</v>
+        <v>3.699411955662795</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.313269087443133</v>
+        <v>-5.321140562788861</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.631242555271796</v>
+        <v>1.570599306233503</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.963710997648819</v>
+        <v>3.906216338748818</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.741333433638879</v>
+        <v>3.683838774738877</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.148772753252171</v>
+        <v>-5.1566442285979</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.681467908024263</v>
+        <v>1.62082465898597</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.948137816724902</v>
+        <v>3.890643157824901</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.740521144075308</v>
+        <v>3.683026485175307</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.176142685936603</v>
+        <v>-5.184014161282332</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.66970764538692</v>
+        <v>1.609064396348627</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.947325527161332</v>
+        <v>3.88983086826133</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.750389923200381</v>
+        <v>3.692895264300379</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.186527880826493</v>
+        <v>-5.194399356172221</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.675422346556037</v>
+        <v>1.614779097517744</v>
       </c>
       <c r="F2037" t="n">
         <v>0.334288776920149</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.95096318935247</v>
+        <v>3.893468530452469</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.821226928976806</v>
+        <v>3.763732270076805</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.205116039548717</v>
+        <v>-5.212987514894446</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.738824088843572</v>
+        <v>1.678180839805279</v>
       </c>
       <c r="F2038" t="n">
         <v>0.3157006181979236</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.01064729989556</v>
+        <v>3.953152640995559</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.818095939795104</v>
+        <v>3.760601280895103</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.205414586244753</v>
+        <v>-5.213286061590482</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.735573680983456</v>
+        <v>1.674930431945163</v>
       </c>
       <c r="F2039" t="n">
         <v>0.3157006181979236</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.007516310713859</v>
+        <v>3.950021651813858</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.822626834734496</v>
+        <v>3.765132175834494</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.104591452554326</v>
+        <v>-5.112462927900054</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.780433829399018</v>
+        <v>1.719790580360725</v>
       </c>
       <c r="F2040" t="n">
         <v>0.3281648336822774</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.019525734943863</v>
+        <v>3.962031076043862</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822756088213039</v>
+        <v>3.765261429313038</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.913810091801919</v>
+        <v>-4.921681567147647</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.856875627178524</v>
+        <v>1.796232378140231</v>
       </c>
       <c r="F2041" t="n">
         <v>0.5189461944346848</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.13412380487385</v>
+        <v>4.076629145973849</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.802592933950636</v>
+        <v>3.745098275050634</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.895293237760098</v>
+        <v>-4.903164713105827</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.844119214532849</v>
+        <v>1.783475965494556</v>
       </c>
       <c r="F2042" t="n">
         <v>0.531876323859893</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.121718728266572</v>
+        <v>4.064224069366571</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.837559870562694</v>
+        <v>3.780065211662693</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.87010005325878</v>
+        <v>-4.877971528604509</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.889163424945435</v>
+        <v>1.828520175907142</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5570695083612114</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.171801575579421</v>
+        <v>4.11430691667942</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.831246438464132</v>
+        <v>3.77375177956413</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.858045926345818</v>
+        <v>-4.865917401691546</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.887671643612058</v>
+        <v>1.827028394573765</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5691236352741742</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.172720619628636</v>
+        <v>4.115225960728635</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.833127068648268</v>
+        <v>3.775632409748266</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.864669173036176</v>
+        <v>-4.872540648381904</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.88690297512005</v>
+        <v>1.826259726081757</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5625003885838158</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.170627301798557</v>
+        <v>4.113132642898556</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.84597809452615</v>
+        <v>3.788483435626149</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.761788583507583</v>
+        <v>-4.769660058853312</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.940906236809369</v>
+        <v>1.880262987771077</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.245206681393595</v>
+        <v>4.187712022493594</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.866180764699744</v>
+        <v>3.808686105799743</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.78523062268767</v>
+        <v>-4.793102098033398</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.951732091310929</v>
+        <v>1.891088842272636</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.26540935156719</v>
+        <v>4.207914692667188</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.866180764699744</v>
+        <v>3.808686105799743</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.803303130979281</v>
+        <v>-4.81117460632501</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.944503087994285</v>
+        <v>1.883859838955992</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.26540935156719</v>
+        <v>4.207914692667188</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.826432678293211</v>
+        <v>3.76893801939321</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.034476924855913</v>
+        <v>-5.042348400201642</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.812285484037099</v>
+        <v>1.751642234998806</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.225661265160657</v>
+        <v>4.168166606260655</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.833455297290151</v>
+        <v>3.77596063839015</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.003190904315458</v>
+        <v>-5.011062379661187</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.83182251125022</v>
+        <v>1.771179262211928</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6966669986528641</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.25145549648187</v>
+        <v>4.193960837581868</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.932626296863055</v>
+        <v>3.875131637963054</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.850165512202174</v>
+        <v>-4.858036987547902</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.992203667668438</v>
+        <v>1.931560418630146</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8496923907661482</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.442441731322744</v>
+        <v>4.384947072422743</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.120092521771348</v>
+        <v>4.062597862871346</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.878472826075444</v>
+        <v>-4.886344301421173</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.168346967027423</v>
+        <v>2.10770371798913</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8496923907661482</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.629907956231037</v>
+        <v>4.572413297331035</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.08949547312543</v>
+        <v>4.032000814225428</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.045066051188966</v>
+        <v>-5.052937526534695</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.071112628336096</v>
+        <v>2.010469379297803</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.499354972517006</v>
+        <v>4.441860313617005</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.093171875787148</v>
+        <v>4.035677216887146</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.872001671806666</v>
+        <v>-4.879873147152395</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.144014782750734</v>
+        <v>2.083371533712441</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.503031375178724</v>
+        <v>4.445536716278722</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.090789930910643</v>
+        <v>4.033295272010641</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.84275569135097</v>
+        <v>-4.850627166696698</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.153331230056508</v>
+        <v>2.092687981018215</v>
       </c>
       <c r="F2055" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.500649430302219</v>
+        <v>4.443154771402217</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,45 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.77689768646953</v>
+        <v>3.699424827539108</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.088083170068278</v>
+        <v>4.030588511168276</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.852470967689106</v>
+        <v>-4.860342443034835</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.146738358678888</v>
+        <v>2.086095109640596</v>
       </c>
       <c r="F2056" t="n">
         <v>0.673383889314489</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.492113503656972</v>
+        <v>4.434618844756971</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="2" t="n">
+        <v>45519</v>
+      </c>
+      <c r="B2057" t="n">
+        <v>3.842601109245432</v>
+      </c>
+      <c r="C2057" t="n">
+        <v>4.129382207483258</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>-4.860342443034835</v>
+      </c>
+      <c r="E2057" t="n">
+        <v>2.086095109640596</v>
+      </c>
+      <c r="F2057" t="n">
+        <v>0.673383889314489</v>
+      </c>
+      <c r="G2057" t="n">
+        <v>4.122446004469626</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240815.xlsx
+++ b/tame_output/ON/bt/strategyON_20240815.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>101.3%</t>
+          <t>105.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-647.6%</t>
+          <t>-636.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.6%</t>
+          <t>-157.6%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.0%</t>
+          <t>-320.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-29.4%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097814</v>
+        <v>3.341378723097813</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094109</v>
+        <v>3.374439043094108</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199278</v>
+        <v>3.405960511199277</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969586</v>
+        <v>3.424633354969585</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297741</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317609</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.685161381615278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.636292910321671</v>
+        <v>-4.629687567476797</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.109438407134259</v>
+        <v>1.112080544272209</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4646190436009336</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.618579223443805</v>
+        <v>-4.611973880598931</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.117202465802746</v>
+        <v>1.119844602940695</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4678003724978504</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.509774337964078</v>
+        <v>-4.503168995119204</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.15772249121463</v>
+        <v>1.160364628352579</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4678003724978504</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.289753539927068</v>
+        <v>-4.283148197082194</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.247309847440048</v>
+        <v>1.249951984577998</v>
       </c>
       <c r="F1929" t="n">
         <v>0.6090202175658307</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.15688585086379</v>
+        <v>-4.150280508018916</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.316351105867182</v>
+        <v>1.318993243005132</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.036712767499291</v>
+        <v>-4.030107424654418</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.365566183653284</v>
+        <v>1.368208320791233</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.901459406169314</v>
+        <v>-3.89485406332444</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.429755630746715</v>
+        <v>1.432397767884664</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.961334233527007</v>
+        <v>-3.954728890682133</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.391843191205064</v>
+        <v>1.394485328343013</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.841514002616169</v>
+        <v>-3.834908659771295</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.455060452803607</v>
+        <v>1.457702589941556</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.843983709077975</v>
+        <v>-3.837378366233101</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.361716769541326</v>
+        <v>1.364358906679276</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.912353895401985</v>
+        <v>-3.905748552557111</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253630556497024</v>
+        <v>1.256272693634973</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.926141948249032</v>
+        <v>-3.919536605404158</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.238552043990096</v>
+        <v>1.241194181128046</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.981662024141621</v>
+        <v>-3.975056681296747</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.353374850325263</v>
+        <v>1.356016987463212</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.806187764349152</v>
+        <v>-3.799582421504278</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.428131786234038</v>
+        <v>1.430773923371988</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.9171240169904</v>
+        <v>-3.910518674145527</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.359499313938746</v>
+        <v>1.362141451076695</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.883460471518119</v>
+        <v>-3.876855128673245</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.301503045529108</v>
+        <v>1.304145182667058</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8450413729493054</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.823607852314395</v>
+        <v>-3.817002509469522</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.33561647964273</v>
+        <v>1.33825861678068</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8450413729493054</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.737364389288018</v>
+        <v>-3.730759046443144</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.365060135427141</v>
+        <v>1.367702272565091</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8450413729493054</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.782671208686998</v>
+        <v>-3.776065865842124</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.338713183112075</v>
+        <v>1.341355320250024</v>
       </c>
       <c r="F1944" t="n">
         <v>0.8042312099400746</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.8117043133893</v>
+        <v>-3.805098970544426</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.327651814264256</v>
+        <v>1.330293951402205</v>
       </c>
       <c r="F1945" t="n">
         <v>0.8042312099400746</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.71889383193844</v>
+        <v>-3.712288489093567</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.294048698735965</v>
+        <v>1.296690835873915</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8970416913909339</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.763283301267868</v>
+        <v>-3.756677958422994</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.278166386928795</v>
+        <v>1.280808524066744</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8526522220615063</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.879824906373211</v>
+        <v>-3.873219563528337</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.226625453398381</v>
+        <v>1.22926759053633</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7361106169561635</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.919749000955782</v>
+        <v>-3.913143658110909</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.216147111396019</v>
+        <v>1.218789248533969</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7361106169561635</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.947529398857136</v>
+        <v>-3.940924056012262</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.216532154004017</v>
+        <v>1.219174291141967</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7083302190548104</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.065910071587274</v>
+        <v>-4.0593047287424</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.007535604912615</v>
+        <v>1.010177742050565</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6411123669038342</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.174524150030605</v>
+        <v>-4.167918807185731</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.084239634254488</v>
+        <v>1.086881771392438</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6411123669038342</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.139115111782462</v>
+        <v>-4.132509768937588</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.112916275656068</v>
+        <v>1.115558412794018</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.100731449224311</v>
+        <v>-4.094126106379437</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.125689182021698</v>
+        <v>1.128331319159647</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.923615119189145</v>
+        <v>-3.917009776344271</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.193264742881066</v>
+        <v>1.195906880019016</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.96870736402269</v>
+        <v>-3.962102021177817</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.175911236709561</v>
+        <v>1.17855337384751</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.789331942783923</v>
+        <v>-3.782726599939049</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.241448380511482</v>
+        <v>1.244090517649432</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.834346156304529</v>
+        <v>-3.827740813459655</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.20425015043483</v>
+        <v>1.206892287572779</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.101350666576964</v>
+        <v>-4.094745323732091</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.103139908664801</v>
+        <v>1.105782045802751</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.202548448014137</v>
+        <v>-4.195943105169263</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.061864717986433</v>
+        <v>1.064506855124383</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.196037481399824</v>
+        <v>-4.189432138554951</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.062069066186475</v>
+        <v>1.064711203324425</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.176999353692527</v>
+        <v>-4.170394010847653</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.066209036477639</v>
+        <v>1.068851173615589</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.229515155967348</v>
+        <v>-4.222909813122474</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.164497117201901</v>
+        <v>1.167139254339851</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.243381917301265</v>
+        <v>-4.236776574456392</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.159783741654468</v>
+        <v>1.162425878792417</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.198577745761336</v>
+        <v>-4.191972402916462</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.183713940667366</v>
+        <v>1.186356077805315</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.050834775526333</v>
+        <v>-4.044229432681459</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.140761350038566</v>
+        <v>1.143403487176516</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46789,19 +46789,19 @@
         <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.706750647194325</v>
+        <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.134655996801031</v>
+        <v>-4.027019095307873</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.052531824160165</v>
+        <v>1.153081243657431</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.03856374323251</v>
+        <v>3.096058402132512</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.707412995585984</v>
+        <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.128503290748247</v>
+        <v>-4.020866389255088</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.055655254972937</v>
+        <v>1.156204674470203</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.042917715255839</v>
+        <v>3.100412374155841</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.706493472326094</v>
+        <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.145312588898749</v>
+        <v>-4.03767568740559</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.048012012452847</v>
+        <v>1.148561431950113</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.031912613105648</v>
+        <v>3.08940727200565</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.86736263679842</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.772829026122915</v>
+        <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.083014590122627</v>
+        <v>-3.975377688629468</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.139266765760117</v>
+        <v>1.239816185257382</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.125424725467134</v>
+        <v>3.182919384367136</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.575121027837042</v>
+        <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.881224392457469</v>
+        <v>-3.773587490964311</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.022274846540307</v>
+        <v>1.122824266037572</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.046527642482754</v>
+        <v>3.104022301382756</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.645411260159217</v>
+        <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.932111105143663</v>
+        <v>-3.824474203650505</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.072210393788004</v>
+        <v>1.17275981328527</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.086285847193213</v>
+        <v>3.143780506093215</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319538</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.660038996275261</v>
+        <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.845500362493856</v>
+        <v>-3.737863461000698</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.121482426963971</v>
+        <v>1.222031846461237</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.148089022032351</v>
+        <v>3.205583680932353</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489378</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.658574977099932</v>
+        <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.905709660499141</v>
+        <v>-3.798072759005982</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.095934688586529</v>
+        <v>1.196484108083794</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.110499424053852</v>
+        <v>3.167994082953854</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397787</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.657066595139861</v>
+        <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.829287614067214</v>
+        <v>-3.721650712574056</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.124995125199228</v>
+        <v>1.225544544696494</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.108991042093781</v>
+        <v>3.166485700993783</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316242</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.656929462575297</v>
+        <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.784914482428645</v>
+        <v>-3.677277580935487</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.142607245290092</v>
+        <v>1.243156664787357</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.135477788512358</v>
+        <v>3.19297244741236</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.651323256713888</v>
+        <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.80739483328753</v>
+        <v>-3.699757931794372</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.128008899085128</v>
+        <v>1.228558318582394</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.129871582650948</v>
+        <v>3.187366241550951</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.657705013741692</v>
+        <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.759739102726474</v>
+        <v>-3.652102201233316</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.153452948337355</v>
+        <v>1.254002367834621</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.164846778015387</v>
+        <v>3.222341436915389</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.662597387116417</v>
+        <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.659220944227719</v>
+        <v>-3.551584042734562</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.198552585111582</v>
+        <v>1.299102004608847</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.230050046489364</v>
+        <v>3.287544705389366</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.649352059592289</v>
+        <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.643315614795367</v>
+        <v>-3.535678713302209</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.191669389360395</v>
+        <v>1.29221880885766</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.169337122539693</v>
+        <v>3.226831781439695</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932763</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.653449762202918</v>
+        <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.598477213186969</v>
+        <v>-3.490840311693811</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.213702452614383</v>
+        <v>1.314251872111648</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.176160884917243</v>
+        <v>3.233655543817246</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.657610701833996</v>
+        <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.617975669428977</v>
+        <v>-3.510338767935819</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.210064009748658</v>
+        <v>1.310613429245923</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.151471039780379</v>
+        <v>3.208965698680381</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.663490304361833</v>
+        <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.573772832343077</v>
+        <v>-3.466135930849919</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.233624747110855</v>
+        <v>1.33417416660812</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.183872344559756</v>
+        <v>3.241367003459758</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265638</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.661900304831081</v>
+        <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.581332498180124</v>
+        <v>-3.473695596686966</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.229010881245284</v>
+        <v>1.329560300742549</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.215164387434895</v>
+        <v>3.272659046334898</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.71314807001412</v>
+        <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.423041080640851</v>
+        <v>-3.315404179147694</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.343575213444032</v>
+        <v>1.444124632941298</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.266412152617935</v>
+        <v>3.323906811517937</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.711588774608373</v>
+        <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.215399077006375</v>
+        <v>-3.107762175513217</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.425072719492076</v>
+        <v>1.525622138989341</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.389438059392874</v>
+        <v>3.446932718292876</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.706537002846643</v>
+        <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.164366984283847</v>
+        <v>-3.056730082790689</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.440433784819357</v>
+        <v>1.540983204316623</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.415005543264661</v>
+        <v>3.472500202164663</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404846</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.723724406939348</v>
+        <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.099142803156641</v>
+        <v>-2.991505901663484</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.483710861362944</v>
+        <v>1.58426028086021</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.471327456033689</v>
+        <v>3.528822114933691</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.84006118688255</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.719685379238629</v>
+        <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.061715783085508</v>
+        <v>-2.95407888159235</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.494642641690678</v>
+        <v>1.595192061187944</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.470439351150478</v>
+        <v>3.527934010050481</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992653</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.720942171569869</v>
+        <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.081827439120216</v>
+        <v>-2.974190537627058</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.487854771608035</v>
+        <v>1.588404191105301</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.47831255048017</v>
+        <v>3.535807209380172</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636279</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.88149994259108</v>
+        <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.028082624693011</v>
+        <v>-2.920445723199853</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.669910468400128</v>
+        <v>1.770459887897393</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.644908307165658</v>
+        <v>3.702402966065661</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957617</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.001612851808897</v>
+        <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.953300363667998</v>
+        <v>-2.845663462174841</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.81993628202795</v>
+        <v>1.920485701525216</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.809890572998483</v>
+        <v>3.867385231898485</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.993320827822756</v>
+        <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.92721627940419</v>
+        <v>-2.819579377911033</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.822077891747332</v>
+        <v>1.922627311244598</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.801598549012342</v>
+        <v>3.859093207912344</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.991514023406535</v>
+        <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.83933836629507</v>
+        <v>-2.731701464801912</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.85542225257476</v>
+        <v>1.955971672072025</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.869347130050132</v>
+        <v>3.926841788950134</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959852</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.009068429133327</v>
+        <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.830445904901786</v>
+        <v>-2.722809003408629</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.876533642858865</v>
+        <v>1.97708306235613</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.886901535776923</v>
+        <v>3.944396194676925</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.000923476537911</v>
+        <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.998922021871664</v>
+        <v>-2.891285120378507</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.800998243475498</v>
+        <v>1.901547662972763</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.861987881751559</v>
+        <v>3.919482540651561</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.982193173725773</v>
+        <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.552665829242224</v>
+        <v>-2.445028927749067</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.960770417715135</v>
+        <v>2.061319837212401</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.786426377137641</v>
+        <v>3.843921036037643</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.972857196222677</v>
+        <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.529944725559072</v>
+        <v>-2.422307824065914</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.960522881685301</v>
+        <v>2.061072301182566</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.777090399634546</v>
+        <v>3.834585058534548</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777666</v>
+        <v>3.783205696777667</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.131763322073846</v>
+        <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.659146538853114</v>
+        <v>-2.551509637359957</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.067748282218853</v>
+        <v>2.168297701716118</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.85847543750929</v>
+        <v>3.915970096409292</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644406</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.168841144567493</v>
+        <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.81392754563137</v>
+        <v>-2.706290644138212</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.042913702001197</v>
+        <v>2.143463121498463</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.87553265557025</v>
+        <v>3.933027314470253</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.165516500557038</v>
+        <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.806872855416196</v>
+        <v>-2.699235953923039</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.042410934076812</v>
+        <v>2.142960353574077</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.8764408256889</v>
+        <v>3.933935484588902</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331109</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.175522654201779</v>
+        <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.779921631089708</v>
+        <v>-2.672284729596551</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.063197577452149</v>
+        <v>2.163746996949414</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.895375186950273</v>
+        <v>3.952869845850275</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784101</v>
+        <v>3.768052067784102</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.359625786346739</v>
+        <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.915874639146025</v>
+        <v>-2.808237737652867</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.192919506374582</v>
+        <v>2.293468925871847</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.079478319095233</v>
+        <v>4.136972977995235</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.351742481249732</v>
+        <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.938282756950897</v>
+        <v>-2.830645855457739</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.176072954155626</v>
+        <v>2.276622373652891</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.071595013998226</v>
+        <v>4.129089672898228</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.35379648079937</v>
+        <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.966506992528497</v>
+        <v>-2.858870091035339</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.166837259474224</v>
+        <v>2.267386678971489</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.084435065018648</v>
+        <v>4.141929723918651</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.410050198521217</v>
+        <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.975947918417027</v>
+        <v>-2.868311016923869</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.219314606840659</v>
+        <v>2.319864026337924</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.21414505326653</v>
+        <v>4.271639712166532</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.412941293066518</v>
+        <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.028221525752668</v>
+        <v>-2.920584624259511</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.201296258451703</v>
+        <v>2.301845677948968</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.185671983410447</v>
+        <v>4.243166642310449</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347697</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.411053105960293</v>
+        <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.104551503353574</v>
+        <v>-2.996914601860416</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.168876080305116</v>
+        <v>2.269425499802381</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.183783796304222</v>
+        <v>4.241278455204224</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887742</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.405873335563155</v>
+        <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.306805223677928</v>
+        <v>-3.19916832218477</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.082794821778237</v>
+        <v>2.183344241275502</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.057251793712472</v>
+        <v>4.114746452612474</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.404307345773308</v>
+        <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.468373649205183</v>
+        <v>-3.360736747712025</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.016601461777487</v>
+        <v>2.117150881274752</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.979616049643896</v>
+        <v>4.037110708543898</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.417380752639226</v>
+        <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.600674941302736</v>
+        <v>-3.493038039809578</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.976754351804384</v>
+        <v>2.07730377130165</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.992689456509815</v>
+        <v>4.050184115409817</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.409385949422166</v>
+        <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.786543252141966</v>
+        <v>-3.678906350648808</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.894412224251632</v>
+        <v>1.994961643748898</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.889555297300786</v>
+        <v>3.947049956200789</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.407909990549168</v>
+        <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.814444039251439</v>
+        <v>-3.706807137758281</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.881775950534845</v>
+        <v>1.982325370032111</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.867321183942027</v>
+        <v>3.92481584284203</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787382</v>
+        <v>3.684895778787383</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.404674434526367</v>
+        <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.936970141954333</v>
+        <v>-3.829333240461175</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.829529953430886</v>
+        <v>1.930079372928152</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.79056996629749</v>
+        <v>3.848064625197492</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.471380394116871</v>
+        <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.167484638139921</v>
+        <v>-4.059847736646764</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.804030114547155</v>
+        <v>1.90457953404442</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.71896722817664</v>
+        <v>3.776461887076643</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781466</v>
+        <v>3.640750087814661</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.611692113118718</v>
+        <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.424205456134745</v>
+        <v>-4.316568554641588</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.841653506351072</v>
+        <v>1.942202925848338</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.794230202692199</v>
+        <v>3.851724861592201</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237089</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.680672382264357</v>
+        <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.578191873910885</v>
+        <v>-4.470554972417728</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.849039208386256</v>
+        <v>1.949588627883521</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.863210471837839</v>
+        <v>3.920705130737841</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423382</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.666723584384478</v>
+        <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.527669970083219</v>
+        <v>-4.420033068590063</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.855299172037443</v>
+        <v>1.955848591534708</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.849261673957959</v>
+        <v>3.906756332857962</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609748</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.678594073439892</v>
+        <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.780145124090944</v>
+        <v>-4.672508222597787</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.766179599489768</v>
+        <v>1.866729018987032</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.861132163013373</v>
+        <v>3.918626821913375</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973152</v>
+        <v>3.674028535973153</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.679804607958836</v>
+        <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.073040880570356</v>
+        <v>-4.965403979077199</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.650231831416946</v>
+        <v>1.750781250914211</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.862342697532317</v>
+        <v>3.919837356432319</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725194</v>
+        <v>3.663509457251941</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.683926350186157</v>
+        <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.259705008705164</v>
+        <v>-5.152068107212007</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.579687922390344</v>
+        <v>1.68023734188761</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2774911784645746</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.850421057264902</v>
+        <v>3.907915716164905</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916196</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.679004202922347</v>
+        <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.537669404288438</v>
+        <v>-5.430032502795281</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.463580016893224</v>
+        <v>1.564129436390489</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1878714441790904</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.791727069429801</v>
+        <v>3.849221728329804</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830323</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.841208259621391</v>
+        <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.654637096927329</v>
+        <v>-5.547000195434172</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.578996996536712</v>
+        <v>1.679546416033977</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1878714441790904</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.953931126128846</v>
+        <v>4.011425785028848</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.836054897585205</v>
+        <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.739355039148282</v>
+        <v>-5.631718137655125</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.539956457612145</v>
+        <v>1.64050587710941</v>
       </c>
       <c r="F2024" t="n">
         <v>0.102755415251044</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.897708146735832</v>
+        <v>3.955202805635834</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.846284315153696</v>
+        <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.821289857417165</v>
+        <v>-5.713652955924008</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.517411947873083</v>
+        <v>1.617961367370348</v>
       </c>
       <c r="F2025" t="n">
         <v>0.0928206696639638</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.901976716952075</v>
+        <v>3.959471375852077</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.855209953609599</v>
+        <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.923265979665572</v>
+        <v>-5.815629078172416</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.485547137429622</v>
+        <v>1.586096556926888</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.00915545258444378</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.849716682058933</v>
+        <v>3.907211340958935</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231804</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.847362840853774</v>
+        <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.813259696188351</v>
+        <v>-5.705622794695194</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.521702538064686</v>
+        <v>1.622251957561951</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01404911933283143</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.855792312453473</v>
+        <v>3.913286971353475</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.851612851575748</v>
+        <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.670200120447426</v>
+        <v>-5.562563218954269</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.583176379083031</v>
+        <v>1.683725798580296</v>
       </c>
       <c r="F2028" t="n">
         <v>0.02206254592281071</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.864850379129435</v>
+        <v>3.922345038029437</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.858873734458284</v>
+        <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.368753394975588</v>
+        <v>-5.261116493482431</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.711015952154302</v>
+        <v>1.811565371651567</v>
       </c>
       <c r="F2029" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.052979297295074</v>
+        <v>4.110473956195076</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.859844912210995</v>
+        <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.393343639210772</v>
+        <v>-5.285706737717615</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.702151032212939</v>
+        <v>1.802700451710204</v>
       </c>
       <c r="F2030" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.053950475047784</v>
+        <v>4.111445133947786</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.860687816590751</v>
+        <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.342305263204252</v>
+        <v>-5.234668361711095</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.723409286995302</v>
+        <v>1.823958706492567</v>
       </c>
       <c r="F2031" t="n">
         <v>0.323509271394648</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.054793379427539</v>
+        <v>4.112288038327542</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.879725915464896</v>
+        <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.301165968337621</v>
+        <v>-5.193529066844464</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.7589031038161</v>
+        <v>1.859452523313365</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3646485662612788</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.098515055221664</v>
+        <v>4.156009714121665</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.695909911588831</v>
+        <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.190559828258019</v>
+        <v>-5.082922926764862</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.619329555971876</v>
+        <v>1.71987897546914</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4752547063408808</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.981062735393359</v>
+        <v>4.038557394293361</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.699411955662795</v>
+        <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.321140562788861</v>
+        <v>-5.213503661295705</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.570599306233503</v>
+        <v>1.671148725730767</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.906216338748818</v>
+        <v>3.963710997648819</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.683838774738877</v>
+        <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.1566442285979</v>
+        <v>-5.049007327104743</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.62082465898597</v>
+        <v>1.721374078483234</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.890643157824901</v>
+        <v>3.948137816724902</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.683026485175307</v>
+        <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.184014161282332</v>
+        <v>-5.076377259789175</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.609064396348627</v>
+        <v>1.709613815845891</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3446739718100383</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.88983086826133</v>
+        <v>3.947325527161332</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.692895264300379</v>
+        <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.194399356172221</v>
+        <v>-5.086762454679064</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.614779097517744</v>
+        <v>1.715328517015008</v>
       </c>
       <c r="F2037" t="n">
         <v>0.334288776920149</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.893468530452469</v>
+        <v>3.95096318935247</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.763732270076805</v>
+        <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.212987514894446</v>
+        <v>-5.105350613401289</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.678180839805279</v>
+        <v>1.778730259302543</v>
       </c>
       <c r="F2038" t="n">
         <v>0.3157006181979236</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.953152640995559</v>
+        <v>4.01064729989556</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.760601280895103</v>
+        <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.213286061590482</v>
+        <v>-5.105649160097325</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.674930431945163</v>
+        <v>1.775479851442427</v>
       </c>
       <c r="F2039" t="n">
         <v>0.3157006181979236</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.950021651813858</v>
+        <v>4.007516310713859</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.765132175834494</v>
+        <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.112462927900054</v>
+        <v>-5.004826026406898</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.719790580360725</v>
+        <v>1.820339999857989</v>
       </c>
       <c r="F2040" t="n">
         <v>0.3281648336822774</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.962031076043862</v>
+        <v>4.019525734943863</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.765261429313038</v>
+        <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.921681567147647</v>
+        <v>-4.814044665654491</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.796232378140231</v>
+        <v>1.896781797637496</v>
       </c>
       <c r="F2041" t="n">
         <v>0.5189461944346848</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.076629145973849</v>
+        <v>4.13412380487385</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.745098275050634</v>
+        <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.903164713105827</v>
+        <v>-4.79552781161267</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.783475965494556</v>
+        <v>1.88402538499182</v>
       </c>
       <c r="F2042" t="n">
         <v>0.531876323859893</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.064224069366571</v>
+        <v>4.121718728266572</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.780065211662693</v>
+        <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.877971528604509</v>
+        <v>-4.770334627111352</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.828520175907142</v>
+        <v>1.929069595404406</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5570695083612114</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.11430691667942</v>
+        <v>4.171801575579421</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.77375177956413</v>
+        <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.865917401691546</v>
+        <v>-4.758280500198389</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.827028394573765</v>
+        <v>1.927577814071029</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5691236352741742</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.115225960728635</v>
+        <v>4.172720619628636</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.775632409748266</v>
+        <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.872540648381904</v>
+        <v>-4.764903746888748</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.826259726081757</v>
+        <v>1.926809145579021</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5625003885838158</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.113132642898556</v>
+        <v>4.170627301798557</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.788483435626149</v>
+        <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.769660058853312</v>
+        <v>-4.662023157360155</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.880262987771077</v>
+        <v>1.980812407268341</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.187712022493594</v>
+        <v>4.245206681393595</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.808686105799743</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.793102098033398</v>
+        <v>-4.685465196540242</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.891088842272636</v>
+        <v>1.9916382617699</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.207914692667188</v>
+        <v>4.26540935156719</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.808686105799743</v>
+        <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.81117460632501</v>
+        <v>-4.703537704831853</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.883859838955992</v>
+        <v>1.984409258453256</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.207914692667188</v>
+        <v>4.26540935156719</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.76893801939321</v>
+        <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.042348400201642</v>
+        <v>-4.934711498708485</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.751642234998806</v>
+        <v>1.85219165449607</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6653809781124087</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.168166606260655</v>
+        <v>4.225661265160657</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.77596063839015</v>
+        <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.011062379661187</v>
+        <v>-4.90342547816803</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.771179262211928</v>
+        <v>1.871728681709192</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6966669986528641</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.193960837581868</v>
+        <v>4.25145549648187</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.875131637963054</v>
+        <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.858036987547902</v>
+        <v>-4.750400086054746</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.931560418630146</v>
+        <v>2.032109838127409</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8496923907661482</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.384947072422743</v>
+        <v>4.442441731322744</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.062597862871346</v>
+        <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.886344301421173</v>
+        <v>-4.778707399928016</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.10770371798913</v>
+        <v>2.208253137486394</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8496923907661482</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.572413297331035</v>
+        <v>4.629907956231037</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.032000814225428</v>
+        <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.052937526534695</v>
+        <v>-4.945300625041538</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.010469379297803</v>
+        <v>2.111018798795067</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.441860313617005</v>
+        <v>4.499354972517006</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.035677216887146</v>
+        <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.879873147152395</v>
+        <v>-4.772236245659238</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.083371533712441</v>
+        <v>2.183920953209705</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.445536716278722</v>
+        <v>4.503031375178724</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.033295272010641</v>
+        <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.850627166696698</v>
+        <v>-4.742990265203542</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.092687981018215</v>
+        <v>2.193237400515479</v>
       </c>
       <c r="F2055" t="n">
         <v>0.6830991656526257</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.443154771402217</v>
+        <v>4.500649430302219</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699424827539108</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.030588511168276</v>
+        <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.860342443034835</v>
+        <v>-4.752705541541678</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.086095109640596</v>
+        <v>2.186644529137859</v>
       </c>
       <c r="F2056" t="n">
         <v>0.673383889314489</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.434618844756971</v>
+        <v>4.492113503656972</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.842601109245432</v>
+        <v>3.780224766077501</v>
       </c>
       <c r="C2057" t="n">
-        <v>4.129382207483258</v>
+        <v>4.17304740647968</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.860342443034835</v>
+        <v>-4.752705541541678</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.086095109640596</v>
+        <v>2.186644529137859</v>
       </c>
       <c r="F2057" t="n">
         <v>0.673383889314489</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.122446004469626</v>
+        <v>4.166111203466047</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240815.xlsx
+++ b/tame_output/ON/bt/strategyON_20240815.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.8%</t>
+          <t>-646.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.6%</t>
+          <t>-161.5%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191731</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311943</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242287</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367677</v>
+        <v>3.821593509367678</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.629687567476797</v>
+        <v>-4.628421434975942</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.112080544272209</v>
+        <v>1.112586997272551</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4646190436009336</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879958</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.611973880598931</v>
+        <v>-4.610707748098076</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.119844602940695</v>
+        <v>1.120351055941037</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4678003724978504</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650233</v>
+        <v>3.848616626502331</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.503168995119204</v>
+        <v>-4.501902862618349</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.160364628352579</v>
+        <v>1.160871081352921</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4678003724978504</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675931</v>
+        <v>3.818668951675932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.283148197082194</v>
+        <v>-4.281882064581339</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.249951984577998</v>
+        <v>1.25045843757834</v>
       </c>
       <c r="F1929" t="n">
         <v>0.6090202175658307</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539942</v>
+        <v>3.843274527539943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.150280508018916</v>
+        <v>-4.149014375518061</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.318993243005132</v>
+        <v>1.319499696005474</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496256</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.030107424654418</v>
+        <v>-4.028841292153563</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.368208320791233</v>
+        <v>1.368714773791575</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576993</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.89485406332444</v>
+        <v>-3.893587930823585</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.432397767884664</v>
+        <v>1.432904220885006</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942099</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.954728890682133</v>
+        <v>-3.953462758181278</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.394485328343013</v>
+        <v>1.394991781343355</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674509</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.834908659771295</v>
+        <v>-3.83364252727044</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.457702589941556</v>
+        <v>1.458209042941898</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430688</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.837378366233101</v>
+        <v>-3.836112233732246</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.364358906679276</v>
+        <v>1.364865359679618</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003595</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.905748552557111</v>
+        <v>-3.904482420056256</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.256272693634973</v>
+        <v>1.256779146635315</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508364</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.919536605404158</v>
+        <v>-3.918270472903303</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.241194181128046</v>
+        <v>1.241700634128388</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417698</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.975056681296747</v>
+        <v>-3.973790548795892</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.356016987463212</v>
+        <v>1.356523440463554</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205891</v>
+        <v>3.746042526205893</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.799582421504278</v>
+        <v>-3.798316289003423</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.430773923371988</v>
+        <v>1.43128037637233</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225436</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.910518674145527</v>
+        <v>-3.909252541644672</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.362141451076695</v>
+        <v>1.362647904077037</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.876855128673245</v>
+        <v>-3.87558899617239</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.304145182667058</v>
+        <v>1.3046516356674</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8450413729493054</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.817002509469522</v>
+        <v>-3.815736376968667</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.33825861678068</v>
+        <v>1.338765069781021</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8450413729493054</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.730759046443144</v>
+        <v>-3.729492913942289</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.367702272565091</v>
+        <v>1.368208725565433</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8450413729493054</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.776065865842124</v>
+        <v>-3.774799733341269</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.341355320250024</v>
+        <v>1.341861773250366</v>
       </c>
       <c r="F1944" t="n">
         <v>0.8042312099400746</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803188</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.805098970544426</v>
+        <v>-3.803832838043571</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.330293951402205</v>
+        <v>1.330800404402547</v>
       </c>
       <c r="F1945" t="n">
         <v>0.8042312099400746</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.712288489093567</v>
+        <v>-3.711022356592712</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.296690835873915</v>
+        <v>1.297197288874257</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8970416913909339</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.756677958422994</v>
+        <v>-3.755411825922139</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.280808524066744</v>
+        <v>1.281314977067086</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8526522220615063</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.873219563528337</v>
+        <v>-3.871953431027482</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.22926759053633</v>
+        <v>1.229774043536672</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7361106169561635</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.913143658110909</v>
+        <v>-3.911877525610054</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.218789248533969</v>
+        <v>1.219295701534311</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7361106169561635</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.940924056012262</v>
+        <v>-3.939657923511407</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.219174291141967</v>
+        <v>1.219680744142309</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7083302190548104</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.0593047287424</v>
+        <v>-4.058038596241545</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.010177742050565</v>
+        <v>1.010684195050907</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6411123669038342</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.167918807185731</v>
+        <v>-4.166652674684876</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.086881771392438</v>
+        <v>1.08738822439278</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6411123669038342</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.132509768937588</v>
+        <v>-4.131243636436733</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.115558412794018</v>
+        <v>1.11606486579436</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.094126106379437</v>
+        <v>-4.092859973878582</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.128331319159647</v>
+        <v>1.128837772159989</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.917009776344271</v>
+        <v>-3.915743643843416</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.195906880019016</v>
+        <v>1.196413333019358</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.962102021177817</v>
+        <v>-3.960835888676962</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.17855337384751</v>
+        <v>1.179059826847852</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.782726599939049</v>
+        <v>-3.781460467438194</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.244090517649432</v>
+        <v>1.244596970649774</v>
       </c>
       <c r="F1957" t="n">
         <v>0.7743767444633143</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982223</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.827740813459655</v>
+        <v>-3.8264746809588</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.206892287572779</v>
+        <v>1.207398740573121</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7440278491487097</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.094745323732091</v>
+        <v>-4.093479191231236</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.105782045802751</v>
+        <v>1.106288498803093</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5496648111057612</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.195943105169263</v>
+        <v>-4.194676972668408</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.064506855124383</v>
+        <v>1.065013308124725</v>
       </c>
       <c r="F1960" t="n">
         <v>0.481255997560442</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.189432138554951</v>
+        <v>-4.188166006054096</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.064711203324425</v>
+        <v>1.065217656324767</v>
       </c>
       <c r="F1961" t="n">
         <v>0.481255997560442</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.170394010847653</v>
+        <v>-4.169127878346798</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.068851173615589</v>
+        <v>1.069357626615931</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4230723862292474</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.222909813122474</v>
+        <v>-4.221643680621619</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.167139254339851</v>
+        <v>1.167645707340193</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4230723862292474</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.236776574456392</v>
+        <v>-4.235510441955537</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.162425878792417</v>
+        <v>1.162932331792759</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3852144694954245</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.191972402916462</v>
+        <v>-4.190706270415607</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.186356077805315</v>
+        <v>1.186862530805657</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3852144694954245</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.044229432681459</v>
+        <v>-4.042963300180604</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.143403487176516</v>
+        <v>1.143909940176858</v>
       </c>
       <c r="F1966" t="n">
         <v>0.5530218267303076</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.027019095307873</v>
+        <v>-4.126784521455303</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.153081243657431</v>
+        <v>1.113175073198459</v>
       </c>
       <c r="F1967" t="n">
         <v>0.5530218267303076</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.020866389255088</v>
+        <v>-4.120631815402518</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.156204674470203</v>
+        <v>1.116298504011231</v>
       </c>
       <c r="F1968" t="n">
         <v>0.5591745327830919</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.03767568740559</v>
+        <v>-4.13744111355302</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.148561431950113</v>
+        <v>1.108655261491141</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5423652346325902</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679842</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.975377688629468</v>
+        <v>-4.075143114776898</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.239816185257382</v>
+        <v>1.199910014798411</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5876594989070323</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.773587490964311</v>
+        <v>-3.87335291711174</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.122824266037572</v>
+        <v>1.082918095578601</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7856776910761867</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.824474203650505</v>
+        <v>-3.924239629797935</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.17275981328527</v>
+        <v>1.132853642826298</v>
       </c>
       <c r="F1972" t="n">
         <v>0.7347909783899922</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319538</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.737863461000698</v>
+        <v>-3.837628887148127</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.222031846461237</v>
+        <v>1.182125676002265</v>
       </c>
       <c r="F1973" t="n">
         <v>0.8134167095951504</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489378</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.798072759005982</v>
+        <v>-3.897838185153412</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.196484108083794</v>
+        <v>1.156577937624823</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7532074115898659</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397787</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.721650712574056</v>
+        <v>-3.821416138721485</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.225544544696494</v>
+        <v>1.185638374237522</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7532074115898659</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316242</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.677277580935487</v>
+        <v>-3.777043007082916</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.243156664787357</v>
+        <v>1.203250494328385</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7975805432284345</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.699757931794372</v>
+        <v>-3.799523357941801</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.228558318582394</v>
+        <v>1.188652148123422</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7975805432284345</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.652102201233316</v>
+        <v>-3.751867627380745</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.254002367834621</v>
+        <v>1.214096197375649</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8452362737894902</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.551584042734562</v>
+        <v>-3.651349468881991</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.299102004608847</v>
+        <v>1.259195834149876</v>
       </c>
       <c r="F1979" t="n">
         <v>0.9457544322882447</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557288</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.535678713302209</v>
+        <v>-3.635444139449638</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.29221880885766</v>
+        <v>1.252312638398689</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8666417715790058</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932763</v>
+        <v>3.816837033932765</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.490840311693811</v>
+        <v>-3.59060573784124</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.314251872111648</v>
+        <v>1.274345701652677</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8711852045238753</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.510338767935819</v>
+        <v>-3.610104194083248</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.310613429245923</v>
+        <v>1.270707258786951</v>
       </c>
       <c r="F1982" t="n">
         <v>0.823100563243971</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.466135930849919</v>
+        <v>-3.565901356997348</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.33417416660812</v>
+        <v>1.294267996149149</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8673034003298714</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265638</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.473695596686966</v>
+        <v>-3.573461022834395</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.329560300742549</v>
+        <v>1.289654130283578</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9221068043396907</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.315404179147694</v>
+        <v>-3.415169605295123</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.444124632941298</v>
+        <v>1.404218462482326</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9221068043396907</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.107762175513217</v>
+        <v>-3.207527601660646</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.525622138989341</v>
+        <v>1.48571596853037</v>
       </c>
       <c r="F1986" t="n">
         <v>1.129748807974167</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.056730082790689</v>
+        <v>-3.156495508938118</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.540983204316623</v>
+        <v>1.501077033857651</v>
       </c>
       <c r="F1987" t="n">
         <v>1.180780900696695</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404846</v>
+        <v>3.842547360404848</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.991505901663484</v>
+        <v>-3.091271327810913</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.58426028086021</v>
+        <v>1.544354110401238</v>
       </c>
       <c r="F1988" t="n">
         <v>1.246005081823901</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688255</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.95407888159235</v>
+        <v>-3.053844307739779</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.595192061187944</v>
+        <v>1.555285890728972</v>
       </c>
       <c r="F1989" t="n">
         <v>1.251256619853082</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992653</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.974190537627058</v>
+        <v>-3.073955963774487</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.588404191105301</v>
+        <v>1.548498020646329</v>
       </c>
       <c r="F1990" t="n">
         <v>1.262283964850502</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636279</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.920445723199853</v>
+        <v>-3.020211149347282</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.770459887897393</v>
+        <v>1.730553717438422</v>
       </c>
       <c r="F1991" t="n">
         <v>1.272347274290964</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957617</v>
+        <v>3.813222820957619</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.845663462174841</v>
+        <v>-2.94542888832227</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.920485701525216</v>
+        <v>1.880579531066244</v>
       </c>
       <c r="F1992" t="n">
         <v>1.347129535315976</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.819579377911033</v>
+        <v>-2.919344804058462</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.922627311244598</v>
+        <v>1.882721140785626</v>
       </c>
       <c r="F1993" t="n">
         <v>1.347129535315976</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.731701464801912</v>
+        <v>-2.831466890949341</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.955971672072025</v>
+        <v>1.916065501613054</v>
       </c>
       <c r="F1994" t="n">
         <v>1.463055177739327</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959852</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.722809003408629</v>
+        <v>-2.822574429556058</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.97708306235613</v>
+        <v>1.937176891897159</v>
       </c>
       <c r="F1995" t="n">
         <v>1.463055177739327</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945359</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.891285120378507</v>
+        <v>-2.991050546525936</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.901547662972763</v>
+        <v>1.861641492513791</v>
       </c>
       <c r="F1996" t="n">
         <v>1.435107342022747</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.445028927749067</v>
+        <v>-2.544794353896496</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.061319837212401</v>
+        <v>2.021413666753429</v>
       </c>
       <c r="F1997" t="n">
         <v>1.340388672353114</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563263</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.422307824065914</v>
+        <v>-2.522073250213343</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.061072301182566</v>
+        <v>2.021166130723595</v>
       </c>
       <c r="F1998" t="n">
         <v>1.340388672353114</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777667</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.551509637359957</v>
+        <v>-2.651275063507386</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.168297701716118</v>
+        <v>2.128391531257147</v>
       </c>
       <c r="F1999" t="n">
         <v>1.211186859059072</v>
@@ -47551,10 +47551,10 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.706290644138212</v>
+        <v>-2.806056070285641</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.143463121498463</v>
+        <v>2.103556951039491</v>
       </c>
       <c r="F2000" t="n">
         <v>1.177819185004596</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.699235953923039</v>
+        <v>-2.799001380070468</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.142960353574077</v>
+        <v>2.103054183115106</v>
       </c>
       <c r="F2001" t="n">
         <v>1.184873875219769</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633111</v>
+        <v>3.766673496331111</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.672284729596551</v>
+        <v>-2.77205015574398</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.163746996949414</v>
+        <v>2.123840826490443</v>
       </c>
       <c r="F2002" t="n">
         <v>1.199754221247489</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784102</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.808237737652867</v>
+        <v>-2.908003163800296</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.293468925871847</v>
+        <v>2.253562755412876</v>
       </c>
       <c r="F2003" t="n">
         <v>1.199754221247489</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.830645855457739</v>
+        <v>-2.930411281605168</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.276622373652891</v>
+        <v>2.23671620319392</v>
       </c>
       <c r="F2004" t="n">
         <v>1.199754221247489</v>
@@ -47666,10 +47666,10 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.858870091035339</v>
+        <v>-2.958635517182768</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.267386678971489</v>
+        <v>2.227480508512517</v>
       </c>
       <c r="F2005" t="n">
         <v>1.217730973698797</v>
@@ -47689,10 +47689,10 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.868311016923869</v>
+        <v>-2.968076443071298</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.319864026337924</v>
+        <v>2.279957855878953</v>
       </c>
       <c r="F2006" t="n">
         <v>1.340158091242189</v>
@@ -47712,10 +47712,10 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.920584624259511</v>
+        <v>-3.02035005040694</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.301845677948968</v>
+        <v>2.261939507489997</v>
       </c>
       <c r="F2007" t="n">
         <v>1.287884483906547</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.996914601860416</v>
+        <v>-3.096680028007845</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.269425499802381</v>
+        <v>2.22951932934341</v>
       </c>
       <c r="F2008" t="n">
         <v>1.287884483906547</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.19916832218477</v>
+        <v>-3.298933748332199</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.183344241275502</v>
+        <v>2.143438070816531</v>
       </c>
       <c r="F2009" t="n">
         <v>1.085630763582194</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.360736747712025</v>
+        <v>-3.460502173859454</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.117150881274752</v>
+        <v>2.077244710815781</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9588478397843144</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.493038039809578</v>
+        <v>-3.592803465957007</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.07730377130165</v>
+        <v>2.037397600842678</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9588478397843144</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.678906350648808</v>
+        <v>-3.778671776796237</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.994961643748898</v>
+        <v>1.955055473289926</v>
       </c>
       <c r="F2012" t="n">
         <v>0.8002822464643667</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.706807137758281</v>
+        <v>-3.80657256390571</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.982325370032111</v>
+        <v>1.942419199573139</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7656853223214319</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787383</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.829333240461175</v>
+        <v>-3.929098666608604</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.930079372928152</v>
+        <v>1.89017320246918</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6431592196185381</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.059847736646764</v>
+        <v>-4.159613162794193</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.90457953404442</v>
+        <v>1.864673363585449</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4126447234329493</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814661</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.316568554641588</v>
+        <v>-4.416333980789016</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.942202925848338</v>
+        <v>1.902296755389366</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3042301492891345</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237089</v>
+        <v>3.66828900423709</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.470554972417728</v>
+        <v>-4.570320398565157</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.949588627883521</v>
+        <v>1.90968245742455</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3042301492891345</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.420033068590063</v>
+        <v>-4.519798494737491</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.955848591534708</v>
+        <v>1.915942421075737</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3042301492891345</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.65633273360975</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.672508222597787</v>
+        <v>-4.772273648745215</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.866729018987032</v>
+        <v>1.826822848528061</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3042301492891345</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973153</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.965403979077199</v>
+        <v>-5.065169405224627</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.750781250914211</v>
+        <v>1.71087508045524</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3042301492891345</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251941</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.152068107212007</v>
+        <v>-5.251833533359435</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.68023734188761</v>
+        <v>1.640331171428638</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2774911784645746</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.430032502795281</v>
+        <v>-5.529797928942709</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.564129436390489</v>
+        <v>1.524223265931518</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1878714441790904</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.547000195434172</v>
+        <v>-5.6467656215816</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.679546416033977</v>
+        <v>1.639640245575006</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1878714441790904</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.631718137655125</v>
+        <v>-5.731483563802553</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.64050587710941</v>
+        <v>1.600599706650439</v>
       </c>
       <c r="F2024" t="n">
         <v>0.102755415251044</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.713652955924008</v>
+        <v>-5.813418382071436</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.617961367370348</v>
+        <v>1.578055196911377</v>
       </c>
       <c r="F2025" t="n">
         <v>0.0928206696639638</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.783632867332687</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.815629078172416</v>
+        <v>-5.915394504319844</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.586096556926888</v>
+        <v>1.546190386467916</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.00915545258444378</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231804</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.705622794695194</v>
+        <v>-5.805388220842622</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.622251957561951</v>
+        <v>1.58234578710298</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01404911933283143</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.562563218954269</v>
+        <v>-5.662328645101697</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.683725798580296</v>
+        <v>1.643819628121324</v>
       </c>
       <c r="F2028" t="n">
         <v>0.02206254592281071</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.261116493482431</v>
+        <v>-5.360881919629859</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.811565371651567</v>
+        <v>1.771659201192596</v>
       </c>
       <c r="F2029" t="n">
         <v>0.323509271394648</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.285706737717615</v>
+        <v>-5.385472163865043</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.802700451710204</v>
+        <v>1.762794281251232</v>
       </c>
       <c r="F2030" t="n">
         <v>0.323509271394648</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.234668361711095</v>
+        <v>-5.334433787858523</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.823958706492567</v>
+        <v>1.784052536033596</v>
       </c>
       <c r="F2031" t="n">
         <v>0.323509271394648</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.193529066844464</v>
+        <v>-5.293294492991892</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.859452523313365</v>
+        <v>1.819546352854394</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3646485662612788</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.082922926764862</v>
+        <v>-5.18268835291229</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.71987897546914</v>
+        <v>1.679972805010169</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4752547063408808</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.213503661295705</v>
+        <v>-5.313269087443133</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.671148725730767</v>
+        <v>1.631242555271796</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3446739718100383</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.049007327104743</v>
+        <v>-5.148772753252171</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.721374078483234</v>
+        <v>1.681467908024263</v>
       </c>
       <c r="F2035" t="n">
         <v>0.3446739718100383</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.076377259789175</v>
+        <v>-5.176142685936603</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.709613815845891</v>
+        <v>1.66970764538692</v>
       </c>
       <c r="F2036" t="n">
         <v>0.3446739718100383</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.086762454679064</v>
+        <v>-5.186527880826493</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.715328517015008</v>
+        <v>1.675422346556037</v>
       </c>
       <c r="F2037" t="n">
         <v>0.334288776920149</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.105350613401289</v>
+        <v>-5.205116039548717</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.778730259302543</v>
+        <v>1.738824088843572</v>
       </c>
       <c r="F2038" t="n">
         <v>0.3157006181979236</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.105649160097325</v>
+        <v>-5.205414586244753</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.775479851442427</v>
+        <v>1.735573680983456</v>
       </c>
       <c r="F2039" t="n">
         <v>0.3157006181979236</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.004826026406898</v>
+        <v>-5.104591452554326</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.820339999857989</v>
+        <v>1.780433829399018</v>
       </c>
       <c r="F2040" t="n">
         <v>0.3281648336822774</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.814044665654491</v>
+        <v>-4.913810091801919</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.896781797637496</v>
+        <v>1.856875627178524</v>
       </c>
       <c r="F2041" t="n">
         <v>0.5189461944346848</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.79552781161267</v>
+        <v>-4.895293237760098</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.88402538499182</v>
+        <v>1.844119214532849</v>
       </c>
       <c r="F2042" t="n">
         <v>0.531876323859893</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.770334627111352</v>
+        <v>-4.87010005325878</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.929069595404406</v>
+        <v>1.889163424945435</v>
       </c>
       <c r="F2043" t="n">
         <v>0.5570695083612114</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.758280500198389</v>
+        <v>-4.858045926345818</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.927577814071029</v>
+        <v>1.887671643612058</v>
       </c>
       <c r="F2044" t="n">
         <v>0.5691236352741742</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.764903746888748</v>
+        <v>-4.864669173036176</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.926809145579021</v>
+        <v>1.88690297512005</v>
       </c>
       <c r="F2045" t="n">
         <v>0.5625003885838158</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.662023157360155</v>
+        <v>-4.761788583507583</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.980812407268341</v>
+        <v>1.940906236809369</v>
       </c>
       <c r="F2046" t="n">
         <v>0.6653809781124087</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.685465196540242</v>
+        <v>-4.78523062268767</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.9916382617699</v>
+        <v>1.951732091310929</v>
       </c>
       <c r="F2047" t="n">
         <v>0.6653809781124087</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781706</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.703537704831853</v>
+        <v>-4.803303130979281</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.984409258453256</v>
+        <v>1.944503087994285</v>
       </c>
       <c r="F2048" t="n">
         <v>0.6653809781124087</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082835</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.934711498708485</v>
+        <v>-5.034476924855913</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.85219165449607</v>
+        <v>1.812285484037099</v>
       </c>
       <c r="F2049" t="n">
         <v>0.6653809781124087</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.90342547816803</v>
+        <v>-5.003190904315458</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.871728681709192</v>
+        <v>1.83182251125022</v>
       </c>
       <c r="F2050" t="n">
         <v>0.6966669986528641</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.750400086054746</v>
+        <v>-4.850165512202174</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.032109838127409</v>
+        <v>1.992203667668438</v>
       </c>
       <c r="F2051" t="n">
         <v>0.8496923907661482</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.778707399928016</v>
+        <v>-4.878472826075444</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.208253137486394</v>
+        <v>2.168346967027423</v>
       </c>
       <c r="F2052" t="n">
         <v>0.8496923907661482</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.945300625041538</v>
+        <v>-5.045066051188966</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.111018798795067</v>
+        <v>2.071112628336096</v>
       </c>
       <c r="F2053" t="n">
         <v>0.6830991656526257</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.772236245659238</v>
+        <v>-4.872001671806666</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.183920953209705</v>
+        <v>2.144014782750734</v>
       </c>
       <c r="F2054" t="n">
         <v>0.6830991656526257</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682206</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.742990265203542</v>
+        <v>-4.84275569135097</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.193237400515479</v>
+        <v>2.153331230056508</v>
       </c>
       <c r="F2055" t="n">
         <v>0.6830991656526257</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539108</v>
+        <v>3.69942482753911</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.752705541541678</v>
+        <v>-4.852470967689106</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.186644529137859</v>
+        <v>2.146738358678888</v>
       </c>
       <c r="F2056" t="n">
         <v>0.673383889314489</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.780224766077501</v>
+        <v>3.780224766077503</v>
       </c>
       <c r="C2057" t="n">
         <v>4.17304740647968</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.752705541541678</v>
+        <v>-4.852470967689106</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.186644529137859</v>
+        <v>2.146738358678888</v>
       </c>
       <c r="F2057" t="n">
         <v>0.673383889314489</v>

--- a/tame_output/ON/bt/strategyON_20240815.xlsx
+++ b/tame_output/ON/bt/strategyON_20240815.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>59.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>99.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.2%</t>
+          <t>429.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-646.8%</t>
+          <t>-648.6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.5%</t>
+          <t>-162.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.4%</t>
+          <t>-407.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-156.7%</t>
+          <t>-169.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,37 +1456,37 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-35.4%</t>
         </is>
       </c>
     </row>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097813</v>
+        <v>3.341378723097814</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.433987709767826</v>
+        <v>-6.25757582969015</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5449271854718107</v>
+        <v>0.6154919375028811</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094108</v>
+        <v>3.374439043094109</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.777246229410845</v>
+        <v>-6.600834349333169</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4037233427602986</v>
+        <v>0.4742880947913686</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199277</v>
+        <v>3.405960511199278</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.825449046653189</v>
+        <v>-6.649037166575513</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3828471359183618</v>
+        <v>0.4534118879494322</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969585</v>
+        <v>3.424633354969586</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.122110388463386</v>
+        <v>-6.945698508385711</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2679615751234912</v>
+        <v>0.3385263271545615</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.8087317556553376</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.308830096772689</v>
+        <v>-7.132418216695013</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1892473872653668</v>
+        <v>0.2598121392964372</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.8087317556553376</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297741</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.69183148551532</v>
+        <v>-7.515419605437645</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.03594473044673041</v>
+        <v>0.1065094824778008</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.8087317556553376</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317609</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.696317930716709</v>
+        <v>-7.519906050639033</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.03672166833760526</v>
+        <v>0.1072864203686752</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8132182008567264</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737163</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.055848253220711</v>
+        <v>-7.879436373143035</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1017401573659455</v>
+        <v>-0.03117540533487517</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8132182008567264</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341306</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.106197316674933</v>
+        <v>-7.929785436597257</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1139637627904571</v>
+        <v>-0.04339901075938668</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8635672643109484</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539457</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.203816594096329</v>
+        <v>-8.027404714018653</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1499697231372465</v>
+        <v>-0.07940497110617617</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9611865417323451</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.257888093604688</v>
+        <v>-8.081476213527012</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.168704766619018</v>
+        <v>-0.09814001458794719</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.015258041240704</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.462146268934552</v>
+        <v>-8.285734388856875</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2448948396323209</v>
+        <v>-0.1743300876012506</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.142896985854693</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.495799107443025</v>
+        <v>-8.319387227365349</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2538734205512743</v>
+        <v>-0.1833086685202039</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.243310353771731</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.422329275775576</v>
+        <v>-8.2459173956979</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2091137863908736</v>
+        <v>-0.1385490343598033</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.169840522104282</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.597453693162119</v>
+        <v>-8.421041813084443</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.264608332597974</v>
+        <v>-0.1940435805669036</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.344964939490826</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.831905787176609</v>
+        <v>-8.655493907098933</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3656083351053661</v>
+        <v>-0.2950435830742957</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.344964939490826</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.936280518203056</v>
+        <v>-8.759868638125379</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4140304182899208</v>
+        <v>-0.3434656662588504</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.449339670517272</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.09879398390164</v>
+        <v>-8.922382103823963</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.477920014730798</v>
+        <v>-0.4073552626997277</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.546973100935959</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.224830777269929</v>
+        <v>-9.048418897192253</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5256410034489991</v>
+        <v>-0.4550762514179287</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.521721478126216</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.167759005373998</v>
+        <v>-8.991347125296322</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4988219590042262</v>
+        <v>-0.4282572069731554</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.521721478126216</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.309430847098119</v>
+        <v>-9.133018967020442</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.556965922592616</v>
+        <v>-0.4864011705615452</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.521721478126216</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940715</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.259840002673284</v>
+        <v>-9.083428122595608</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5220761746578098</v>
+        <v>-0.4515114226267394</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.472130633701382</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770575</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.110921668201428</v>
+        <v>-8.934509788123751</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4755599745157504</v>
+        <v>-0.4049952224846796</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.440881042966209</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615278</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.885076515482016</v>
+        <v>-8.70866463540434</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3756428403917771</v>
+        <v>-0.3050780883607063</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.398954367379046</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.760497859144424</v>
+        <v>-8.584085979066748</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3246722333006811</v>
+        <v>-0.2541074812696107</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.398954367379046</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646212</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.813393147188711</v>
+        <v>-8.636981267111034</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3431965743562881</v>
+        <v>-0.2726318223252178</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.393999021290599</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611563</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.741259971900829</v>
+        <v>-8.564848091823153</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3086096000024994</v>
+        <v>-0.2380448479714286</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.393999021290599</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955323</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669893579291182</v>
+        <v>-8.493481699213506</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2898003053525056</v>
+        <v>-0.2192355533214352</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.322632628680952</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232408</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.576434545305958</v>
+        <v>-8.400022665228281</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2623001730713233</v>
+        <v>-0.1917354210402529</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.322632628680952</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436224</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.565781363752526</v>
+        <v>-8.38936948367485</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2598734609493243</v>
+        <v>-0.1893087089182539</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.322632628680952</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467874325076036</v>
+        <v>-8.291462444998359</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.221010960452189</v>
+        <v>-0.1504462084211187</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.254646878820395</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097237</v>
+        <v>3.800829354097238</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443920784100078</v>
+        <v>-8.267508904022401</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2107610379163121</v>
+        <v>-0.1401962858852417</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.230693337844438</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017764</v>
+        <v>3.789311112017765</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179860845777281</v>
+        <v>-8.003448965699604</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1183973787489458</v>
+        <v>-0.04783262671787547</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9666333995216414</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839717</v>
+        <v>3.833252747839718</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.472781222272443</v>
+        <v>-7.296369342194766</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1616474369926886</v>
+        <v>0.232212189023759</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9666333995216414</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388722</v>
+        <v>3.839374447388723</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.432596923906252</v>
+        <v>-7.256185043828576</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1780647802270061</v>
+        <v>0.2486295322580765</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.9264491011554506</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626467</v>
+        <v>3.856161751626468</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.26919705296689</v>
+        <v>-7.092785172889213</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.242791549823508</v>
+        <v>0.3133563018545784</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.7630492302160882</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291809</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.035715830737291</v>
+        <v>-6.859303950659615</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3441084675532</v>
+        <v>0.4146732195842704</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.5295680079864896</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.886049439729776</v>
+        <v>-6.7096375596521</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4010828136432467</v>
+        <v>0.4716475656743171</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.4366645167439537</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.75377396609889</v>
+        <v>-6.577362086021213</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4493604898426287</v>
+        <v>0.5199252418736986</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.304389043113067</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.598035633539148</v>
+        <v>-6.421623753461471</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.514470883554162</v>
+        <v>0.585035635585232</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.1486507105533255</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.513070966809828</v>
+        <v>-6.336659086732152</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5613630914695489</v>
+        <v>0.6319278435006184</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.06368604382400589</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.618660956582932</v>
+        <v>-6.442249076505257</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3911511659610882</v>
+        <v>0.4617159179921582</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.1692760335971102</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.550426371957505</v>
+        <v>-6.374014491879829</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4669893416883455</v>
+        <v>0.5375540937194154</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.1508607107245742</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.402486330549905</v>
+        <v>-6.22607445047223</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4062864355632176</v>
+        <v>0.4768511875942876</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1305397948160167</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.349516808295917</v>
+        <v>-6.173104928218241</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4187602582113348</v>
+        <v>0.4893250102424047</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.07757027256202781</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.183728612335626</v>
+        <v>-6.007316732257951</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4781149245003582</v>
+        <v>0.5486796765314281</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.07757027256202781</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.150365405856857</v>
+        <v>-5.973953525779182</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5059225614730085</v>
+        <v>0.5764873135040784</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.07757027256202781</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.042106268734336</v>
+        <v>-5.86569438865666</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5437583367812122</v>
+        <v>0.6143230888122821</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.07757027256202781</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.918815133917205</v>
+        <v>-5.742403253839529</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5905728847186418</v>
+        <v>0.6611376367497117</v>
       </c>
       <c r="F1915" t="n">
         <v>0.04572086225510269</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.866118266785914</v>
+        <v>-5.689706386708238</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6193526098084834</v>
+        <v>0.6899173618395533</v>
       </c>
       <c r="F1916" t="n">
         <v>0.09841772938639387</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.622352824802469</v>
+        <v>-5.445940944724794</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7126394949489119</v>
+        <v>0.7832042469799818</v>
       </c>
       <c r="F1917" t="n">
         <v>0.09841772938639387</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.532577152425997</v>
+        <v>-5.356165272348322</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7506740778195167</v>
+        <v>0.8212388298505866</v>
       </c>
       <c r="F1918" t="n">
         <v>0.1600171743007039</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.282726758476922</v>
+        <v>-5.106314878399247</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8433563103828488</v>
+        <v>0.9139210624139187</v>
       </c>
       <c r="F1919" t="n">
         <v>0.1600171743007039</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.10683466600949</v>
+        <v>-4.930422785931815</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9173122708904704</v>
+        <v>0.9878770229215401</v>
       </c>
       <c r="F1920" t="n">
         <v>0.1600171743007039</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.935388202987027</v>
+        <v>-4.758976322909351</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9992183621540094</v>
+        <v>1.069783114185079</v>
       </c>
       <c r="F1921" t="n">
         <v>0.331463637323167</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.855365915877906</v>
+        <v>-4.67895403580023</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.030247754613955</v>
+        <v>1.100812506645025</v>
       </c>
       <c r="F1922" t="n">
         <v>0.411485924432288</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.791730173643971</v>
+        <v>-4.615318293566296</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.060396852561846</v>
+        <v>1.130961604592916</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4751216666662225</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.698032855427576</v>
+        <v>-4.521620975349901</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.079070038632199</v>
+        <v>1.149634790663269</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4751216666662225</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.708535478492865</v>
+        <v>-4.53212359841519</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.076612066030961</v>
+        <v>1.147176818062031</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4646190436009336</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.628421434975942</v>
+        <v>-4.459881030243995</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.112586997272551</v>
+        <v>1.180003159165329</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4646190436009336</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.610707748098076</v>
+        <v>-4.44216734336613</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.120351055941037</v>
+        <v>1.187767217833815</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4678003724978504</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.501902862618349</v>
+        <v>-4.333362457886403</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.160871081352921</v>
+        <v>1.228287243245699</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4678003724978504</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.281882064581339</v>
+        <v>-4.113341659849392</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.25045843757834</v>
+        <v>1.317874599471118</v>
       </c>
       <c r="F1929" t="n">
         <v>0.6090202175658307</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.149014375518061</v>
+        <v>-3.980473970786114</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.319499696005474</v>
+        <v>1.386915857898253</v>
       </c>
       <c r="F1930" t="n">
         <v>0.6090202175658307</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.028841292153563</v>
+        <v>-3.860300887421615</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.368714773791575</v>
+        <v>1.436130935684354</v>
       </c>
       <c r="F1931" t="n">
         <v>0.7291933009303296</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.893587930823585</v>
+        <v>-3.725047526091638</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.432904220885006</v>
+        <v>1.500320382777785</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8644466622603068</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.953462758181278</v>
+        <v>-3.78492235344933</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.394991781343355</v>
+        <v>1.462407943236134</v>
       </c>
       <c r="F1933" t="n">
         <v>0.8045718349026146</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.83364252727044</v>
+        <v>-3.665102122538493</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.458209042941898</v>
+        <v>1.525625204834677</v>
       </c>
       <c r="F1934" t="n">
         <v>0.8045718349026146</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.836112233732246</v>
+        <v>-3.667571829000299</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.364865359679618</v>
+        <v>1.432281521572396</v>
       </c>
       <c r="F1935" t="n">
         <v>0.8021021284408085</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.904482420056256</v>
+        <v>-3.735942015324309</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.256779146635315</v>
+        <v>1.324195308528094</v>
       </c>
       <c r="F1936" t="n">
         <v>0.8113778274770235</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.918270472903303</v>
+        <v>-3.749730068171355</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.241700634128388</v>
+        <v>1.309116796021166</v>
       </c>
       <c r="F1937" t="n">
         <v>0.8113778274770235</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.973790548795892</v>
+        <v>-3.805250144063945</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.356523440463554</v>
+        <v>1.423939602356333</v>
       </c>
       <c r="F1938" t="n">
         <v>0.8113778274770235</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.798316289003423</v>
+        <v>-3.629775884271476</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.43128037637233</v>
+        <v>1.498696538265108</v>
       </c>
       <c r="F1939" t="n">
         <v>0.8113778274770235</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.909252541644672</v>
+        <v>-3.740712136912724</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.362647904077037</v>
+        <v>1.430064065969816</v>
       </c>
       <c r="F1940" t="n">
         <v>0.8113778274770235</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.87558899617239</v>
+        <v>-3.707048591440442</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.3046516356674</v>
+        <v>1.372067797560178</v>
       </c>
       <c r="F1941" t="n">
         <v>0.8450413729493054</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.815736376968667</v>
+        <v>-3.647195972236719</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.338765069781021</v>
+        <v>1.4061812316738</v>
       </c>
       <c r="F1942" t="n">
         <v>0.8450413729493054</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.729492913942289</v>
+        <v>-3.560952509210342</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.368208725565433</v>
+        <v>1.435624887458211</v>
       </c>
       <c r="F1943" t="n">
         <v>0.8450413729493054</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.774799733341269</v>
+        <v>-3.606259328609322</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.341861773250366</v>
+        <v>1.409277935143145</v>
       </c>
       <c r="F1944" t="n">
         <v>0.8042312099400746</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.803832838043571</v>
+        <v>-3.635292433311623</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.330800404402547</v>
+        <v>1.398216566295326</v>
       </c>
       <c r="F1945" t="n">
         <v>0.8042312099400746</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.711022356592712</v>
+        <v>-3.542481951860764</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.297197288874257</v>
+        <v>1.364613450767035</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8970416913909339</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.755411825922139</v>
+        <v>-3.586871421190192</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.281314977067086</v>
+        <v>1.348731138959865</v>
       </c>
       <c r="F1947" t="n">
         <v>0.8526522220615063</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.871953431027482</v>
+        <v>-3.703413026295534</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.229774043536672</v>
+        <v>1.297190205429451</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7361106169561635</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.911877525610054</v>
+        <v>-3.743337120878106</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.219295701534311</v>
+        <v>1.28671186342709</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7361106169561635</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.939657923511407</v>
+        <v>-3.771117518779459</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.219680744142309</v>
+        <v>1.287096906035087</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7083302190548104</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.058038596241545</v>
+        <v>-3.889498191509598</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.010684195050907</v>
+        <v>1.078100356943685</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6411123669038342</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.166652674684876</v>
+        <v>-3.998112269952929</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.08738822439278</v>
+        <v>1.154804386285558</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6411123669038342</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.131243636436733</v>
+        <v>-3.962703231704786</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.11606486579436</v>
+        <v>1.183481027687139</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6411123669038342</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.092859973878582</v>
+        <v>-3.924319569146635</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.128837772159989</v>
+        <v>1.196253934052768</v>
       </c>
       <c r="F1954" t="n">
         <v>0.6794960294619854</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.915743643843416</v>
+        <v>-3.747203239111469</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.196413333019358</v>
+        <v>1.263829494912136</v>
       </c>
       <c r="F1955" t="n">
         <v>0.6794960294619854</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.960835888676962</v>
+        <v>-3.792295483945014</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.179059826847852</v>
+        <v>1.246475988740631</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6175999862925956</v>
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.781460467438194</v>
+        <v>-3.799600631621227</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.244596970649774</v>
+        <v>1.23734090497656</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7743767444633143</v>
+        <v>0.6489126794788868</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.222163628616787</v>
+        <v>3.146885189626131</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.8264746809588</v>
+        <v>-3.844614845141833</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.207398740573121</v>
+        <v>1.200142674899908</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7440278491487097</v>
+        <v>0.6185637841642821</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.184761746759615</v>
+        <v>3.109483307768958</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.093479191231236</v>
+        <v>-4.111619355414268</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.106288498803093</v>
+        <v>1.099032433129879</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5496648111057612</v>
+        <v>0.4242007461213336</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.073835486272791</v>
+        <v>2.998557047282135</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.194676972668408</v>
+        <v>-4.212817136851441</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.065013308124725</v>
+        <v>1.057757242451512</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.481255997560442</v>
+        <v>0.3557919325760144</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.031994120042101</v>
+        <v>2.956715681051445</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.188166006054096</v>
+        <v>-4.206306170237128</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.065217656324767</v>
+        <v>1.057961590651553</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.481255997560442</v>
+        <v>0.3557919325760144</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.029594081596418</v>
+        <v>2.954315642605761</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.169127878346798</v>
+        <v>-4.187268042529831</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.069357626615931</v>
+        <v>1.062101560942717</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.2976083212448198</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.991208634005946</v>
+        <v>2.915930195015289</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.221643680621619</v>
+        <v>-4.239783844804651</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.167645707340193</v>
+        <v>1.160389641666979</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4230723862292474</v>
+        <v>0.2976083212448198</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.110503035640136</v>
+        <v>3.03522459664948</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.235510441955537</v>
+        <v>-4.253650606138569</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.162932331792759</v>
+        <v>1.155676266119546</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.2597504045109969</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.088621614585976</v>
+        <v>3.01334317559532</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.190706270415607</v>
+        <v>-4.208846434598639</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.186862530805657</v>
+        <v>1.179606465132444</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3852144694954245</v>
+        <v>0.2597504045109969</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.094630144982902</v>
+        <v>3.019351705992245</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.042963300180604</v>
+        <v>-4.061103464363637</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.143909940176858</v>
+        <v>1.136653874503644</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.4275577617458801</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.093264780601031</v>
+        <v>3.017986341610375</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.126784521455303</v>
+        <v>-4.144924685638335</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.113175073198459</v>
+        <v>1.105919007525246</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5530218267303076</v>
+        <v>0.4275577617458801</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.096058402132512</v>
+        <v>3.020779963141856</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.120631815402518</v>
+        <v>-4.138771979585551</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.116298504011231</v>
+        <v>1.109042438338018</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5591745327830919</v>
+        <v>0.4337104677986643</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100412374155841</v>
+        <v>3.025133935165185</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.13744111355302</v>
+        <v>-4.155581277736053</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.108655261491141</v>
+        <v>1.101399195817927</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5423652346325902</v>
+        <v>0.4169011696481627</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.08940727200565</v>
+        <v>3.014128833014994</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.075143114776898</v>
+        <v>-4.09328327895993</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.199910014798411</v>
+        <v>1.192653949125197</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5876594989070323</v>
+        <v>0.4621954339226048</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182919384367136</v>
+        <v>3.10764094537648</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.87335291711174</v>
+        <v>-3.891493081294772</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.082918095578601</v>
+        <v>1.075662029905387</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7856776910761867</v>
+        <v>0.6602136260917592</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.104022301382756</v>
+        <v>3.0287438623921</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.924239629797935</v>
+        <v>-3.942379793980967</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.132853642826298</v>
+        <v>1.125597577153085</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7347909783899922</v>
+        <v>0.6093269134055646</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143780506093215</v>
+        <v>3.068502067102558</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.837628887148127</v>
+        <v>-3.85576905133116</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.182125676002265</v>
+        <v>1.174869610329051</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8134167095951504</v>
+        <v>0.6879526446107228</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.205583680932353</v>
+        <v>3.130305241941697</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.897838185153412</v>
+        <v>-3.915978349336444</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.156577937624823</v>
+        <v>1.149321871951609</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.6277433466054383</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.167994082953854</v>
+        <v>3.092715643963198</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.821416138721485</v>
+        <v>-3.839556302904517</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.185638374237522</v>
+        <v>1.178382308564309</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7532074115898659</v>
+        <v>0.6277433466054383</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166485700993783</v>
+        <v>3.091207262003127</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.777043007082916</v>
+        <v>-3.795183171265949</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.203250494328385</v>
+        <v>1.195994428655172</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.6721164782440069</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.19297244741236</v>
+        <v>3.117694008421704</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.799523357941801</v>
+        <v>-3.817663522124834</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.188652148123422</v>
+        <v>1.181396082450209</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7975805432284345</v>
+        <v>0.6721164782440069</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187366241550951</v>
+        <v>3.112087802560294</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.751867627380745</v>
+        <v>-3.770007791563778</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.214096197375649</v>
+        <v>1.206840131702436</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8452362737894902</v>
+        <v>0.7197722088050625</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222341436915389</v>
+        <v>3.147062997924732</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.651349468881991</v>
+        <v>-3.669489633065023</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.259195834149876</v>
+        <v>1.251939768476662</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9457544322882447</v>
+        <v>0.8202903673038171</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287544705389366</v>
+        <v>3.21226626639871</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.635444139449638</v>
+        <v>-3.653584303632671</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.252312638398689</v>
+        <v>1.245056572725476</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8666417715790058</v>
+        <v>0.7411777065945782</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226831781439695</v>
+        <v>3.151553342449039</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.59060573784124</v>
+        <v>-3.608745902024272</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.274345701652677</v>
+        <v>1.267089635979463</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8711852045238753</v>
+        <v>0.7457211395394476</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233655543817246</v>
+        <v>3.158377104826589</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.610104194083248</v>
+        <v>-3.628244358266281</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.270707258786951</v>
+        <v>1.263451193113738</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.823100563243971</v>
+        <v>0.6976364982595433</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208965698680381</v>
+        <v>3.133687259689725</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.565901356997348</v>
+        <v>-3.58404152118038</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.294267996149149</v>
+        <v>1.287011930475936</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8673034003298714</v>
+        <v>0.7418393353454438</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241367003459758</v>
+        <v>3.166088564469102</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.573461022834395</v>
+        <v>-3.591601187017427</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.289654130283578</v>
+        <v>1.282398064610364</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.7966427393552631</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272659046334898</v>
+        <v>3.197380607344241</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.415169605295123</v>
+        <v>-3.433309769478155</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.404218462482326</v>
+        <v>1.396962396809113</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9221068043396907</v>
+        <v>0.7966427393552631</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323906811517937</v>
+        <v>3.248628372527281</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.207527601660646</v>
+        <v>-3.225667765843679</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.48571596853037</v>
+        <v>1.478459902857157</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.129748807974167</v>
+        <v>1.004284742989739</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446932718292876</v>
+        <v>3.37165427930222</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.156495508938118</v>
+        <v>-3.174635673121151</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.501077033857651</v>
+        <v>1.493820968184438</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.180780900696695</v>
+        <v>1.055316835712267</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472500202164663</v>
+        <v>3.397221763174006</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.091271327810913</v>
+        <v>-3.109411491993945</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.544354110401238</v>
+        <v>1.537098044728025</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.246005081823901</v>
+        <v>1.120541016839473</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528822114933691</v>
+        <v>3.453543675943035</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.053844307739779</v>
+        <v>-3.071984471922811</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.555285890728972</v>
+        <v>1.548029825055759</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.251256619853082</v>
+        <v>1.125792554868655</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527934010050481</v>
+        <v>3.452655571059824</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.073955963774487</v>
+        <v>-3.092096127957519</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.548498020646329</v>
+        <v>1.541241954973116</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.262283964850502</v>
+        <v>1.136819899866074</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535807209380172</v>
+        <v>3.460528770389516</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.020211149347282</v>
+        <v>-3.038351313530315</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.730553717438422</v>
+        <v>1.723297651765209</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.272347274290964</v>
+        <v>1.146883209306536</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.702402966065661</v>
+        <v>3.627124527075004</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.94542888832227</v>
+        <v>-2.963569052505302</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.880579531066244</v>
+        <v>1.873323465393031</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.347129535315976</v>
+        <v>1.221665470331549</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.867385231898485</v>
+        <v>3.792106792907829</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.919344804058462</v>
+        <v>-2.937484968241494</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.882721140785626</v>
+        <v>1.875465075112413</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.347129535315976</v>
+        <v>1.221665470331549</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.859093207912344</v>
+        <v>3.783814768921688</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.831466890949341</v>
+        <v>-2.849607055132374</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.916065501613054</v>
+        <v>1.908809435939841</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.463055177739327</v>
+        <v>1.3375911127549</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.926841788950134</v>
+        <v>3.851563349959478</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.822574429556058</v>
+        <v>-2.84071459373909</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.937176891897159</v>
+        <v>1.929920826223945</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.463055177739327</v>
+        <v>1.3375911127549</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.944396194676925</v>
+        <v>3.869117755686269</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.991050546525936</v>
+        <v>-3.009190710708968</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.861641492513791</v>
+        <v>1.854385426840578</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.435107342022747</v>
+        <v>1.309643277038319</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.919482540651561</v>
+        <v>3.844204101660905</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.544794353896496</v>
+        <v>-2.562934518079528</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.021413666753429</v>
+        <v>2.014157601080216</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.340388672353114</v>
+        <v>1.214924607368686</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.843921036037643</v>
+        <v>3.768642597046987</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.522073250213343</v>
+        <v>-2.540213414396375</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.021166130723595</v>
+        <v>2.013910065050382</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.340388672353114</v>
+        <v>1.214924607368686</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.834585058534548</v>
+        <v>3.759306619543891</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.651275063507386</v>
+        <v>-2.669415227690418</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.128391531257147</v>
+        <v>2.121135465583934</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.211186859059072</v>
+        <v>1.085722794074644</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.915970096409292</v>
+        <v>3.840691657418635</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.806056070285641</v>
+        <v>-2.824196234468674</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.103556951039491</v>
+        <v>2.096300885366278</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.177819185004596</v>
+        <v>1.052355120020168</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933027314470253</v>
+        <v>3.857748875479596</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.799001380070468</v>
+        <v>-2.8171415442535</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.103054183115106</v>
+        <v>2.095798117441892</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.184873875219769</v>
+        <v>1.059409810235342</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933935484588902</v>
+        <v>3.858657045598245</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.77205015574398</v>
+        <v>-2.790190319927012</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.123840826490443</v>
+        <v>2.116584760817229</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.199754221247489</v>
+        <v>1.074290156263061</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952869845850275</v>
+        <v>3.877591406859619</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.908003163800296</v>
+        <v>-2.926143327983328</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.253562755412876</v>
+        <v>2.246306689739662</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.199754221247489</v>
+        <v>1.074290156263061</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136972977995235</v>
+        <v>4.061694539004578</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.930411281605168</v>
+        <v>-2.9485514457882</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.23671620319392</v>
+        <v>2.229460137520707</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.199754221247489</v>
+        <v>1.074290156263061</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129089672898228</v>
+        <v>4.053811233907571</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.958635517182768</v>
+        <v>-2.976775681365801</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.227480508512517</v>
+        <v>2.220224442839304</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.217730973698797</v>
+        <v>1.092266908714369</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141929723918651</v>
+        <v>4.066651284927994</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.968076443071298</v>
+        <v>-2.986216607254331</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.279957855878953</v>
+        <v>2.27270179020574</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.340158091242189</v>
+        <v>1.214694026257761</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271639712166532</v>
+        <v>4.196361273175876</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.02035005040694</v>
+        <v>-3.038490214589972</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.261939507489997</v>
+        <v>2.254683441816784</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.287884483906547</v>
+        <v>1.16242041892212</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.243166642310449</v>
+        <v>4.167888203319792</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.096680028007845</v>
+        <v>-3.114820192190878</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.22951932934341</v>
+        <v>2.222263263670197</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.287884483906547</v>
+        <v>1.16242041892212</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.241278455204224</v>
+        <v>4.166000016213567</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.298933748332199</v>
+        <v>-3.317073912515231</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.143438070816531</v>
+        <v>2.136182005143318</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.085630763582194</v>
+        <v>0.9601666985977662</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.114746452612474</v>
+        <v>4.039468013621818</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.460502173859454</v>
+        <v>-3.478642338042486</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.077244710815781</v>
+        <v>2.069988645142568</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.8333837747998868</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.037110708543898</v>
+        <v>3.961832269553242</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.592803465957007</v>
+        <v>-3.610943630140039</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.037397600842678</v>
+        <v>2.030141535169465</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9588478397843144</v>
+        <v>0.8333837747998868</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.050184115409817</v>
+        <v>3.97490567641916</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.778671776796237</v>
+        <v>-3.79681194097927</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.955055473289926</v>
+        <v>1.947799407616713</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8002822464643667</v>
+        <v>0.6748181814799391</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947049956200789</v>
+        <v>3.871771517210132</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.80657256390571</v>
+        <v>-3.824712728088743</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.942419199573139</v>
+        <v>1.935163133899926</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7656853223214319</v>
+        <v>0.6402212573370043</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.92481584284203</v>
+        <v>3.849537403851373</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.929098666608604</v>
+        <v>-3.947238830791636</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.89017320246918</v>
+        <v>1.882917136795967</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6431592196185381</v>
+        <v>0.5176951546341104</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848064625197492</v>
+        <v>3.772786186206836</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.159613162794193</v>
+        <v>-4.177753326977225</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.864673363585449</v>
+        <v>1.857417297912235</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4126447234329493</v>
+        <v>0.2871806584485217</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.776461887076643</v>
+        <v>3.701183448085986</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.416333980789016</v>
+        <v>-4.434474144972049</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.902296755389366</v>
+        <v>1.895040689716152</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.1787660843047069</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.851724861592201</v>
+        <v>3.776446422601544</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.570320398565157</v>
+        <v>-4.58846056274819</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.90968245742455</v>
+        <v>1.902426391751336</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.1787660843047069</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.920705130737841</v>
+        <v>3.845426691747184</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.519798494737491</v>
+        <v>-4.537938658920524</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.915942421075737</v>
+        <v>1.908686355402523</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.1787660843047069</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.906756332857962</v>
+        <v>3.831477893867305</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.772273648745215</v>
+        <v>-4.790413812928248</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.826822848528061</v>
+        <v>1.819566782854848</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.1787660843047069</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.918626821913375</v>
+        <v>3.843348382922719</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.065169405224627</v>
+        <v>-5.08330956940766</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.71087508045524</v>
+        <v>1.703619014782026</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3042301492891345</v>
+        <v>0.1787660843047069</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.919837356432319</v>
+        <v>3.844558917441663</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.251833533359435</v>
+        <v>-5.269973697542468</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.640331171428638</v>
+        <v>1.633075105755425</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2774911784645746</v>
+        <v>0.152027113480147</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.907915716164905</v>
+        <v>3.832637277174248</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.529797928942709</v>
+        <v>-5.547938093125742</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.524223265931518</v>
+        <v>1.516967200258305</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1878714441790904</v>
+        <v>0.06240737919466272</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.849221728329804</v>
+        <v>3.773943289339147</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.6467656215816</v>
+        <v>-5.664905785764633</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.639640245575006</v>
+        <v>1.632384179901793</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1878714441790904</v>
+        <v>0.06240737919466272</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.011425785028848</v>
+        <v>3.936147346038191</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.731483563802553</v>
+        <v>-5.749623727985586</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.600599706650439</v>
+        <v>1.593343640977225</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.102755415251044</v>
+        <v>-0.02270864973338366</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.955202805635834</v>
+        <v>3.879924366645177</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.813418382071436</v>
+        <v>-5.831558546254469</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.578055196911377</v>
+        <v>1.570799131238163</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.0928206696639638</v>
+        <v>-0.03264339532046384</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.959471375852077</v>
+        <v>3.884192936861421</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.915394504319844</v>
+        <v>-5.933534668502877</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.546190386467916</v>
+        <v>1.538934320794703</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.00915545258444378</v>
+        <v>-0.1346195175688714</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.907211340958935</v>
+        <v>3.831932901968278</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.805388220842622</v>
+        <v>-5.823528385025655</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.58234578710298</v>
+        <v>1.575089721429767</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.01404911933283143</v>
+        <v>-0.1114149456515962</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.913286971353475</v>
+        <v>3.838008532362819</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.662328645101697</v>
+        <v>-5.68046880928473</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.643819628121324</v>
+        <v>1.636563562448111</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.02206254592281071</v>
+        <v>-0.1034015190616169</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.922345038029437</v>
+        <v>3.847066599038781</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.360881919629859</v>
+        <v>-5.379022083812893</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.771659201192596</v>
+        <v>1.764403135519382</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.323509271394648</v>
+        <v>0.1980452064102203</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.110473956195076</v>
+        <v>4.035195517204419</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.385472163865043</v>
+        <v>-5.403612328048077</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.762794281251232</v>
+        <v>1.755538215578019</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.323509271394648</v>
+        <v>0.1980452064102203</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.111445133947786</v>
+        <v>4.03616669495713</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.334433787858523</v>
+        <v>-5.352573952041556</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.784052536033596</v>
+        <v>1.776796470360382</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.323509271394648</v>
+        <v>0.1980452064102203</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.112288038327542</v>
+        <v>4.037009599336884</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.293294492991892</v>
+        <v>-5.311434657174925</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.819546352854394</v>
+        <v>1.81229028718118</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3646485662612788</v>
+        <v>0.2391845012768511</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.156009714121665</v>
+        <v>4.080731275131009</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.18268835291229</v>
+        <v>-5.200828517095323</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.679972805010169</v>
+        <v>1.672716739336956</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4752547063408808</v>
+        <v>0.3497906413564532</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.038557394293361</v>
+        <v>3.963278955302704</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.313269087443133</v>
+        <v>-5.331409251626166</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.631242555271796</v>
+        <v>1.623986489598582</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3446739718100383</v>
+        <v>0.2192099068256106</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.963710997648819</v>
+        <v>3.888432558658163</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.148772753252171</v>
+        <v>-5.166912917435204</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.681467908024263</v>
+        <v>1.674211842351049</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3446739718100383</v>
+        <v>0.2192099068256106</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.948137816724902</v>
+        <v>3.872859377734245</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.176142685936603</v>
+        <v>-5.194282850119636</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.66970764538692</v>
+        <v>1.662451579713706</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3446739718100383</v>
+        <v>0.2192099068256106</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.947325527161332</v>
+        <v>3.872047088170675</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.186527880826493</v>
+        <v>-5.204668045009526</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.675422346556037</v>
+        <v>1.668166280882823</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.334288776920149</v>
+        <v>0.2088247119357213</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.95096318935247</v>
+        <v>3.875684750361814</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.205116039548717</v>
+        <v>-5.223256203731751</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.738824088843572</v>
+        <v>1.731568023170358</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.3157006181979236</v>
+        <v>0.190236553213496</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.01064729989556</v>
+        <v>3.935368860904903</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.205414586244753</v>
+        <v>-5.223554750427787</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.735573680983456</v>
+        <v>1.728317615310242</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3157006181979236</v>
+        <v>0.190236553213496</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.007516310713859</v>
+        <v>3.932237871723203</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.104591452554326</v>
+        <v>-5.122731616737359</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.780433829399018</v>
+        <v>1.773177763725805</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3281648336822774</v>
+        <v>0.2027007686978498</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.019525734943863</v>
+        <v>3.944247295953206</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.913810091801919</v>
+        <v>-4.931950255984952</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.856875627178524</v>
+        <v>1.849619561505311</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5189461944346848</v>
+        <v>0.3934821294502572</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.13412380487385</v>
+        <v>4.058845365883194</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.895293237760098</v>
+        <v>-4.913433401943132</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.844119214532849</v>
+        <v>1.836863148859635</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.531876323859893</v>
+        <v>0.4064122588754654</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.121718728266572</v>
+        <v>4.046440289275915</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.87010005325878</v>
+        <v>-4.888240217441814</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.889163424945435</v>
+        <v>1.881907359272221</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5570695083612114</v>
+        <v>0.4316054433767837</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.171801575579421</v>
+        <v>4.096523136588765</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.858045926345818</v>
+        <v>-4.876186090528851</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.887671643612058</v>
+        <v>1.880415577938844</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5691236352741742</v>
+        <v>0.4436595702897466</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.172720619628636</v>
+        <v>4.09744218063798</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.864669173036176</v>
+        <v>-4.882809337219209</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.88690297512005</v>
+        <v>1.879646909446836</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5625003885838158</v>
+        <v>0.4370363235993882</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.170627301798557</v>
+        <v>4.095348862807901</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.761788583507583</v>
+        <v>-4.779928747690616</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.940906236809369</v>
+        <v>1.933650171136156</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6653809781124087</v>
+        <v>0.5399169131279811</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.245206681393595</v>
+        <v>4.169928242402939</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.78523062268767</v>
+        <v>-4.803370786870703</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.951732091310929</v>
+        <v>1.944476025637716</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6653809781124087</v>
+        <v>0.5399169131279811</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.26540935156719</v>
+        <v>4.190130912576533</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.803303130979281</v>
+        <v>-4.821443295162315</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.944503087994285</v>
+        <v>1.937247022321071</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6653809781124087</v>
+        <v>0.5399169131279811</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.26540935156719</v>
+        <v>4.190130912576533</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.034476924855913</v>
+        <v>-5.052617089038947</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.812285484037099</v>
+        <v>1.805029418363885</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6653809781124087</v>
+        <v>0.5399169131279811</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.225661265160657</v>
+        <v>4.15038282617</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.003190904315458</v>
+        <v>-5.021331068498491</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.83182251125022</v>
+        <v>1.824566445577007</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6966669986528641</v>
+        <v>0.5712029336684364</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.25145549648187</v>
+        <v>4.176177057491213</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.850165512202174</v>
+        <v>-4.868305676385207</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.992203667668438</v>
+        <v>1.984947601995224</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8496923907661482</v>
+        <v>0.7242283257817206</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.442441731322744</v>
+        <v>4.367163292332088</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.878472826075444</v>
+        <v>-4.896612990258477</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.168346967027423</v>
+        <v>2.161090901354209</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8496923907661482</v>
+        <v>0.7242283257817206</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.629907956231037</v>
+        <v>4.554629517240381</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.045066051188966</v>
+        <v>-5.063206215371999</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.071112628336096</v>
+        <v>2.063856562662882</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6830991656526257</v>
+        <v>0.5576351006681981</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.499354972517006</v>
+        <v>4.424076533526349</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.872001671806666</v>
+        <v>-4.8901418359897</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.144014782750734</v>
+        <v>2.13675871707752</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6830991656526257</v>
+        <v>0.5576351006681981</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.503031375178724</v>
+        <v>4.427752936188067</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.84275569135097</v>
+        <v>-4.860895855534003</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.153331230056508</v>
+        <v>2.146075164383294</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6830991656526257</v>
+        <v>0.5576351006681981</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.500649430302219</v>
+        <v>4.425370991311562</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69942482753911</v>
+        <v>3.699424827539109</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.852470967689106</v>
+        <v>-4.870611131872139</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.146738358678888</v>
+        <v>2.139482293005674</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.673383889314489</v>
+        <v>0.5479198243300614</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.492113503656972</v>
+        <v>4.416835064666315</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.780224766077503</v>
+        <v>3.87349206810979</v>
       </c>
       <c r="C2057" t="n">
-        <v>4.17304740647968</v>
+        <v>4.113374804035086</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.852470967689106</v>
+        <v>-4.870611131872139</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.146738358678888</v>
+        <v>2.139482293005674</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.673383889314489</v>
+        <v>0.5479198243300614</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.166111203466047</v>
+        <v>4.106438601021454</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240815.xlsx
+++ b/tame_output/ON/bt/strategyON_20240815.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>97.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>429.8%</t>
+          <t>430.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-648.6%</t>
+          <t>-661.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.3%</t>
+          <t>-167.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-422.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-407.4%</t>
+          <t>-365.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-178.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-9.6%</t>
         </is>
       </c>
     </row>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108632</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097814</v>
+        <v>3.341378723097813</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.25757582969015</v>
+        <v>-6.433987709767826</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6154919375028811</v>
+        <v>0.5449271854718107</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094109</v>
+        <v>3.374439043094108</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.600834349333169</v>
+        <v>-6.646616382938449</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4742880947913686</v>
+        <v>0.4559752813492568</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199278</v>
+        <v>3.405960511199277</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.649037166575513</v>
+        <v>-6.694819200180793</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4534118879494322</v>
+        <v>0.4350990745073204</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969586</v>
+        <v>3.424633354969585</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.945698508385711</v>
+        <v>-6.99148054199099</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3385263271545615</v>
+        <v>0.3202135137124498</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.8087317556553376</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.132418216695013</v>
+        <v>-7.178200250300293</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2598121392964372</v>
+        <v>0.2414993258543254</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.8087317556553376</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297741</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.515419605437645</v>
+        <v>-7.561201639042924</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.1065094824778008</v>
+        <v>0.08819666903568901</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.8087317556553376</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317609</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.519906050639033</v>
+        <v>-7.565688084244313</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1072864203686752</v>
+        <v>0.08897360692656342</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8132182008567264</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.879436373143035</v>
+        <v>-7.925218406748314</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.03117540533487517</v>
+        <v>-0.04948821877698695</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8132182008567264</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.929785436597257</v>
+        <v>-7.975567470202536</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.04339901075938668</v>
+        <v>-0.06171182420149846</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8635672643109484</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.027404714018653</v>
+        <v>-8.073186747623932</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.07940497110617617</v>
+        <v>-0.09771778454828794</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9611865417323451</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.081476213527012</v>
+        <v>-8.127258247132291</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.09814001458794719</v>
+        <v>-0.116452828030059</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.015258041240704</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.285734388856875</v>
+        <v>-8.331516422462155</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1743300876012506</v>
+        <v>-0.1926429010433623</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.142896985854693</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.319387227365349</v>
+        <v>-8.365169260970628</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1833086685202039</v>
+        <v>-0.2016214819623157</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.243310353771731</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.2459173956979</v>
+        <v>-8.291699429303179</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1385490343598033</v>
+        <v>-0.156861847801915</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.169840522104282</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.421041813084443</v>
+        <v>-8.466823846689723</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1940435805669036</v>
+        <v>-0.2123563940090154</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.344964939490826</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.655493907098933</v>
+        <v>-8.701275940704212</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2950435830742957</v>
+        <v>-0.3133563965164075</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.344964939490826</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.759868638125379</v>
+        <v>-8.805650671730659</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3434656662588504</v>
+        <v>-0.3617784797009622</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.449339670517272</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.922382103823963</v>
+        <v>-8.968164137429243</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4073552626997277</v>
+        <v>-0.4256680761418394</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.546973100935959</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.048418897192253</v>
+        <v>-9.094200930797532</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4550762514179287</v>
+        <v>-0.4733890648600405</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.521721478126216</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.991347125296322</v>
+        <v>-9.037129158901601</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4282572069731554</v>
+        <v>-0.4465700204152672</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.521721478126216</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.133018967020442</v>
+        <v>-9.178801000625722</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4864011705615452</v>
+        <v>-0.504713984003657</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.521721478126216</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.083428122595608</v>
+        <v>-9.129210156200887</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4515114226267394</v>
+        <v>-0.4698242360688512</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.472130633701382</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.934509788123751</v>
+        <v>-8.980291821729031</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4049952224846796</v>
+        <v>-0.4233080359267913</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.440881042966209</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.685161381615278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.70866463540434</v>
+        <v>-8.754446669009621</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3050780883607063</v>
+        <v>-0.3233909018028189</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.398954367379046</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.584085979066748</v>
+        <v>-8.629868012672029</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2541074812696107</v>
+        <v>-0.2724202947117234</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.398954367379046</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.636981267111034</v>
+        <v>-8.682763300716315</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2726318223252178</v>
+        <v>-0.29094463576733</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.393999021290599</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.564848091823153</v>
+        <v>-8.610630125428434</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2380448479714286</v>
+        <v>-0.2563576614135412</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.393999021290599</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.493481699213506</v>
+        <v>-8.539263732818787</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2192355533214352</v>
+        <v>-0.2375483667635474</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.322632628680952</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.400022665228281</v>
+        <v>-8.445804698833562</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.1917354210402529</v>
+        <v>-0.2100482344823651</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.322632628680952</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.38936948367485</v>
+        <v>-8.435151517280131</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1893087089182539</v>
+        <v>-0.2076215223603666</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.322632628680952</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.291462444998359</v>
+        <v>-8.33724447860364</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1504462084211187</v>
+        <v>-0.1687590218632309</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.254646878820395</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097238</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.267508904022401</v>
+        <v>-8.313290937627682</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1401962858852417</v>
+        <v>-0.1585090993273544</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.230693337844438</v>
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.003448965699604</v>
+        <v>-8.20159743408726</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.04783262671787547</v>
+        <v>-0.1270920140729372</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-1.118999834304015</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.57392334416273</v>
+        <v>2.482503483293305</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.296369342194766</v>
+        <v>-7.494517810582422</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.232212189023759</v>
+        <v>0.1529528016686972</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9666333995216414</v>
+        <v>-1.118999834304015</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.571136310502429</v>
+        <v>2.479716449633004</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.256185043828576</v>
+        <v>-7.454333512216231</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2486295322580765</v>
+        <v>0.1693701449030147</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9264491011554506</v>
+        <v>-1.078815535937824</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.595590513409984</v>
+        <v>2.50417065254056</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.092785172889213</v>
+        <v>-7.290933641276869</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3133563018545784</v>
+        <v>0.2340969144995166</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.7630492302160882</v>
+        <v>-0.9154156649984615</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.692997257194359</v>
+        <v>2.601577396324935</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.859303950659615</v>
+        <v>-7.05745241904727</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4146732195842704</v>
+        <v>0.3354138322292082</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5295680079864896</v>
+        <v>-0.6819344427688629</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.841010419369971</v>
+        <v>2.749590558500546</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.7096375596521</v>
+        <v>-6.907786028039755</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4716475656743171</v>
+        <v>0.3923881783192553</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4366645167439537</v>
+        <v>-0.589030951526327</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.893860303802533</v>
+        <v>2.802440442933109</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.577362086021213</v>
+        <v>-6.775510554408869</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5199252418736986</v>
+        <v>0.4406658545186368</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.304389043113067</v>
+        <v>-0.4567554778954404</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.968593074728092</v>
+        <v>2.877173213858668</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.421623753461471</v>
+        <v>-6.619772221849127</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.585035635585232</v>
+        <v>0.5057762482301702</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1486507105533255</v>
+        <v>-0.3010171453356988</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.064851134951573</v>
+        <v>2.97343127408215</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.336659086732152</v>
+        <v>-6.534807555119807</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6319278435006184</v>
+        <v>0.552668456145557</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.06368604382400589</v>
+        <v>-0.2160524786063792</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.128736276212824</v>
+        <v>3.0373164153434</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.442249076505257</v>
+        <v>-6.640397544892911</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4617159179921582</v>
+        <v>0.3824565306370964</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.1692760335971102</v>
+        <v>-0.3216424683794836</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.937406352749742</v>
+        <v>2.845986491880319</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.374014491879829</v>
+        <v>-6.572162960267484</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5375540937194154</v>
+        <v>0.4582947063643541</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1508607107245742</v>
+        <v>-0.3032271455069476</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.99699988835035</v>
+        <v>2.905580027480926</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.22607445047223</v>
+        <v>-6.424222918859885</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4768511875942876</v>
+        <v>0.3975918002392262</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1305397948160167</v>
+        <v>-0.28290622959839</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.889313515207317</v>
+        <v>2.797893654337893</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.173104928218241</v>
+        <v>-6.371253396605896</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4893250102424047</v>
+        <v>0.4100656228873434</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.2299367073444011</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.912381242306233</v>
+        <v>2.820961381436809</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.007316732257951</v>
+        <v>-6.205465200645605</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5486796765314281</v>
+        <v>0.4694202891763664</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.2299367073444011</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.90542063021114</v>
+        <v>2.814000769341716</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.973953525779182</v>
+        <v>-6.172101994166836</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5764873135040784</v>
+        <v>0.4972279261490171</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.2299367073444011</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.919882984592283</v>
+        <v>2.828463123722859</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.86569438865666</v>
+        <v>-6.063842857044315</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6143230888122821</v>
+        <v>0.5350637014572208</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.07757027256202781</v>
+        <v>-0.2299367073444011</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.914415105051478</v>
+        <v>2.822995244182054</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.742403253839529</v>
+        <v>-5.940551722227184</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6611376367497117</v>
+        <v>0.5818782493946499</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.04572086225510269</v>
+        <v>-0.1066455725272706</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.985887879952333</v>
+        <v>2.894468019082909</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.689706386708238</v>
+        <v>-5.887854855095893</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6899173618395533</v>
+        <v>0.6106579744844916</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.09841772938639387</v>
+        <v>-0.05394870539597946</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.025206978468433</v>
+        <v>2.933787117599008</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.445940944724794</v>
+        <v>-5.644089413112448</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7832042469799818</v>
+        <v>0.70394485962492</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.09841772938639387</v>
+        <v>-0.05394870539597946</v>
       </c>
       <c r="G1917" t="n">
-        <v>3.020987686815483</v>
+        <v>2.929567825946059</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.356165272348322</v>
+        <v>-5.554313740735976</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8212388298505866</v>
+        <v>0.7419794424955248</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.007650739518330563</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.060071667684086</v>
+        <v>2.968651806814661</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.106314878399247</v>
+        <v>-5.304463346786902</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9139210624139187</v>
+        <v>0.8346616750588569</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.007650739518330563</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.052813742667788</v>
+        <v>2.961393881798363</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.930422785931815</v>
+        <v>-5.128571254319469</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9878770229215401</v>
+        <v>0.9086176355664786</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1600171743007039</v>
+        <v>0.007650739518330563</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.056412866188436</v>
+        <v>2.964993005319012</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.758976322909351</v>
+        <v>-4.957124791297006</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.069783114185079</v>
+        <v>0.9905237268300175</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.331463637323167</v>
+        <v>0.1790972025407937</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.172608250056468</v>
+        <v>3.081188389187044</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.67895403580023</v>
+        <v>-4.877102504187885</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.100812506645025</v>
+        <v>1.021553119289963</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.411485924432288</v>
+        <v>0.2591194896499147</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.219642099938238</v>
+        <v>3.128222239068813</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.615318293566296</v>
+        <v>-4.813466761953951</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.130961604592916</v>
+        <v>1.051702217237854</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.3227552318838492</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.262518346332915</v>
+        <v>3.171098485463491</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.521620975349901</v>
+        <v>-4.719769443737555</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.149634790663269</v>
+        <v>1.070375403308208</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4751216666662225</v>
+        <v>0.3227552318838492</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.243712605116711</v>
+        <v>3.152292744247287</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.53212359841519</v>
+        <v>-4.730272066802844</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.147176818062031</v>
+        <v>1.06791743070697</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.3122526088185603</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.239154107902415</v>
+        <v>3.147734247032991</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367678</v>
+        <v>3.821593509367677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.459881030243995</v>
+        <v>-4.65802949863165</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.180003159165329</v>
+        <v>1.100743771810268</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4646190436009336</v>
+        <v>0.3122526088185603</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.243083421737235</v>
+        <v>3.151663560867811</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.44216734336613</v>
+        <v>-4.640315811753784</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.187767217833815</v>
+        <v>1.108507830478754</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.3154339377154771</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.245670802992725</v>
+        <v>3.154250942123301</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.333362457886403</v>
+        <v>-4.531510926274057</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.228287243245699</v>
+        <v>1.149027855890638</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4678003724978504</v>
+        <v>0.3154339377154771</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.242668874212719</v>
+        <v>3.151249013343295</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.113341659849392</v>
+        <v>-4.311490128237047</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.317874599471118</v>
+        <v>1.238615212116057</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.4566537827834574</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.328979818264121</v>
+        <v>3.237559957394697</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.980473970786114</v>
+        <v>-4.178622439173769</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.386915857898253</v>
+        <v>1.307656470543191</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6090202175658307</v>
+        <v>0.4566537827834574</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.344874001065945</v>
+        <v>3.25345414019652</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.860300887421615</v>
+        <v>-4.05844935580927</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.436130935684354</v>
+        <v>1.356871548329292</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7291933009303296</v>
+        <v>0.5768268661479563</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.418123695524946</v>
+        <v>3.326703834655522</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.725047526091638</v>
+        <v>-3.923195994479293</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.500320382777785</v>
+        <v>1.421060995422723</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8644466622603068</v>
+        <v>0.7120802274779334</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.509363814884372</v>
+        <v>3.417943954014948</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.78492235344933</v>
+        <v>-3.983070821836986</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.462407943236134</v>
+        <v>1.383148555881072</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.6522054001202413</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.459476409871182</v>
+        <v>3.368056549001758</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.665102122538493</v>
+        <v>-3.863250590926148</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.525625204834677</v>
+        <v>1.446365817479615</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8045718349026146</v>
+        <v>0.6522054001202413</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.474765579105391</v>
+        <v>3.383345718235967</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.667571829000299</v>
+        <v>-3.865720297387954</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.432281521572396</v>
+        <v>1.353022134217334</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8021021284408085</v>
+        <v>0.6497356936584351</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.380927954550749</v>
+        <v>3.289508093681325</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.735942015324309</v>
+        <v>-3.934090483711964</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.324195308528094</v>
+        <v>1.244935921173032</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.65901139269465</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.305755235457779</v>
+        <v>3.214335374588355</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.749730068171355</v>
+        <v>-3.947878536559011</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.309116796021166</v>
+        <v>1.229857408666104</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.65901139269465</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.29619194408967</v>
+        <v>3.204772083220246</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.805250144063945</v>
+        <v>-4.0033986124516</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.423939602356333</v>
+        <v>1.344680215001271</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.65901139269465</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.433222780781873</v>
+        <v>3.341802919912449</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.629775884271476</v>
+        <v>-3.827924352659131</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.498696538265108</v>
+        <v>1.419437150910047</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.65901139269465</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.43779001277366</v>
+        <v>3.346370151904237</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.740712136912724</v>
+        <v>-3.93886060530038</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.430064065969816</v>
+        <v>1.350804678614754</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8113778274770235</v>
+        <v>0.65901139269465</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.413532041534868</v>
+        <v>3.322112180665444</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.707048591440442</v>
+        <v>-3.905197059828098</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.372067797560178</v>
+        <v>1.292808410205117</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.6926749381669319</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.362268482219687</v>
+        <v>3.270848621350262</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.647195972236719</v>
+        <v>-3.845344440624375</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.4061812316738</v>
+        <v>1.326921844318738</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.6926749381669319</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.372440868651819</v>
+        <v>3.281021007782395</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.560952509210342</v>
+        <v>-3.759100977597997</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.435624887458211</v>
+        <v>1.35636550010315</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8450413729493054</v>
+        <v>0.6926749381669319</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.367387139225679</v>
+        <v>3.275967278356255</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.606259328609322</v>
+        <v>-3.804407796996977</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.409277935143145</v>
+        <v>1.330018547788083</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.6518647751577011</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.334676816864667</v>
+        <v>3.243256955995242</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.635292433311623</v>
+        <v>-3.833440901699279</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.398216566295326</v>
+        <v>1.318957178940264</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.8042312099400746</v>
+        <v>0.6518647751577011</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.335228689897768</v>
+        <v>3.243808829028344</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.542481951860764</v>
+        <v>-3.74063042024842</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.364613450767035</v>
+        <v>1.285354063411973</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8970416913909339</v>
+        <v>0.7446752566085605</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.320187670659649</v>
+        <v>3.228767809790225</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.586871421190192</v>
+        <v>-3.785019889577847</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.348731138959865</v>
+        <v>1.269471751604803</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8526522220615063</v>
+        <v>0.7002857872791328</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.295427464986593</v>
+        <v>3.204007604117169</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.703413026295534</v>
+        <v>-3.90156149468319</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.297190205429451</v>
+        <v>1.217930818074389</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.5837441821737901</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.220578210435111</v>
+        <v>3.129158349565687</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.743337120878106</v>
+        <v>-3.941485589265762</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.28671186342709</v>
+        <v>1.207452476072028</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7361106169561635</v>
+        <v>0.5837441821737901</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.226069506265778</v>
+        <v>3.134649645396354</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.771117518779459</v>
+        <v>-3.969265987167115</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.287096906035087</v>
+        <v>1.207837518680025</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7083302190548104</v>
+        <v>0.555963784272437</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.220898469293505</v>
+        <v>3.129478608424081</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.889498191509598</v>
+        <v>-4.087646659897253</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.078100356943685</v>
+        <v>0.9988409695886236</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.4887459321214608</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.018923478003573</v>
+        <v>2.927503617134149</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.998112269952929</v>
+        <v>-4.196260738340584</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.154804386285558</v>
+        <v>1.075544998930497</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.4887459321214608</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.139073138722778</v>
+        <v>3.047653277853354</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.962703231704786</v>
+        <v>-4.160851700092441</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.183481027687139</v>
+        <v>1.104221640332077</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6411123669038342</v>
+        <v>0.4887459321214608</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.153586164825101</v>
+        <v>3.062166303955677</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.924319569146635</v>
+        <v>-4.12246803753429</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.196253934052768</v>
+        <v>1.116994546697706</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.527129594679612</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.174035803702361</v>
+        <v>3.082615942832937</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.747203239111469</v>
+        <v>-3.945351707499124</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.263829494912136</v>
+        <v>1.184570107557074</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6794960294619854</v>
+        <v>0.527129594679612</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.170764832547663</v>
+        <v>3.079344971678239</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.792295483945014</v>
+        <v>-3.99044395233267</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.246475988740631</v>
+        <v>1.167216601385569</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6175999862925956</v>
+        <v>0.4652335515102222</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.134310598407942</v>
+        <v>3.042890737538518</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.799600631621227</v>
+        <v>-3.811068531093902</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.23734090497656</v>
+        <v>1.232753745187491</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6489126794788868</v>
+        <v>0.6220103096809408</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.146885189626131</v>
+        <v>3.130743767747363</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.844614845141833</v>
+        <v>-3.856082744614508</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.200142674899908</v>
+        <v>1.195555515110838</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6185637841642821</v>
+        <v>0.5916614143663362</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.109483307768958</v>
+        <v>3.09334188589019</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.111619355414268</v>
+        <v>-4.123087254886943</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.099032433129879</v>
+        <v>1.094445273340809</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4242007461213336</v>
+        <v>0.3972983763233877</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.998557047282135</v>
+        <v>2.982415625403367</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.212817136851441</v>
+        <v>-4.224285036324116</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.057757242451512</v>
+        <v>1.053170082662442</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3557919325760144</v>
+        <v>0.3288895627780685</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.956715681051445</v>
+        <v>2.940574259172677</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.206306170237128</v>
+        <v>-4.217774069709804</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.057961590651553</v>
+        <v>1.053374430862484</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3557919325760144</v>
+        <v>0.3288895627780685</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.954315642605761</v>
+        <v>2.938174220726994</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.187268042529831</v>
+        <v>-4.198735942002506</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.062101560942717</v>
+        <v>1.057514401153647</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2976083212448198</v>
+        <v>0.2707059514468739</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.915930195015289</v>
+        <v>2.899788773136522</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.239783844804651</v>
+        <v>-4.251251744277327</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.160389641666979</v>
+        <v>1.15580248187791</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2976083212448198</v>
+        <v>0.2707059514468739</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.03522459664948</v>
+        <v>3.019083174770712</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.253650606138569</v>
+        <v>-4.265118505611245</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.155676266119546</v>
+        <v>1.151089106330476</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2597504045109969</v>
+        <v>0.232848034713051</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.01334317559532</v>
+        <v>2.997201753716552</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.208846434598639</v>
+        <v>-4.220314334071315</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.179606465132444</v>
+        <v>1.175019305343374</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2597504045109969</v>
+        <v>0.232848034713051</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.019351705992245</v>
+        <v>3.003210284113478</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.061103464363637</v>
+        <v>-4.072571363836312</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.136653874503644</v>
+        <v>1.132066714714574</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4275577617458801</v>
+        <v>0.4006553919479341</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.017986341610375</v>
+        <v>3.001844919731607</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181166</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.144924685638335</v>
+        <v>-4.156392585111011</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.105919007525246</v>
+        <v>1.101331847736176</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4275577617458801</v>
+        <v>0.4006553919479341</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.020779963141856</v>
+        <v>3.004638541263088</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.138771979585551</v>
+        <v>-4.150239879058226</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.109042438338018</v>
+        <v>1.104455278548948</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4337104677986643</v>
+        <v>0.4068080980007184</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.025133935165185</v>
+        <v>3.008992513286417</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.155581277736053</v>
+        <v>-4.167049177208728</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.101399195817927</v>
+        <v>1.096812036028858</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4169011696481627</v>
+        <v>0.3899987998502168</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.014128833014994</v>
+        <v>2.997987411136227</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.09328327895993</v>
+        <v>-4.104751178432606</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.192653949125197</v>
+        <v>1.188066789336127</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4621954339226048</v>
+        <v>0.4352930641246588</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.10764094537648</v>
+        <v>3.091499523497713</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.891493081294772</v>
+        <v>-3.902960980767448</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.075662029905387</v>
+        <v>1.071074870116318</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6602136260917592</v>
+        <v>0.6333112562938132</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.0287438623921</v>
+        <v>3.012602440513332</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.942379793980967</v>
+        <v>-3.953847693453643</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.125597577153085</v>
+        <v>1.121010417364015</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6093269134055646</v>
+        <v>0.5824245436076187</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.068502067102558</v>
+        <v>3.052360645223791</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.85576905133116</v>
+        <v>-3.867236950803835</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.174869610329051</v>
+        <v>1.170282450539982</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6879526446107228</v>
+        <v>0.661050274812777</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.130305241941697</v>
+        <v>3.114163820062929</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.915978349336444</v>
+        <v>-3.92744624880912</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.149321871951609</v>
+        <v>1.144734712162539</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6277433466054383</v>
+        <v>0.6008409768074925</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.092715643963198</v>
+        <v>3.07657422208443</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.839556302904517</v>
+        <v>-3.851024202377193</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.178382308564309</v>
+        <v>1.173795148775239</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6277433466054383</v>
+        <v>0.6008409768074925</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.091207262003127</v>
+        <v>3.075065840124359</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.795183171265949</v>
+        <v>-3.806651070738624</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.195994428655172</v>
+        <v>1.191407268866102</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6721164782440069</v>
+        <v>0.6452141084460611</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.117694008421704</v>
+        <v>3.101552586542936</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.817663522124834</v>
+        <v>-3.829131421597509</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.181396082450209</v>
+        <v>1.176808922661139</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6721164782440069</v>
+        <v>0.6452141084460611</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.112087802560294</v>
+        <v>3.095946380681527</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.770007791563778</v>
+        <v>-3.781475691036453</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.206840131702436</v>
+        <v>1.202252971913366</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7197722088050625</v>
+        <v>0.6928698390071167</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.147062997924732</v>
+        <v>3.130921576045965</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.669489633065023</v>
+        <v>-3.680957532537699</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.251939768476662</v>
+        <v>1.247352608687593</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8202903673038171</v>
+        <v>0.7933879975058713</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.21226626639871</v>
+        <v>3.196124844519942</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.653584303632671</v>
+        <v>-3.665052203105346</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.245056572725476</v>
+        <v>1.240469412936406</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7411777065945782</v>
+        <v>0.7142753367966324</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.151553342449039</v>
+        <v>3.135411920570271</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.608745902024272</v>
+        <v>-3.620213801496948</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.267089635979463</v>
+        <v>1.262502476190394</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7457211395394476</v>
+        <v>0.7188187697415018</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.158377104826589</v>
+        <v>3.142235682947821</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.628244358266281</v>
+        <v>-3.639712257738956</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.263451193113738</v>
+        <v>1.258864033324668</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6976364982595433</v>
+        <v>0.6707341284615975</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.133687259689725</v>
+        <v>3.117545837810957</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.58404152118038</v>
+        <v>-3.595509420653056</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.287011930475936</v>
+        <v>1.282424770686866</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7418393353454438</v>
+        <v>0.714936965547498</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.166088564469102</v>
+        <v>3.149947142590334</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.591601187017427</v>
+        <v>-3.603069086490103</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.282398064610364</v>
+        <v>1.277810904821294</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7966427393552631</v>
+        <v>0.7697403695573173</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.197380607344241</v>
+        <v>3.181239185465473</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.433309769478155</v>
+        <v>-3.44477766895083</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.396962396809113</v>
+        <v>1.392375237020043</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7966427393552631</v>
+        <v>0.7697403695573173</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.248628372527281</v>
+        <v>3.232486950648513</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.225667765843679</v>
+        <v>-3.237135665316354</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.478459902857157</v>
+        <v>1.473872743068087</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.004284742989739</v>
+        <v>0.9773823731917934</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.37165427930222</v>
+        <v>3.355512857423452</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.174635673121151</v>
+        <v>-3.186103572593826</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.493820968184438</v>
+        <v>1.489233808395368</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.055316835712267</v>
+        <v>1.028414465914322</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.397221763174006</v>
+        <v>3.381080341295239</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404848</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.109411491993945</v>
+        <v>-3.12087939146662</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.537098044728025</v>
+        <v>1.532510884938955</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.120541016839473</v>
+        <v>1.093638647041527</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.453543675943035</v>
+        <v>3.437402254064267</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.071984471922811</v>
+        <v>-3.083452371395487</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.548029825055759</v>
+        <v>1.543442665266689</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.125792554868655</v>
+        <v>1.098890185070709</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.452655571059824</v>
+        <v>3.436514149181057</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.092096127957519</v>
+        <v>-3.103564027430195</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.541241954973116</v>
+        <v>1.536654795184046</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.136819899866074</v>
+        <v>1.109917530068128</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.460528770389516</v>
+        <v>3.444387348510748</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.038351313530315</v>
+        <v>-3.04981921300299</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.723297651765209</v>
+        <v>1.718710491976139</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.146883209306536</v>
+        <v>1.11998083950859</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.627124527075004</v>
+        <v>3.610983105196236</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957619</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.963569052505302</v>
+        <v>-2.975036951977978</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.873323465393031</v>
+        <v>1.868736305603961</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.221665470331549</v>
+        <v>1.194763100533603</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.792106792907829</v>
+        <v>3.775965371029061</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.937484968241494</v>
+        <v>-2.94895286771417</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.875465075112413</v>
+        <v>1.870877915323343</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.221665470331549</v>
+        <v>1.194763100533603</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.783814768921688</v>
+        <v>3.76767334704292</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.849607055132374</v>
+        <v>-2.861074954605049</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.908809435939841</v>
+        <v>1.904222276150771</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.3375911127549</v>
+        <v>1.310688742956954</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.851563349959478</v>
+        <v>3.83542192808071</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.84071459373909</v>
+        <v>-2.852182493211766</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.929920826223945</v>
+        <v>1.925333666434875</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.3375911127549</v>
+        <v>1.310688742956954</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.869117755686269</v>
+        <v>3.852976333807502</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.009190710708968</v>
+        <v>-3.020658610181643</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.854385426840578</v>
+        <v>1.849798267051508</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.309643277038319</v>
+        <v>1.282740907240373</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.844204101660905</v>
+        <v>3.828062679782137</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.562934518079528</v>
+        <v>-2.574402417552204</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.014157601080216</v>
+        <v>2.009570441291146</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.214924607368686</v>
+        <v>1.188022237570741</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.768642597046987</v>
+        <v>3.752501175168219</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.540213414396375</v>
+        <v>-2.551681313869051</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.013910065050382</v>
+        <v>2.009322905261312</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.214924607368686</v>
+        <v>1.188022237570741</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.759306619543891</v>
+        <v>3.743165197665124</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.669415227690418</v>
+        <v>-2.680883127163094</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.121135465583934</v>
+        <v>2.116548305794864</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.085722794074644</v>
+        <v>1.058820424276698</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.840691657418635</v>
+        <v>3.824550235539868</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.824196234468674</v>
+        <v>-2.835664133941349</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.096300885366278</v>
+        <v>2.091713725577208</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.052355120020168</v>
+        <v>1.025452750222222</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.857748875479596</v>
+        <v>3.841607453600829</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.8171415442535</v>
+        <v>-2.828609443726176</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.095798117441892</v>
+        <v>2.091210957652823</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.059409810235342</v>
+        <v>1.032507440437396</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.858657045598245</v>
+        <v>3.842515623719478</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331111</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.790190319927012</v>
+        <v>-2.801658219399688</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.116584760817229</v>
+        <v>2.111997601028159</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.074290156263061</v>
+        <v>1.047387786465115</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.877591406859619</v>
+        <v>3.861449984980851</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.926143327983328</v>
+        <v>-2.937611227456004</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.246306689739662</v>
+        <v>2.241719529950593</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.074290156263061</v>
+        <v>1.047387786465115</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.061694539004578</v>
+        <v>4.04555311712581</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.9485514457882</v>
+        <v>-2.960019345260876</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.229460137520707</v>
+        <v>2.224872977731637</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.074290156263061</v>
+        <v>1.047387786465115</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.053811233907571</v>
+        <v>4.037669812028803</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.976775681365801</v>
+        <v>-2.988243580838476</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.220224442839304</v>
+        <v>2.215637283050234</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.092266908714369</v>
+        <v>1.065364538916424</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.066651284927994</v>
+        <v>4.050509863049227</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.986216607254331</v>
+        <v>-2.997684506727006</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.27270179020574</v>
+        <v>2.26811463041667</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.214694026257761</v>
+        <v>1.187791656459815</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.196361273175876</v>
+        <v>4.180219851297108</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.038490214589972</v>
+        <v>-3.049958114062647</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.254683441816784</v>
+        <v>2.250096282027714</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.16242041892212</v>
+        <v>1.135518049124174</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.167888203319792</v>
+        <v>4.151746781441025</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.114820192190878</v>
+        <v>-3.126288091663553</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.222263263670197</v>
+        <v>2.217676103881127</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.16242041892212</v>
+        <v>1.135518049124174</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.166000016213567</v>
+        <v>4.1498585943348</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.317073912515231</v>
+        <v>-3.328541811987907</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.136182005143318</v>
+        <v>2.131594845354248</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9601666985977662</v>
+        <v>0.9332643287998204</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.039468013621818</v>
+        <v>4.02332659174305</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.478642338042486</v>
+        <v>-3.490110237515162</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.069988645142568</v>
+        <v>2.065401485353498</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8333837747998868</v>
+        <v>0.806481405001941</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.961832269553242</v>
+        <v>3.945690847674475</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.610943630140039</v>
+        <v>-3.622411529612715</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.030141535169465</v>
+        <v>2.025554375380395</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8333837747998868</v>
+        <v>0.806481405001941</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.97490567641916</v>
+        <v>3.958764254540394</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.79681194097927</v>
+        <v>-3.808279840451945</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.947799407616713</v>
+        <v>1.943212247827643</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6748181814799391</v>
+        <v>0.6479158116819933</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.871771517210132</v>
+        <v>3.855630095331365</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.824712728088743</v>
+        <v>-3.836180627561418</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.935163133899926</v>
+        <v>1.930575974110856</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6402212573370043</v>
+        <v>0.6133188875390585</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.849537403851373</v>
+        <v>3.833395981972606</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.947238830791636</v>
+        <v>-3.958706730264312</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.882917136795967</v>
+        <v>1.878329977006897</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5176951546341104</v>
+        <v>0.4907927848361646</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.772786186206836</v>
+        <v>3.756644764328068</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.177753326977225</v>
+        <v>-4.1892212264499</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.857417297912235</v>
+        <v>1.852830138123165</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2871806584485217</v>
+        <v>0.2602782886505759</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.701183448085986</v>
+        <v>3.685042026207219</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.434474144972049</v>
+        <v>-4.445942044444724</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.895040689716152</v>
+        <v>1.890453529927083</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1787660843047069</v>
+        <v>0.1518637145067611</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.776446422601544</v>
+        <v>3.760305000722777</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.66828900423709</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.58846056274819</v>
+        <v>-4.599928462220864</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.902426391751336</v>
+        <v>1.897839231962267</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1787660843047069</v>
+        <v>0.1518637145067611</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.845426691747184</v>
+        <v>3.829285269868417</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.537938658920524</v>
+        <v>-4.549406558393199</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.908686355402523</v>
+        <v>1.904099195613454</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1787660843047069</v>
+        <v>0.1518637145067611</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.831477893867305</v>
+        <v>3.815336471988537</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65633273360975</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.790413812928248</v>
+        <v>-4.801881712400923</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.819566782854848</v>
+        <v>1.814979623065778</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1787660843047069</v>
+        <v>0.1518637145067611</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.843348382922719</v>
+        <v>3.827206961043951</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.08330956940766</v>
+        <v>-5.094777468880335</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.703619014782026</v>
+        <v>1.699031854992957</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1787660843047069</v>
+        <v>0.1518637145067611</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.844558917441663</v>
+        <v>3.828417495562895</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.269973697542468</v>
+        <v>-5.281441597015143</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.633075105755425</v>
+        <v>1.628487945966355</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.152027113480147</v>
+        <v>0.1251247436822012</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.832637277174248</v>
+        <v>3.816495855295481</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.547938093125742</v>
+        <v>-5.559405992598417</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.516967200258305</v>
+        <v>1.512380040469235</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.06240737919466272</v>
+        <v>0.03550500939671691</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.773943289339147</v>
+        <v>3.75780186746038</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.664905785764633</v>
+        <v>-5.676373685237308</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.632384179901793</v>
+        <v>1.627797020112723</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.06240737919466272</v>
+        <v>0.03550500939671691</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.936147346038191</v>
+        <v>3.920005924159423</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.749623727985586</v>
+        <v>-5.761091627458261</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.593343640977225</v>
+        <v>1.588756481188156</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.02270864973338366</v>
+        <v>-0.04961101953132946</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.879924366645177</v>
+        <v>3.86378294476641</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.831558546254469</v>
+        <v>-5.843026445727144</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.570799131238163</v>
+        <v>1.566211971449094</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.03264339532046384</v>
+        <v>-0.05954576511840964</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.884192936861421</v>
+        <v>3.868051514982653</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.933534668502877</v>
+        <v>-5.945002567975552</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.538934320794703</v>
+        <v>1.534347161005633</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1346195175688714</v>
+        <v>-0.1615218873668172</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.831932901968278</v>
+        <v>3.815791480089511</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.823528385025655</v>
+        <v>-5.83499628449833</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.575089721429767</v>
+        <v>1.570502561640697</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1114149456515962</v>
+        <v>-0.138317315449542</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.838008532362819</v>
+        <v>3.821867110484051</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.68046880928473</v>
+        <v>-5.691936708757405</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.636563562448111</v>
+        <v>1.631976402659042</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1034015190616169</v>
+        <v>-0.1303038888595627</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.847066599038781</v>
+        <v>3.830925177160013</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.379022083812893</v>
+        <v>-5.390489983285567</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.764403135519382</v>
+        <v>1.759815975730313</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1980452064102203</v>
+        <v>0.1711428366122745</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.035195517204419</v>
+        <v>4.019054095325652</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.403612328048077</v>
+        <v>-5.415080227520751</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.755538215578019</v>
+        <v>1.75095105578895</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1980452064102203</v>
+        <v>0.1711428366122745</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.03616669495713</v>
+        <v>4.020025273078362</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.352573952041556</v>
+        <v>-5.364041851514231</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.776796470360382</v>
+        <v>1.772209310571313</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1980452064102203</v>
+        <v>0.1711428366122745</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.037009599336884</v>
+        <v>4.020868177458118</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.311434657174925</v>
+        <v>-5.3229025566476</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.81229028718118</v>
+        <v>1.807703127392111</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2391845012768511</v>
+        <v>0.2122821314789053</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.080731275131009</v>
+        <v>4.064589853252241</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.200828517095323</v>
+        <v>-5.212296416567998</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.672716739336956</v>
+        <v>1.668129579547886</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3497906413564532</v>
+        <v>0.3228882715585074</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.963278955302704</v>
+        <v>3.947137533423937</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.331409251626166</v>
+        <v>-5.342877151098841</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.623986489598582</v>
+        <v>1.619399329809513</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2192099068256106</v>
+        <v>0.1923075370276648</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.888432558658163</v>
+        <v>3.872291136779395</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.166912917435204</v>
+        <v>-5.178380816907879</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.674211842351049</v>
+        <v>1.66962468256198</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2192099068256106</v>
+        <v>0.1923075370276648</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.872859377734245</v>
+        <v>3.856717955855478</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.194282850119636</v>
+        <v>-5.205750749592311</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.662451579713706</v>
+        <v>1.657864419924637</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2192099068256106</v>
+        <v>0.1923075370276648</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.872047088170675</v>
+        <v>3.855905666291907</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.204668045009526</v>
+        <v>-5.2161359444822</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.668166280882823</v>
+        <v>1.663579121093753</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.2088247119357213</v>
+        <v>0.1819223421377755</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.875684750361814</v>
+        <v>3.859543328483046</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.223256203731751</v>
+        <v>-5.234724103204425</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.731568023170358</v>
+        <v>1.726980863381288</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.190236553213496</v>
+        <v>0.1633341834155502</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.935368860904903</v>
+        <v>3.919227439026137</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.223554750427787</v>
+        <v>-5.235022649900461</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.728317615310242</v>
+        <v>1.723730455521173</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.190236553213496</v>
+        <v>0.1633341834155502</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.932237871723203</v>
+        <v>3.916096449844435</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.122731616737359</v>
+        <v>-5.128549796808271</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.773177763725805</v>
+        <v>1.77085049169744</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2027007686978498</v>
+        <v>0.2351568824064776</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.944247295953206</v>
+        <v>3.963720964178383</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.931950255984952</v>
+        <v>-4.937768436055864</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.849619561505311</v>
+        <v>1.847292289476946</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.3934821294502572</v>
+        <v>0.425938243158885</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.058845365883194</v>
+        <v>4.07831903410837</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.913433401943132</v>
+        <v>-4.919251582014043</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.836863148859635</v>
+        <v>1.834535876831271</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4064122588754654</v>
+        <v>0.4388683725840932</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.046440289275915</v>
+        <v>4.065913957501092</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.888240217441814</v>
+        <v>-4.894058397512725</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.881907359272221</v>
+        <v>1.879580087243857</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4316054433767837</v>
+        <v>0.4640615570854115</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.096523136588765</v>
+        <v>4.115996804813941</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.876186090528851</v>
+        <v>-4.882004270599762</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.880415577938844</v>
+        <v>1.87808830591048</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4436595702897466</v>
+        <v>0.4761156839983743</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.09744218063798</v>
+        <v>4.116915848863156</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.882809337219209</v>
+        <v>-4.888627517290121</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.879646909446836</v>
+        <v>1.877319637418472</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4370363235993882</v>
+        <v>0.469492437308016</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.095348862807901</v>
+        <v>4.114822531033077</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.779928747690616</v>
+        <v>-4.785746927761528</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.933650171136156</v>
+        <v>1.931322899107792</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5399169131279811</v>
+        <v>0.572373026836609</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.169928242402939</v>
+        <v>4.189401910628116</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.803370786870703</v>
+        <v>-4.809188966941615</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.944476025637716</v>
+        <v>1.942148753609351</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5399169131279811</v>
+        <v>0.572373026836609</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.190130912576533</v>
+        <v>4.20960458080171</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.821443295162315</v>
+        <v>-4.827261475233226</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.937247022321071</v>
+        <v>1.934919750292707</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5399169131279811</v>
+        <v>0.572373026836609</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.190130912576533</v>
+        <v>4.20960458080171</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.052617089038947</v>
+        <v>-5.058435269109858</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.805029418363885</v>
+        <v>1.802702146335521</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5399169131279811</v>
+        <v>0.572373026836609</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.15038282617</v>
+        <v>4.169856494395177</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.021331068498491</v>
+        <v>-5.027149248569403</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.824566445577007</v>
+        <v>1.822239173548643</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.5712029336684364</v>
+        <v>0.6036590473770643</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.176177057491213</v>
+        <v>4.19565072571639</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.868305676385207</v>
+        <v>-4.874123856456118</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.984947601995224</v>
+        <v>1.98262032996686</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.7242283257817206</v>
+        <v>0.7566844394903485</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.367163292332088</v>
+        <v>4.386636960557264</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.896612990258477</v>
+        <v>-4.902431170329389</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.161090901354209</v>
+        <v>2.158763629325845</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.7242283257817206</v>
+        <v>0.7566844394903485</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.554629517240381</v>
+        <v>4.574103185465557</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.063206215371999</v>
+        <v>-5.069024395442911</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.063856562662882</v>
+        <v>2.061529290634518</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.5576351006681981</v>
+        <v>0.590091214376826</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.424076533526349</v>
+        <v>4.443550201751526</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.8901418359897</v>
+        <v>-4.895960016060611</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.13675871707752</v>
+        <v>2.134431445049156</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.5576351006681981</v>
+        <v>0.590091214376826</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.427752936188067</v>
+        <v>4.447226604413244</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.860895855534003</v>
+        <v>-4.866714035604915</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.146075164383294</v>
+        <v>2.14374789235493</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.5576351006681981</v>
+        <v>0.590091214376826</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.425370991311562</v>
+        <v>4.444844659536739</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.870611131872139</v>
+        <v>-4.873471457531876</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.139482293005674</v>
+        <v>2.13833816274178</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5479198243300614</v>
+        <v>0.5833337924498644</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.416835064666315</v>
+        <v>4.438083445538196</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.87349206810979</v>
+        <v>3.865781134771164</v>
       </c>
       <c r="C2057" t="n">
-        <v>4.113374804035086</v>
+        <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.870611131872139</v>
+        <v>-4.999439551001559</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.139482293005674</v>
+        <v>2.089379727497141</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5479198243300614</v>
+        <v>0.4573656989801811</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.106438601021454</v>
+        <v>4.363931391599621</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240815.xlsx
+++ b/tame_output/ON/bt/strategyON_20240815.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>56.9%</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.2%</t>
+          <t>430.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-661.5%</t>
+          <t>-650.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.3%</t>
+          <t>-162.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-422.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-365.2%</t>
+          <t>-324.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-178.3%</t>
+          <t>-165.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-2.2%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097813</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094108</v>
+        <v>3.374439043094109</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.646616382938449</v>
+        <v>-6.777246229410845</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4559752813492568</v>
+        <v>0.4037233427602986</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199277</v>
+        <v>3.405960511199278</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.694819200180793</v>
+        <v>-6.825449046653189</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4350990745073204</v>
+        <v>0.3828471359183618</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969585</v>
+        <v>3.424633354969586</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.99148054199099</v>
+        <v>-7.122110388463386</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3202135137124498</v>
+        <v>0.2679615751234912</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.8087317556553376</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.178200250300293</v>
+        <v>-7.308830096772689</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2414993258543254</v>
+        <v>0.1892473872653668</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.8087317556553376</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.561201639042924</v>
+        <v>-7.69183148551532</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.08819666903568901</v>
+        <v>0.03594473044673041</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.8087317556553376</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.565688084244313</v>
+        <v>-7.696317930716709</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.08897360692656342</v>
+        <v>0.03672166833760526</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8132182008567264</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.925218406748314</v>
+        <v>-8.055848253220711</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04948821877698695</v>
+        <v>-0.1017401573659455</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8132182008567264</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.975567470202536</v>
+        <v>-8.106197316674933</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.06171182420149846</v>
+        <v>-0.1139637627904571</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8635672643109484</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.073186747623932</v>
+        <v>-8.203816594096329</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.09771778454828794</v>
+        <v>-0.1499697231372465</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9611865417323451</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.127258247132291</v>
+        <v>-8.257888093604688</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.116452828030059</v>
+        <v>-0.168704766619018</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.015258041240704</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.331516422462155</v>
+        <v>-8.462146268934552</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1926429010433623</v>
+        <v>-0.2448948396323209</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.142896985854693</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.365169260970628</v>
+        <v>-8.495799107443025</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2016214819623157</v>
+        <v>-0.2538734205512743</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.243310353771731</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.291699429303179</v>
+        <v>-8.422329275775576</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.156861847801915</v>
+        <v>-0.2091137863908736</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.169840522104282</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.466823846689723</v>
+        <v>-8.597453693162119</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2123563940090154</v>
+        <v>-0.264608332597974</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.344964939490826</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.701275940704212</v>
+        <v>-8.831905787176609</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3133563965164075</v>
+        <v>-0.3656083351053661</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.344964939490826</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.805650671730659</v>
+        <v>-8.936280518203056</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3617784797009622</v>
+        <v>-0.4140304182899208</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.449339670517272</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.968164137429243</v>
+        <v>-9.09879398390164</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4256680761418394</v>
+        <v>-0.477920014730798</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.546973100935959</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.094200930797532</v>
+        <v>-9.224830777269929</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4733890648600405</v>
+        <v>-0.5256410034489991</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.521721478126216</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.037129158901601</v>
+        <v>-9.167759005373998</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4465700204152672</v>
+        <v>-0.4988219590042262</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.521721478126216</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.178801000625722</v>
+        <v>-9.309430847098119</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.504713984003657</v>
+        <v>-0.556965922592616</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.521721478126216</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.129210156200887</v>
+        <v>-9.259840002673284</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4698242360688512</v>
+        <v>-0.5220761746578098</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.472130633701382</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.980291821729031</v>
+        <v>-9.110921668201428</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4233080359267913</v>
+        <v>-0.4755599745157504</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.440881042966209</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.754446669009621</v>
+        <v>-8.885076515482016</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3233909018028189</v>
+        <v>-0.3756428403917771</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.398954367379046</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.629868012672029</v>
+        <v>-8.760497859144424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.2724202947117234</v>
+        <v>-0.3246722333006811</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.398954367379046</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.682763300716315</v>
+        <v>-8.813393147188711</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.29094463576733</v>
+        <v>-0.3431965743562881</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.393999021290599</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.610630125428434</v>
+        <v>-8.741259971900829</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2563576614135412</v>
+        <v>-0.3086096000024994</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.393999021290599</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.539263732818787</v>
+        <v>-8.669893579291182</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2375483667635474</v>
+        <v>-0.2898003053525056</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.322632628680952</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.445804698833562</v>
+        <v>-8.576434545305958</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2100482344823651</v>
+        <v>-0.2623001730713233</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.322632628680952</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.435151517280131</v>
+        <v>-8.565781363752526</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2076215223603666</v>
+        <v>-0.2598734609493243</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.322632628680952</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.33724447860364</v>
+        <v>-8.467874325076036</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1687590218632309</v>
+        <v>-0.221010960452189</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.254646878820395</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.313290937627682</v>
+        <v>-8.443920784100078</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1585090993273544</v>
+        <v>-0.2107610379163121</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.230693337844438</v>
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.20159743408726</v>
+        <v>-8.179860845777281</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1270920140729372</v>
+        <v>-0.1183973787489458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.118999834304015</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.482503483293305</v>
+        <v>2.57392334416273</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.494517810582422</v>
+        <v>-7.472781222272443</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1529528016686972</v>
+        <v>0.1616474369926886</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.118999834304015</v>
+        <v>-0.9666333995216414</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.479716449633004</v>
+        <v>2.571136310502429</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388723</v>
+        <v>3.839374447388722</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.454333512216231</v>
+        <v>-7.432596923906252</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1693701449030147</v>
+        <v>0.1780647802270061</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.078815535937824</v>
+        <v>-0.9264491011554506</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.50417065254056</v>
+        <v>2.595590513409984</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626468</v>
+        <v>3.856161751626467</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.290933641276869</v>
+        <v>-7.26919705296689</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2340969144995166</v>
+        <v>0.242791549823508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9154156649984615</v>
+        <v>-0.7630492302160882</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.601577396324935</v>
+        <v>2.692997257194359</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.05745241904727</v>
+        <v>-7.035715830737291</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3354138322292082</v>
+        <v>0.3441084675532</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6819344427688629</v>
+        <v>-0.5295680079864896</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.749590558500546</v>
+        <v>2.841010419369971</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.907786028039755</v>
+        <v>-6.886049439729776</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3923881783192553</v>
+        <v>0.4010828136432467</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.589030951526327</v>
+        <v>-0.4366645167439537</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.802440442933109</v>
+        <v>2.893860303802533</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.775510554408869</v>
+        <v>-6.75377396609889</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4406658545186368</v>
+        <v>0.4493604898426287</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4567554778954404</v>
+        <v>-0.304389043113067</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.877173213858668</v>
+        <v>2.968593074728092</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.619772221849127</v>
+        <v>-6.598035633539148</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5057762482301702</v>
+        <v>0.514470883554162</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3010171453356988</v>
+        <v>-0.1486507105533255</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.97343127408215</v>
+        <v>3.064851134951573</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.534807555119807</v>
+        <v>-6.513070966809828</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.552668456145557</v>
+        <v>0.5613630914695489</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2160524786063792</v>
+        <v>-0.06368604382400589</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.0373164153434</v>
+        <v>3.128736276212824</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.640397544892911</v>
+        <v>-6.618660956582932</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3824565306370964</v>
+        <v>0.3911511659610882</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3216424683794836</v>
+        <v>-0.1692760335971102</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.845986491880319</v>
+        <v>2.937406352749742</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.572162960267484</v>
+        <v>-6.550426371957505</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4582947063643541</v>
+        <v>0.4669893416883455</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3032271455069476</v>
+        <v>-0.1508607107245742</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.905580027480926</v>
+        <v>2.99699988835035</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.424222918859885</v>
+        <v>-6.402486330549905</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3975918002392262</v>
+        <v>0.4062864355632176</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.28290622959839</v>
+        <v>-0.1305397948160167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.797893654337893</v>
+        <v>2.889313515207317</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.371253396605896</v>
+        <v>-6.349516808295917</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4100656228873434</v>
+        <v>0.4187602582113348</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2299367073444011</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.820961381436809</v>
+        <v>2.912381242306233</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.205465200645605</v>
+        <v>-6.183728612335626</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4694202891763664</v>
+        <v>0.4781149245003582</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2299367073444011</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.814000769341716</v>
+        <v>2.90542063021114</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.172101994166836</v>
+        <v>-6.150365405856857</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4972279261490171</v>
+        <v>0.5059225614730085</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2299367073444011</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.828463123722859</v>
+        <v>2.919882984592283</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.063842857044315</v>
+        <v>-6.042106268734336</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5350637014572208</v>
+        <v>0.5437583367812122</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2299367073444011</v>
+        <v>-0.07757027256202781</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.822995244182054</v>
+        <v>2.914415105051478</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.940551722227184</v>
+        <v>-5.918815133917205</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5818782493946499</v>
+        <v>0.5905728847186418</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1066455725272706</v>
+        <v>0.04572086225510269</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.894468019082909</v>
+        <v>2.985887879952333</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.887854855095893</v>
+        <v>-5.866118266785914</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6106579744844916</v>
+        <v>0.6193526098084834</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.05394870539597946</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.933787117599008</v>
+        <v>3.025206978468433</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.644089413112448</v>
+        <v>-5.622352824802469</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.70394485962492</v>
+        <v>0.7126394949489119</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.05394870539597946</v>
+        <v>0.09841772938639387</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.929567825946059</v>
+        <v>3.020987686815483</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.554313740735976</v>
+        <v>-5.532577152425997</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7419794424955248</v>
+        <v>0.7506740778195167</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.007650739518330563</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.968651806814661</v>
+        <v>3.060071667684086</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.304463346786902</v>
+        <v>-5.282726758476922</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8346616750588569</v>
+        <v>0.8433563103828488</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.007650739518330563</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.961393881798363</v>
+        <v>3.052813742667788</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.128571254319469</v>
+        <v>-5.10683466600949</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9086176355664786</v>
+        <v>0.9173122708904704</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.007650739518330563</v>
+        <v>0.1600171743007039</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.964993005319012</v>
+        <v>3.056412866188436</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.957124791297006</v>
+        <v>-4.935388202987027</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9905237268300175</v>
+        <v>0.9992183621540094</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1790972025407937</v>
+        <v>0.331463637323167</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.081188389187044</v>
+        <v>3.172608250056468</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.877102504187885</v>
+        <v>-4.855365915877906</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.021553119289963</v>
+        <v>1.030247754613955</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2591194896499147</v>
+        <v>0.411485924432288</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.128222239068813</v>
+        <v>3.219642099938238</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.813466761953951</v>
+        <v>-4.791730173643971</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.051702217237854</v>
+        <v>1.060396852561846</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3227552318838492</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.171098485463491</v>
+        <v>3.262518346332915</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.719769443737555</v>
+        <v>-4.698032855427576</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.070375403308208</v>
+        <v>1.079070038632199</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3227552318838492</v>
+        <v>0.4751216666662225</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.152292744247287</v>
+        <v>3.243712605116711</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.730272066802844</v>
+        <v>-4.708535478492865</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.06791743070697</v>
+        <v>1.076612066030961</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3122526088185603</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.147734247032991</v>
+        <v>3.239154107902415</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367677</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.65802949863165</v>
+        <v>-4.636292910321671</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.100743771810268</v>
+        <v>1.109438407134259</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3122526088185603</v>
+        <v>0.4646190436009336</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.151663560867811</v>
+        <v>3.243083421737235</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879958</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.640315811753784</v>
+        <v>-4.538732806063556</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.108507830478754</v>
+        <v>1.149141032754845</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3154339377154771</v>
+        <v>0.486084087898157</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.154250942123301</v>
+        <v>3.256641032232909</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.531510926274057</v>
+        <v>-4.429927920583829</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.149027855890638</v>
+        <v>1.18966105816673</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3154339377154771</v>
+        <v>0.486084087898157</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.151249013343295</v>
+        <v>3.253639103452903</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.311490128237047</v>
+        <v>-4.209907122546818</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.238615212116057</v>
+        <v>1.279248414392148</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4566537827834574</v>
+        <v>0.6273039329661373</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.237559957394697</v>
+        <v>3.339950047504305</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.178622439173769</v>
+        <v>-4.077039433483541</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.307656470543191</v>
+        <v>1.348289672819282</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4566537827834574</v>
+        <v>0.6273039329661373</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.25345414019652</v>
+        <v>3.355844230306128</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.05844935580927</v>
+        <v>-3.956866350119042</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.356871548329292</v>
+        <v>1.397504750605383</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5768268661479563</v>
+        <v>0.7474770163306362</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.326703834655522</v>
+        <v>3.42909392476513</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.923195994479293</v>
+        <v>-3.821612988789065</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.421060995422723</v>
+        <v>1.461694197698814</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7120802274779334</v>
+        <v>0.8827303776606134</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.417943954014948</v>
+        <v>3.520334044124556</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.983070821836986</v>
+        <v>-3.881487816146757</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.383148555881072</v>
+        <v>1.423781758157163</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6522054001202413</v>
+        <v>0.8228555503029212</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.368056549001758</v>
+        <v>3.470446639111366</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.863250590926148</v>
+        <v>-3.76166758523592</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.446365817479615</v>
+        <v>1.486999019755707</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6522054001202413</v>
+        <v>0.8228555503029212</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.383345718235967</v>
+        <v>3.485735808345575</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.865720297387954</v>
+        <v>-3.764137291697726</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.353022134217334</v>
+        <v>1.393655336493426</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6497356936584351</v>
+        <v>0.8203858438411151</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.289508093681325</v>
+        <v>3.391898183790933</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.934090483711964</v>
+        <v>-3.832507478021736</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.244935921173032</v>
+        <v>1.285569123449123</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.65901139269465</v>
+        <v>0.8296615428773301</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.214335374588355</v>
+        <v>3.316725464697963</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.947878536559011</v>
+        <v>-3.846295530868782</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.229857408666104</v>
+        <v>1.270490610942196</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.65901139269465</v>
+        <v>0.8296615428773301</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.204772083220246</v>
+        <v>3.307162173329854</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.0033986124516</v>
+        <v>-3.901815606761372</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.344680215001271</v>
+        <v>1.385313417277362</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.65901139269465</v>
+        <v>0.8296615428773301</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.341802919912449</v>
+        <v>3.444193010022057</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205893</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.827924352659131</v>
+        <v>-3.726341346968903</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.419437150910047</v>
+        <v>1.460070353186138</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.65901139269465</v>
+        <v>0.8296615428773301</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.346370151904237</v>
+        <v>3.448760242013845</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.93886060530038</v>
+        <v>-3.837277599610151</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.350804678614754</v>
+        <v>1.391437880890846</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.65901139269465</v>
+        <v>0.8296615428773301</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.322112180665444</v>
+        <v>3.424502270775052</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.905197059828098</v>
+        <v>-3.803614054137869</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.292808410205117</v>
+        <v>1.333441612481208</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6926749381669319</v>
+        <v>0.863325088349612</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.270848621350262</v>
+        <v>3.37323871145987</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.845344440624375</v>
+        <v>-3.743761434934146</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.326921844318738</v>
+        <v>1.36755504659483</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6926749381669319</v>
+        <v>0.863325088349612</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.281021007782395</v>
+        <v>3.383411097892003</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.759100977597997</v>
+        <v>-3.657517971907769</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.35636550010315</v>
+        <v>1.396998702379241</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6926749381669319</v>
+        <v>0.863325088349612</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.275967278356255</v>
+        <v>3.378357368465863</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.804407796996977</v>
+        <v>-3.702824791306749</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.330018547788083</v>
+        <v>1.370651750064175</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6518647751577011</v>
+        <v>0.8225149253403812</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.243256955995242</v>
+        <v>3.34564704610485</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.833440901699279</v>
+        <v>-3.73185789600905</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.318957178940264</v>
+        <v>1.359590381216355</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6518647751577011</v>
+        <v>0.8225149253403812</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.243808829028344</v>
+        <v>3.346198919137952</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.74063042024842</v>
+        <v>-3.639047414558191</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.285354063411973</v>
+        <v>1.325987265688065</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7446752566085605</v>
+        <v>0.9153254067912405</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.228767809790225</v>
+        <v>3.331157899899833</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.785019889577847</v>
+        <v>-3.683436883887619</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.269471751604803</v>
+        <v>1.310104953880895</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7002857872791328</v>
+        <v>0.8709359374618129</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.204007604117169</v>
+        <v>3.306397694226777</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.90156149468319</v>
+        <v>-3.799978488992962</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.217930818074389</v>
+        <v>1.25856402035048</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5837441821737901</v>
+        <v>0.7543943323564701</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.129158349565687</v>
+        <v>3.231548439675294</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.941485589265762</v>
+        <v>-3.839902583575533</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.207452476072028</v>
+        <v>1.248085678348119</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5837441821737901</v>
+        <v>0.7543943323564701</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.134649645396354</v>
+        <v>3.237039735505962</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.969265987167115</v>
+        <v>-3.867682981476886</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.207837518680025</v>
+        <v>1.248470720956117</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.555963784272437</v>
+        <v>0.726613934455117</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.129478608424081</v>
+        <v>3.231868698533689</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.087646659897253</v>
+        <v>-3.986063654207025</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9988409695886236</v>
+        <v>1.039474171864715</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4887459321214608</v>
+        <v>0.6593960823041408</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.927503617134149</v>
+        <v>3.029893707243757</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.196260738340584</v>
+        <v>-4.094677732650355</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.075544998930497</v>
+        <v>1.116178201206588</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4887459321214608</v>
+        <v>0.6593960823041408</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.047653277853354</v>
+        <v>3.150043367962962</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.160851700092441</v>
+        <v>-4.059268694402212</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.104221640332077</v>
+        <v>1.144854842608168</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4887459321214608</v>
+        <v>0.6593960823041408</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.062166303955677</v>
+        <v>3.164556394065285</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.12246803753429</v>
+        <v>-4.020885031844061</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.116994546697706</v>
+        <v>1.157627748973797</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.527129594679612</v>
+        <v>0.697779744862292</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.082615942832937</v>
+        <v>3.185006032942545</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.945351707499124</v>
+        <v>-3.843768701808895</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.184570107557074</v>
+        <v>1.225203309833166</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.527129594679612</v>
+        <v>0.697779744862292</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.079344971678239</v>
+        <v>3.181735061787847</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.99044395233267</v>
+        <v>-3.888860946642441</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.167216601385569</v>
+        <v>1.207849803661661</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4652335515102222</v>
+        <v>0.6358837016929022</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.042890737538518</v>
+        <v>3.145280827648126</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.811068531093902</v>
+        <v>-3.709485525403673</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.232753745187491</v>
+        <v>1.273386947463582</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6220103096809408</v>
+        <v>0.7926604598636209</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.130743767747363</v>
+        <v>3.233133857856971</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.856082744614508</v>
+        <v>-3.75449973892428</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.195555515110838</v>
+        <v>1.236188717386929</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5916614143663362</v>
+        <v>0.7623115645490163</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.09334188589019</v>
+        <v>3.195731975999798</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.123087254886943</v>
+        <v>-4.021504249196715</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.094445273340809</v>
+        <v>1.135078475616901</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3972983763233877</v>
+        <v>0.5679485265060678</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.982415625403367</v>
+        <v>3.084805715512975</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.224285036324116</v>
+        <v>-4.122702030633888</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.053170082662442</v>
+        <v>1.093803284938533</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3288895627780685</v>
+        <v>0.4995397129607486</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.940574259172677</v>
+        <v>3.042964349282285</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.217774069709804</v>
+        <v>-4.116191064019575</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.053374430862484</v>
+        <v>1.094007633138575</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3288895627780685</v>
+        <v>0.4995397129607486</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.938174220726994</v>
+        <v>3.040564310836602</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.198735942002506</v>
+        <v>-4.097152936312278</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.057514401153647</v>
+        <v>1.098147603429739</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2707059514468739</v>
+        <v>0.4413561016295541</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.899788773136522</v>
+        <v>3.00217886324613</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.251251744277327</v>
+        <v>-4.149668738587098</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.15580248187791</v>
+        <v>1.196435684154001</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2707059514468739</v>
+        <v>0.4413561016295541</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.019083174770712</v>
+        <v>3.12147326488032</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.265118505611245</v>
+        <v>-4.163535499921016</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.151089106330476</v>
+        <v>1.191722308606567</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.232848034713051</v>
+        <v>0.4034981848957311</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.997201753716552</v>
+        <v>3.09959184382616</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.220314334071315</v>
+        <v>-4.118731328381086</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.175019305343374</v>
+        <v>1.215652507619465</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.232848034713051</v>
+        <v>0.4034981848957311</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.003210284113478</v>
+        <v>3.105600374223086</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.072571363836312</v>
+        <v>-3.970988358146084</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.132066714714574</v>
+        <v>1.172699916990666</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4006553919479341</v>
+        <v>0.5713055421306144</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.001844919731607</v>
+        <v>3.104235009841215</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181166</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.156392585111011</v>
+        <v>-4.054809579420782</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.101331847736176</v>
+        <v>1.141965050012267</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4006553919479341</v>
+        <v>0.5713055421306144</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.004638541263088</v>
+        <v>3.107028631372696</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.150239879058226</v>
+        <v>-4.048656873367998</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.104455278548948</v>
+        <v>1.145088480825039</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4068080980007184</v>
+        <v>0.5774582481833986</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.008992513286417</v>
+        <v>3.111382603396025</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.167049177208728</v>
+        <v>-4.0654661715185</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.096812036028858</v>
+        <v>1.137445238304949</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3899987998502168</v>
+        <v>0.5606489500328971</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.997987411136227</v>
+        <v>3.100377501245835</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.104751178432606</v>
+        <v>-4.003168172742377</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.188066789336127</v>
+        <v>1.228699991612219</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4352930641246588</v>
+        <v>0.6059432143073391</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.091499523497713</v>
+        <v>3.193889613607321</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.902960980767448</v>
+        <v>-3.801377975077219</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.071074870116318</v>
+        <v>1.111708072392409</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6333112562938132</v>
+        <v>0.8039614064764935</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.012602440513332</v>
+        <v>3.11499253062294</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.953847693453643</v>
+        <v>-3.852264687763414</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.121010417364015</v>
+        <v>1.161643619640106</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5824245436076187</v>
+        <v>0.753074693790299</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.052360645223791</v>
+        <v>3.154750735333399</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.867236950803835</v>
+        <v>-3.765653945113607</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.170282450539982</v>
+        <v>1.210915652816073</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.661050274812777</v>
+        <v>0.8317004249954573</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.114163820062929</v>
+        <v>3.216553910172538</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.92744624880912</v>
+        <v>-3.825863243118891</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.144734712162539</v>
+        <v>1.185367914438631</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6008409768074925</v>
+        <v>0.7714911269901727</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.07657422208443</v>
+        <v>3.178964312194038</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.851024202377193</v>
+        <v>-3.749441196686965</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.173795148775239</v>
+        <v>1.21442835105133</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6008409768074925</v>
+        <v>0.7714911269901727</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.075065840124359</v>
+        <v>3.177455930233967</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.806651070738624</v>
+        <v>-3.705068065048396</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.191407268866102</v>
+        <v>1.232040471142194</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6452141084460611</v>
+        <v>0.8158642586287413</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.101552586542936</v>
+        <v>3.203942676652544</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.829131421597509</v>
+        <v>-3.727548415907281</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.176808922661139</v>
+        <v>1.21744212493723</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6452141084460611</v>
+        <v>0.8158642586287413</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.095946380681527</v>
+        <v>3.198336470791135</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.781475691036453</v>
+        <v>-3.679892685346225</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.202252971913366</v>
+        <v>1.242886174189457</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6928698390071167</v>
+        <v>0.863519989189797</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.130921576045965</v>
+        <v>3.233311666155573</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.680957532537699</v>
+        <v>-3.579374526847471</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.247352608687593</v>
+        <v>1.287985810963684</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7933879975058713</v>
+        <v>0.9640381476885516</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.196124844519942</v>
+        <v>3.298514934629551</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.665052203105346</v>
+        <v>-3.563469197415118</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.240469412936406</v>
+        <v>1.281102615212497</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7142753367966324</v>
+        <v>0.8849254869793126</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.135411920570271</v>
+        <v>3.237802010679879</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.620213801496948</v>
+        <v>-3.51863079580672</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.262502476190394</v>
+        <v>1.303135678466485</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7188187697415018</v>
+        <v>0.8894689199241821</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.142235682947821</v>
+        <v>3.24462577305743</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.639712257738956</v>
+        <v>-3.538129252048728</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.258864033324668</v>
+        <v>1.299497235600759</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6707341284615975</v>
+        <v>0.8413842786442778</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.117545837810957</v>
+        <v>3.219935927920565</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.595509420653056</v>
+        <v>-3.493926414962828</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.282424770686866</v>
+        <v>1.323057972962957</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.714936965547498</v>
+        <v>0.8855871157301782</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.149947142590334</v>
+        <v>3.252337232699943</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.603069086490103</v>
+        <v>-3.501486080799875</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.277810904821294</v>
+        <v>1.318444107097386</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7697403695573173</v>
+        <v>0.9403905197399975</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.181239185465473</v>
+        <v>3.283629275575081</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.44477766895083</v>
+        <v>-3.343194663260602</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.392375237020043</v>
+        <v>1.433008439296134</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7697403695573173</v>
+        <v>0.9403905197399975</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.232486950648513</v>
+        <v>3.334877040758121</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.237135665316354</v>
+        <v>-3.135552659626126</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.473872743068087</v>
+        <v>1.514505945344178</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9773823731917934</v>
+        <v>1.148032523374474</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.355512857423452</v>
+        <v>3.45790294753306</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.186103572593826</v>
+        <v>-3.084520566903598</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.489233808395368</v>
+        <v>1.529867010671459</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.028414465914322</v>
+        <v>1.199064616097002</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.381080341295239</v>
+        <v>3.483470431404847</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.12087939146662</v>
+        <v>-3.019296385776392</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.532510884938955</v>
+        <v>1.573144087215046</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.093638647041527</v>
+        <v>1.264288797224207</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.437402254064267</v>
+        <v>3.539792344173875</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.083452371395487</v>
+        <v>-2.981869365705259</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.543442665266689</v>
+        <v>1.58407586754278</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.098890185070709</v>
+        <v>1.269540335253389</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.436514149181057</v>
+        <v>3.538904239290665</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.103564027430195</v>
+        <v>-3.001981021739967</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.536654795184046</v>
+        <v>1.577287997460137</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.109917530068128</v>
+        <v>1.280567680250808</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.444387348510748</v>
+        <v>3.546777438620357</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.04981921300299</v>
+        <v>-2.948236207312762</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.718710491976139</v>
+        <v>1.75934369425223</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.11998083950859</v>
+        <v>1.29063098969127</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.610983105196236</v>
+        <v>3.713373195305844</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.975036951977978</v>
+        <v>-2.87345394628775</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.868736305603961</v>
+        <v>1.909369507880052</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.194763100533603</v>
+        <v>1.365413250716283</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.775965371029061</v>
+        <v>3.878355461138669</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.94895286771417</v>
+        <v>-2.847369862023942</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.870877915323343</v>
+        <v>1.911511117599434</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.194763100533603</v>
+        <v>1.365413250716283</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.76767334704292</v>
+        <v>3.870063437152528</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.861074954605049</v>
+        <v>-2.759491948914821</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.904222276150771</v>
+        <v>1.944855478426862</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.310688742956954</v>
+        <v>1.481338893139634</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.83542192808071</v>
+        <v>3.937812018190319</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.852182493211766</v>
+        <v>-2.750599487521538</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.925333666434875</v>
+        <v>1.965966868710967</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.310688742956954</v>
+        <v>1.481338893139634</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.852976333807502</v>
+        <v>3.95536642391711</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.020658610181643</v>
+        <v>-2.919075604491415</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.849798267051508</v>
+        <v>1.890431469327599</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.282740907240373</v>
+        <v>1.453391057423054</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.828062679782137</v>
+        <v>3.930452769891746</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.574402417552204</v>
+        <v>-2.472819411861976</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.009570441291146</v>
+        <v>2.050203643567237</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.188022237570741</v>
+        <v>1.358672387753421</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.752501175168219</v>
+        <v>3.854891265277828</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.551681313869051</v>
+        <v>-2.450098308178823</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.009322905261312</v>
+        <v>2.049956107537403</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.188022237570741</v>
+        <v>1.358672387753421</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.743165197665124</v>
+        <v>3.845555287774732</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.680883127163094</v>
+        <v>-2.579300121472865</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.116548305794864</v>
+        <v>2.157181508070955</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.058820424276698</v>
+        <v>1.229470574459379</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.824550235539868</v>
+        <v>3.926940325649475</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.835664133941349</v>
+        <v>-2.734081128251121</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.091713725577208</v>
+        <v>2.132346927853299</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.025452750222222</v>
+        <v>1.196102900404902</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.841607453600829</v>
+        <v>3.943997543710436</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.828609443726176</v>
+        <v>-2.727026438035947</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.091210957652823</v>
+        <v>2.131844159928914</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.032507440437396</v>
+        <v>1.203157590620076</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.842515623719478</v>
+        <v>3.944905713829086</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.801658219399688</v>
+        <v>-2.700075213709459</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.111997601028159</v>
+        <v>2.15263080330425</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.047387786465115</v>
+        <v>1.218037936647795</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.861449984980851</v>
+        <v>3.963840075090459</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.937611227456004</v>
+        <v>-2.836028221765776</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.241719529950593</v>
+        <v>2.282352732226684</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.047387786465115</v>
+        <v>1.218037936647795</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.04555311712581</v>
+        <v>4.147943207235419</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.960019345260876</v>
+        <v>-2.858436339570648</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.224872977731637</v>
+        <v>2.265506180007728</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.047387786465115</v>
+        <v>1.218037936647795</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.037669812028803</v>
+        <v>4.140059902138412</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.988243580838476</v>
+        <v>-2.886660575148248</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.215637283050234</v>
+        <v>2.256270485326326</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.065364538916424</v>
+        <v>1.236014689099104</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.050509863049227</v>
+        <v>4.152899953158834</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.997684506727006</v>
+        <v>-2.896101501036778</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.26811463041667</v>
+        <v>2.30874783269276</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.187791656459815</v>
+        <v>1.358441806642495</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.180219851297108</v>
+        <v>4.282609941406717</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.049958114062647</v>
+        <v>-2.948375108372419</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.250096282027714</v>
+        <v>2.290729484303805</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.135518049124174</v>
+        <v>1.306168199306854</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.151746781441025</v>
+        <v>4.254136871550632</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.126288091663553</v>
+        <v>-3.024705085973325</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.217676103881127</v>
+        <v>2.258309306157217</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.135518049124174</v>
+        <v>1.306168199306854</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.1498585943348</v>
+        <v>4.252248684444408</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.328541811987907</v>
+        <v>-3.226958806297679</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.131594845354248</v>
+        <v>2.172228047630338</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9332643287998204</v>
+        <v>1.103914478982501</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.02332659174305</v>
+        <v>4.125716681852658</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.490110237515162</v>
+        <v>-3.388527231824934</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.065401485353498</v>
+        <v>2.106034687629589</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.806481405001941</v>
+        <v>0.9771315551846212</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.945690847674475</v>
+        <v>4.048080937784083</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389348</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.622411529612715</v>
+        <v>-3.520828523922487</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.025554375380395</v>
+        <v>2.066187577656486</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.806481405001941</v>
+        <v>0.9771315551846212</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.958764254540394</v>
+        <v>4.061154344650001</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.808279840451945</v>
+        <v>-3.706696834761717</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.943212247827643</v>
+        <v>1.983845450103734</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6479158116819933</v>
+        <v>0.8185659618646736</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.855630095331365</v>
+        <v>3.958020185440973</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.836180627561418</v>
+        <v>-3.73459762187119</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.930575974110856</v>
+        <v>1.971209176386947</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6133188875390585</v>
+        <v>0.7839690377217388</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.833395981972606</v>
+        <v>3.935786072082214</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.958706730264312</v>
+        <v>-3.857123724574084</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.878329977006897</v>
+        <v>1.918963179282988</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4907927848361646</v>
+        <v>0.6614429350188449</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.756644764328068</v>
+        <v>3.859034854437676</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.1892212264499</v>
+        <v>-4.087638220759672</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.852830138123165</v>
+        <v>1.893463340399256</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2602782886505759</v>
+        <v>0.4309284388332562</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.685042026207219</v>
+        <v>3.787432116316827</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.445942044444724</v>
+        <v>-4.344359038754496</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.890453529927083</v>
+        <v>1.931086732203174</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1518637145067611</v>
+        <v>0.3225138646894413</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.760305000722777</v>
+        <v>3.862695090832385</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.599928462220864</v>
+        <v>-4.498345456530637</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.897839231962267</v>
+        <v>1.938472434238357</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1518637145067611</v>
+        <v>0.3225138646894413</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.829285269868417</v>
+        <v>3.931675359978025</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.549406558393199</v>
+        <v>-4.447823552702971</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.904099195613454</v>
+        <v>1.944732397889545</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1518637145067611</v>
+        <v>0.3225138646894413</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.815336471988537</v>
+        <v>3.917726562098146</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.801881712400923</v>
+        <v>-4.700298706710695</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.814979623065778</v>
+        <v>1.855612825341869</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1518637145067611</v>
+        <v>0.3225138646894413</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.827206961043951</v>
+        <v>3.92959705115356</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.094777468880335</v>
+        <v>-4.993194463190108</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.699031854992957</v>
+        <v>1.739665057269048</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1518637145067611</v>
+        <v>0.3225138646894413</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.828417495562895</v>
+        <v>3.930807585672503</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.281441597015143</v>
+        <v>-5.179858591324916</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.628487945966355</v>
+        <v>1.669121148242446</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1251247436822012</v>
+        <v>0.2957748938648814</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.816495855295481</v>
+        <v>3.918885945405089</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.559405992598417</v>
+        <v>-5.457822986908189</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.512380040469235</v>
+        <v>1.553013242745326</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.03550500939671691</v>
+        <v>0.2061551595793972</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.75780186746038</v>
+        <v>3.860191957569988</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.676373685237308</v>
+        <v>-5.57479067954708</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.627797020112723</v>
+        <v>1.668430222388813</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.03550500939671691</v>
+        <v>0.2061551595793972</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.920005924159423</v>
+        <v>4.022396014269032</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.761091627458261</v>
+        <v>-5.659508621768033</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.588756481188156</v>
+        <v>1.629389683464246</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04961101953132946</v>
+        <v>0.1210391306513508</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.86378294476641</v>
+        <v>3.966173034876018</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.843026445727144</v>
+        <v>-5.741443440036917</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.566211971449094</v>
+        <v>1.606845173725184</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.05954576511840964</v>
+        <v>0.1111043850642706</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.868051514982653</v>
+        <v>3.970441605092261</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332687</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.945002567975552</v>
+        <v>-5.843419562285324</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.534347161005633</v>
+        <v>1.574980363281724</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1615218873668172</v>
+        <v>0.009128262815863042</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.815791480089511</v>
+        <v>3.918181570199119</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.83499628449833</v>
+        <v>-5.733413278808102</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.570502561640697</v>
+        <v>1.611135763916788</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.138317315449542</v>
+        <v>0.03233283473313825</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.821867110484051</v>
+        <v>3.92425720059366</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.691936708757405</v>
+        <v>-5.590353703067177</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.631976402659042</v>
+        <v>1.672609604935132</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1303038888595627</v>
+        <v>0.04034626132311753</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.830925177160013</v>
+        <v>3.933315267269622</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.390489983285567</v>
+        <v>-5.28890697759534</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.759815975730313</v>
+        <v>1.800449178006403</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1711428366122745</v>
+        <v>0.3417929867949548</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.019054095325652</v>
+        <v>4.121444185435259</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.415080227520751</v>
+        <v>-5.313497221830524</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.75095105578895</v>
+        <v>1.79158425806504</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1711428366122745</v>
+        <v>0.3417929867949548</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.020025273078362</v>
+        <v>4.122415363187971</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.364041851514231</v>
+        <v>-5.262458845824003</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.772209310571313</v>
+        <v>1.812842512847403</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1711428366122745</v>
+        <v>0.3417929867949548</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.020868177458118</v>
+        <v>4.123258267567725</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.3229025566476</v>
+        <v>-5.221319550957372</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.807703127392111</v>
+        <v>1.848336329668201</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2122821314789053</v>
+        <v>0.3829322816615856</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.064589853252241</v>
+        <v>4.16697994336185</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.212296416567998</v>
+        <v>-5.110713410877771</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.668129579547886</v>
+        <v>1.708762781823976</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3228882715585074</v>
+        <v>0.4935384217411876</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.947137533423937</v>
+        <v>4.049527623533545</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.342877151098841</v>
+        <v>-5.241294145408613</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.619399329809513</v>
+        <v>1.660032532085603</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1923075370276648</v>
+        <v>0.362957687210345</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.872291136779395</v>
+        <v>3.974681226889003</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.178380816907879</v>
+        <v>-5.076797811217651</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.66962468256198</v>
+        <v>1.71025788483807</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.1923075370276648</v>
+        <v>0.362957687210345</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.856717955855478</v>
+        <v>3.959108045965086</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.205750749592311</v>
+        <v>-5.104167743902083</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.657864419924637</v>
+        <v>1.698497622200728</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.1923075370276648</v>
+        <v>0.362957687210345</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.855905666291907</v>
+        <v>3.958295756401515</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.2161359444822</v>
+        <v>-5.114552938791973</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.663579121093753</v>
+        <v>1.704212323369844</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.1819223421377755</v>
+        <v>0.3525724923204557</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.859543328483046</v>
+        <v>3.961933418592655</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.234724103204425</v>
+        <v>-5.133141097514198</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.726980863381288</v>
+        <v>1.767614065657379</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.1633341834155502</v>
+        <v>0.3339843335982304</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.919227439026137</v>
+        <v>4.021617529135744</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.235022649900461</v>
+        <v>-5.133439644210234</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.723730455521173</v>
+        <v>1.764363657797263</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.1633341834155502</v>
+        <v>0.3339843335982304</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.916096449844435</v>
+        <v>4.018486539954043</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.128549796808271</v>
+        <v>-5.032616510519806</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.77085049169744</v>
+        <v>1.809223806212826</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.2351568824064776</v>
+        <v>0.3464485490825842</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.963720964178383</v>
+        <v>4.030495964184047</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.937768436055864</v>
+        <v>-4.841835149767399</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.847292289476946</v>
+        <v>1.885665603992332</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.425938243158885</v>
+        <v>0.5372299098349915</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.07831903410837</v>
+        <v>4.145094034114035</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.919251582014043</v>
+        <v>-4.823318295725579</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.834535876831271</v>
+        <v>1.872909191346657</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.4388683725840932</v>
+        <v>0.5501600392601997</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.065913957501092</v>
+        <v>4.132688957506756</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.894058397512725</v>
+        <v>-4.798125111224261</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.879580087243857</v>
+        <v>1.917953401759242</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.4640615570854115</v>
+        <v>0.5753532237615181</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.115996804813941</v>
+        <v>4.182771804819605</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.882004270599762</v>
+        <v>-4.786070984311298</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.87808830591048</v>
+        <v>1.916461620425865</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.4761156839983743</v>
+        <v>0.5874073506744809</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.116915848863156</v>
+        <v>4.183690848868821</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.888627517290121</v>
+        <v>-4.792694231001656</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.877319637418472</v>
+        <v>1.915692951933858</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.469492437308016</v>
+        <v>0.5807841039841226</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.114822531033077</v>
+        <v>4.181597531038742</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.785746927761528</v>
+        <v>-4.689813641473063</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.931322899107792</v>
+        <v>1.969696213623177</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.572373026836609</v>
+        <v>0.6836646935127155</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.189401910628116</v>
+        <v>4.25617691063378</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.809188966941615</v>
+        <v>-4.71325568065315</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.942148753609351</v>
+        <v>1.980522068124737</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.572373026836609</v>
+        <v>0.6836646935127155</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.20960458080171</v>
+        <v>4.276379580807374</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781706</v>
+        <v>3.666767386781708</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.827261475233226</v>
+        <v>-4.731328188944762</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934919750292707</v>
+        <v>1.973293064808092</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.572373026836609</v>
+        <v>0.6836646935127155</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.20960458080171</v>
+        <v>4.276379580807374</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082835</v>
+        <v>3.670068888082837</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.058435269109858</v>
+        <v>-4.962501982821394</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.802702146335521</v>
+        <v>1.841075460850906</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.572373026836609</v>
+        <v>0.6836646935127155</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.169856494395177</v>
+        <v>4.23663149440084</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.027149248569403</v>
+        <v>-4.931215962280938</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.822239173548643</v>
+        <v>1.860612488064028</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.6036590473770643</v>
+        <v>0.7149507140531709</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.19565072571639</v>
+        <v>4.262425725722053</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677827</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.874123856456118</v>
+        <v>-4.778190570167654</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.98262032996686</v>
+        <v>2.020993644482246</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.7566844394903485</v>
+        <v>0.867976106166455</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.386636960557264</v>
+        <v>4.453411960562928</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.902431170329389</v>
+        <v>-4.806497884040924</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.158763629325845</v>
+        <v>2.19713694384123</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.7566844394903485</v>
+        <v>0.867976106166455</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.574103185465557</v>
+        <v>4.64087818547122</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.069024395442911</v>
+        <v>-4.973091109154447</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.061529290634518</v>
+        <v>2.099902605149904</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.590091214376826</v>
+        <v>0.7013828810529326</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.443550201751526</v>
+        <v>4.51032520175719</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568386</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.895960016060611</v>
+        <v>-4.800026729772147</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.134431445049156</v>
+        <v>2.172804759564541</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.590091214376826</v>
+        <v>0.7013828810529326</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.447226604413244</v>
+        <v>4.514001604418907</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.740601586682208</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.866714035604915</v>
+        <v>-4.77078074931645</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.14374789235493</v>
+        <v>2.182121206870315</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.590091214376826</v>
+        <v>0.7013828810529326</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.444844659536739</v>
+        <v>4.511619659542403</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539109</v>
+        <v>3.699424827539112</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.873471457531876</v>
+        <v>-4.780496025654586</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.13833816274178</v>
+        <v>2.175528335492696</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5833337924498644</v>
+        <v>0.6916676047147958</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.438083445538196</v>
+        <v>4.503083732897156</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.865781134771164</v>
+        <v>3.84981069930919</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.999439551001559</v>
+        <v>-4.89080245543461</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.089379727497141</v>
+        <v>2.13283456572392</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4573656989801811</v>
+        <v>0.5813611749347727</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.363931391599621</v>
+        <v>4.438328677172376</v>
       </c>
     </row>
   </sheetData>
